--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>60014</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.941999971866608</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.927999973297119</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>136309</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.938000023365021</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.921000003814697</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.921000003814697</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.926999986171722</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>122637</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.949000000953674</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.945999979972839</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>89382</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.944999992847443</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.926999986171722</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.926999986171722</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.949000000953674</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>145278</v>
+        <v>74379</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.934000015258789</v>
+        <v>0.935999989509583</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.924000024795532</v>
+        <v>0.926999986171722</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.925999999046326</v>
+        <v>0.926999986171722</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.924000024795532</v>
+        <v>0.926999986171722</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>279241</v>
+        <v>145278</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.984000027179718</v>
+        <v>0.934000015258789</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.925000011920929</v>
+        <v>0.924000024795532</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.935999989509583</v>
+        <v>0.925999999046326</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.984000027179718</v>
+        <v>0.924000024795532</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>322354</v>
+        <v>279241</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.978999972343445</v>
+        <v>0.984000027179718</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.931999981403351</v>
+        <v>0.925000011920929</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.931999981403351</v>
+        <v>0.935999989509583</v>
       </c>
       <c r="F2717" t="n">
-        <v>0.953999996185303</v>
+        <v>0.984000027179718</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>112982</v>
+        <v>322354</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.954999983310699</v>
+        <v>0.978999972343445</v>
       </c>
       <c r="D2718" t="n">
         <v>0.931999981403351</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.953000009059906</v>
+        <v>0.931999981403351</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.944000005722046</v>
+        <v>0.953999996185303</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>60014</v>
+        <v>112982</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.941999971866608</v>
+        <v>0.954999983310699</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.927999973297119</v>
+        <v>0.931999981403351</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.930000007152557</v>
+        <v>0.953000009059906</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.930000007152557</v>
+        <v>0.944000005722046</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>136309</v>
+        <v>60014</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.938000023365021</v>
+        <v>0.941999971866608</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.921000003814697</v>
+        <v>0.927999973297119</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.921000003814697</v>
+        <v>0.930000007152557</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.926999986171722</v>
+        <v>0.930000007152557</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>122637</v>
+        <v>136309</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.949000000953674</v>
+        <v>0.938000023365021</v>
       </c>
       <c r="D2721" t="n">
-        <v>0.931999981403351</v>
+        <v>0.921000003814697</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.931999981403351</v>
+        <v>0.921000003814697</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.945999979972839</v>
+        <v>0.926999986171722</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>89382</v>
+        <v>122637</v>
       </c>
       <c r="C2722" t="n">
+        <v>0.949000000953674</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.931999981403351</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.945999979972839</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>248836</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.953000009059906</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.921999990940094</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.926999986171722</v>
+      </c>
+      <c r="F2723" t="n">
         <v>0.944999992847443</v>
       </c>
-      <c r="D2722" t="n">
-        <v>0.926999986171722</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>0.926999986171722</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>0.949000000953674</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.830999970436096</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.833999991416931</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>427276</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.846000015735626</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.820999979972839</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.820999979972839</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -63285,7 +63285,7 @@
         <v>427276</v>
       </c>
       <c r="C2736" t="n">
-        <v>0.846000015735626</v>
+        <v>0.850000023841858</v>
       </c>
       <c r="D2736" t="n">
         <v>0.820999979972839</v>
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.820999979972839</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.850000023841858</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>175103</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.837999999523163</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.850000023841858</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.850000023841858</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.841000020503998</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>157474</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.841000020503998</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.825999975204468</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.832000017166138</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.832000017166138</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.825999975204468</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>93667</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.833999991416931</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.825999975204468</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.825999975204468</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>157071</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.845000028610229</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.830999970436096</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.830999970436096</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.830999970436096</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RCS.MI.xlsx
+++ b/data/RCS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G2" t="n">
-        <v>0.351986587047577</v>
+        <v>0.351986646652222</v>
       </c>
       <c r="H2" t="n">
         <v>5728108</v>
@@ -456,7 +456,7 @@
         <v>0.603500008583069</v>
       </c>
       <c r="G3" t="n">
-        <v>0.355818927288055</v>
+        <v>0.355818957090378</v>
       </c>
       <c r="H3" t="n">
         <v>6222140</v>
@@ -485,7 +485,7 @@
         <v>0.578999996185303</v>
       </c>
       <c r="G4" t="n">
-        <v>0.341373890638351</v>
+        <v>0.341373950242996</v>
       </c>
       <c r="H4" t="n">
         <v>4131152</v>
@@ -514,7 +514,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G5" t="n">
-        <v>0.353755384683609</v>
+        <v>0.353755354881287</v>
       </c>
       <c r="H5" t="n">
         <v>10686633</v>
@@ -601,7 +601,7 @@
         <v>0.58050000667572</v>
       </c>
       <c r="G8" t="n">
-        <v>0.342258274555206</v>
+        <v>0.342258334159851</v>
       </c>
       <c r="H8" t="n">
         <v>9644799</v>
@@ -659,7 +659,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>0.382055789232254</v>
+        <v>0.382055819034576</v>
       </c>
       <c r="H10" t="n">
         <v>12803149</v>
@@ -717,7 +717,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G12" t="n">
-        <v>0.347269833087921</v>
+        <v>0.347269862890244</v>
       </c>
       <c r="H12" t="n">
         <v>3997139</v>
@@ -746,7 +746,7 @@
         <v>0.567499995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>0.334593623876572</v>
+        <v>0.334593594074249</v>
       </c>
       <c r="H13" t="n">
         <v>3764408</v>
@@ -775,7 +775,7 @@
         <v>0.528999984264374</v>
       </c>
       <c r="G14" t="n">
-        <v>0.311894297599792</v>
+        <v>0.31189426779747</v>
       </c>
       <c r="H14" t="n">
         <v>2441909</v>
@@ -833,7 +833,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G16" t="n">
-        <v>0.336067587137222</v>
+        <v>0.3360675573349</v>
       </c>
       <c r="H16" t="n">
         <v>4044236</v>
@@ -949,7 +949,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G20" t="n">
-        <v>0.318379819393158</v>
+        <v>0.31837984919548</v>
       </c>
       <c r="H20" t="n">
         <v>4006046</v>
@@ -1036,7 +1036,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G23" t="n">
-        <v>0.336067587137222</v>
+        <v>0.3360675573349</v>
       </c>
       <c r="H23" t="n">
         <v>1303298</v>
@@ -1065,7 +1065,7 @@
         <v>0.564499974250793</v>
       </c>
       <c r="G24" t="n">
-        <v>0.332824856042862</v>
+        <v>0.332824885845184</v>
       </c>
       <c r="H24" t="n">
         <v>2244610</v>
@@ -1123,7 +1123,7 @@
         <v>0.552999973297119</v>
       </c>
       <c r="G26" t="n">
-        <v>0.32604455947876</v>
+        <v>0.326044499874115</v>
       </c>
       <c r="H26" t="n">
         <v>1156311</v>
@@ -1152,7 +1152,7 @@
         <v>0.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.294796139001846</v>
+        <v>0.294796109199524</v>
       </c>
       <c r="H27" t="n">
         <v>1715796</v>
@@ -1268,7 +1268,7 @@
         <v>0.435600012540817</v>
       </c>
       <c r="G31" t="n">
-        <v>0.256826400756836</v>
+        <v>0.256826430559158</v>
       </c>
       <c r="H31" t="n">
         <v>3669546</v>
@@ -1384,7 +1384,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G35" t="n">
-        <v>0.305998355150223</v>
+        <v>0.305998414754868</v>
       </c>
       <c r="H35" t="n">
         <v>1739590</v>
@@ -1413,7 +1413,7 @@
         <v>0.549499988555908</v>
       </c>
       <c r="G36" t="n">
-        <v>0.323980927467346</v>
+        <v>0.323980957269669</v>
       </c>
       <c r="H36" t="n">
         <v>4491873</v>
@@ -1500,7 +1500,7 @@
         <v>0.516499996185303</v>
       </c>
       <c r="G39" t="n">
-        <v>0.304524451494217</v>
+        <v>0.304524391889572</v>
       </c>
       <c r="H39" t="n">
         <v>1664409</v>
@@ -1529,7 +1529,7 @@
         <v>0.496199995279312</v>
       </c>
       <c r="G40" t="n">
-        <v>0.292555689811707</v>
+        <v>0.292555660009384</v>
       </c>
       <c r="H40" t="n">
         <v>1411516</v>
@@ -1645,7 +1645,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G44" t="n">
-        <v>0.359651297330856</v>
+        <v>0.359651237726212</v>
       </c>
       <c r="H44" t="n">
         <v>8479760</v>
@@ -1674,7 +1674,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G45" t="n">
-        <v>0.331350892782211</v>
+        <v>0.331350833177567</v>
       </c>
       <c r="H45" t="n">
         <v>10790857</v>
@@ -1703,7 +1703,7 @@
         <v>0.581499993801117</v>
       </c>
       <c r="G46" t="n">
-        <v>0.342847853899002</v>
+        <v>0.342847883701324</v>
       </c>
       <c r="H46" t="n">
         <v>7459305</v>
@@ -1877,7 +1877,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G52" t="n">
-        <v>0.307767182588577</v>
+        <v>0.3077672123909</v>
       </c>
       <c r="H52" t="n">
         <v>4330461</v>
@@ -1935,7 +1935,7 @@
         <v>0.504499971866608</v>
       </c>
       <c r="G54" t="n">
-        <v>0.297449290752411</v>
+        <v>0.297449320554733</v>
       </c>
       <c r="H54" t="n">
         <v>1380137</v>
@@ -2022,7 +2022,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G57" t="n">
-        <v>0.297744125127792</v>
+        <v>0.29774409532547</v>
       </c>
       <c r="H57" t="n">
         <v>973506</v>
@@ -2051,7 +2051,7 @@
         <v>0.504499971866608</v>
       </c>
       <c r="G58" t="n">
-        <v>0.297449290752411</v>
+        <v>0.297449320554733</v>
       </c>
       <c r="H58" t="n">
         <v>1108097</v>
@@ -2196,7 +2196,7 @@
         <v>0.471300005912781</v>
       </c>
       <c r="G63" t="n">
-        <v>0.277874827384949</v>
+        <v>0.277874797582626</v>
       </c>
       <c r="H63" t="n">
         <v>1652522</v>
@@ -2254,7 +2254,7 @@
         <v>0.422199994325638</v>
       </c>
       <c r="G65" t="n">
-        <v>0.248925864696503</v>
+        <v>0.248925879597664</v>
       </c>
       <c r="H65" t="n">
         <v>1848982</v>
@@ -2283,7 +2283,7 @@
         <v>0.411199986934662</v>
       </c>
       <c r="G66" t="n">
-        <v>0.242440313100815</v>
+        <v>0.24244037270546</v>
       </c>
       <c r="H66" t="n">
         <v>1742432</v>
@@ -2312,7 +2312,7 @@
         <v>0.42179998755455</v>
       </c>
       <c r="G67" t="n">
-        <v>0.248690009117126</v>
+        <v>0.248690024018288</v>
       </c>
       <c r="H67" t="n">
         <v>1227853</v>
@@ -2341,7 +2341,7 @@
         <v>0.407999992370605</v>
       </c>
       <c r="G68" t="n">
-        <v>0.240553662180901</v>
+        <v>0.240553632378578</v>
       </c>
       <c r="H68" t="n">
         <v>1020713</v>
@@ -2370,7 +2370,7 @@
         <v>0.455000013113022</v>
       </c>
       <c r="G69" t="n">
-        <v>0.268264472484589</v>
+        <v>0.268264502286911</v>
       </c>
       <c r="H69" t="n">
         <v>2063027</v>
@@ -2399,7 +2399,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G70" t="n">
-        <v>0.345501095056534</v>
+        <v>0.345501035451889</v>
       </c>
       <c r="H70" t="n">
         <v>22162574</v>
@@ -2428,7 +2428,7 @@
         <v>0.58050000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>0.342258274555206</v>
+        <v>0.342258334159851</v>
       </c>
       <c r="H71" t="n">
         <v>8073771</v>
@@ -2457,7 +2457,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G72" t="n">
-        <v>0.336067587137222</v>
+        <v>0.3360675573349</v>
       </c>
       <c r="H72" t="n">
         <v>5826266</v>
@@ -2515,7 +2515,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G74" t="n">
-        <v>0.336067587137222</v>
+        <v>0.3360675573349</v>
       </c>
       <c r="H74" t="n">
         <v>5145635</v>
@@ -2544,7 +2544,7 @@
         <v>0.579500019550323</v>
       </c>
       <c r="G75" t="n">
-        <v>0.341668725013733</v>
+        <v>0.341668754816055</v>
       </c>
       <c r="H75" t="n">
         <v>2531035</v>
@@ -2573,7 +2573,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G76" t="n">
-        <v>0.343732267618179</v>
+        <v>0.343732297420502</v>
       </c>
       <c r="H76" t="n">
         <v>2091533</v>
@@ -2602,7 +2602,7 @@
         <v>0.582499980926514</v>
       </c>
       <c r="G77" t="n">
-        <v>0.343437433242798</v>
+        <v>0.343437492847443</v>
       </c>
       <c r="H77" t="n">
         <v>1726771</v>
@@ -2631,7 +2631,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G78" t="n">
-        <v>0.359651297330856</v>
+        <v>0.359651237726212</v>
       </c>
       <c r="H78" t="n">
         <v>6109221</v>
@@ -2689,7 +2689,7 @@
         <v>0.611500024795532</v>
       </c>
       <c r="G80" t="n">
-        <v>0.360535651445389</v>
+        <v>0.360535740852356</v>
       </c>
       <c r="H80" t="n">
         <v>857838</v>
@@ -2747,7 +2747,7 @@
         <v>0.597000002861023</v>
       </c>
       <c r="G82" t="n">
-        <v>0.351986587047577</v>
+        <v>0.351986646652222</v>
       </c>
       <c r="H82" t="n">
         <v>1768784</v>
@@ -2776,7 +2776,7 @@
         <v>0.583500027656555</v>
       </c>
       <c r="G83" t="n">
-        <v>0.344027072191238</v>
+        <v>0.344027161598206</v>
       </c>
       <c r="H83" t="n">
         <v>2482623</v>
@@ -2805,7 +2805,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G84" t="n">
-        <v>0.331940472126007</v>
+        <v>0.331940442323685</v>
       </c>
       <c r="H84" t="n">
         <v>3819493</v>
@@ -2863,7 +2863,7 @@
         <v>0.595499992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>0.351102203130722</v>
+        <v>0.351102232933044</v>
       </c>
       <c r="H86" t="n">
         <v>3363264</v>
@@ -2921,7 +2921,7 @@
         <v>0.584999978542328</v>
       </c>
       <c r="G88" t="n">
-        <v>0.344911456108093</v>
+        <v>0.344911426305771</v>
       </c>
       <c r="H88" t="n">
         <v>3396210</v>
@@ -2950,7 +2950,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G89" t="n">
-        <v>0.336067587137222</v>
+        <v>0.3360675573349</v>
       </c>
       <c r="H89" t="n">
         <v>5256371</v>
@@ -2979,7 +2979,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G90" t="n">
-        <v>0.353755384683609</v>
+        <v>0.353755354881287</v>
       </c>
       <c r="H90" t="n">
         <v>8230761</v>
@@ -3008,7 +3008,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G91" t="n">
-        <v>0.346090644598007</v>
+        <v>0.346090704202652</v>
       </c>
       <c r="H91" t="n">
         <v>9487961</v>
@@ -3037,7 +3037,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G92" t="n">
-        <v>0.353755384683609</v>
+        <v>0.353755354881287</v>
       </c>
       <c r="H92" t="n">
         <v>9366365</v>
@@ -3095,7 +3095,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G94" t="n">
-        <v>0.350807428359985</v>
+        <v>0.350807458162308</v>
       </c>
       <c r="H94" t="n">
         <v>3492166</v>
@@ -3124,7 +3124,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G95" t="n">
-        <v>0.408882230520248</v>
+        <v>0.408882260322571</v>
       </c>
       <c r="H95" t="n">
         <v>33075869</v>
@@ -3153,7 +3153,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G96" t="n">
-        <v>0.421558439731598</v>
+        <v>0.421558499336243</v>
       </c>
       <c r="H96" t="n">
         <v>23343098</v>
@@ -3182,7 +3182,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G97" t="n">
-        <v>0.422148048877716</v>
+        <v>0.422148108482361</v>
       </c>
       <c r="H97" t="n">
         <v>9052842</v>
@@ -3240,7 +3240,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G99" t="n">
-        <v>0.426864802837372</v>
+        <v>0.426864832639694</v>
       </c>
       <c r="H99" t="n">
         <v>7705095</v>
@@ -3269,7 +3269,7 @@
         <v>0.718500018119812</v>
       </c>
       <c r="G100" t="n">
-        <v>0.423622012138367</v>
+        <v>0.423622071743011</v>
       </c>
       <c r="H100" t="n">
         <v>4119815</v>
@@ -3298,7 +3298,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G101" t="n">
-        <v>0.424211621284485</v>
+        <v>0.424211591482162</v>
       </c>
       <c r="H101" t="n">
         <v>7253269</v>
@@ -3327,7 +3327,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G102" t="n">
-        <v>0.432171136140823</v>
+        <v>0.432171106338501</v>
       </c>
       <c r="H102" t="n">
         <v>9661648</v>
@@ -3385,7 +3385,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G104" t="n">
-        <v>0.451627671718597</v>
+        <v>0.451627641916275</v>
       </c>
       <c r="H104" t="n">
         <v>3693755</v>
@@ -3443,7 +3443,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G106" t="n">
-        <v>0.449269354343414</v>
+        <v>0.449269324541092</v>
       </c>
       <c r="H106" t="n">
         <v>6287582</v>
@@ -3472,7 +3472,7 @@
         <v>0.764500021934509</v>
       </c>
       <c r="G107" t="n">
-        <v>0.450743317604065</v>
+        <v>0.45074325799942</v>
       </c>
       <c r="H107" t="n">
         <v>8668559</v>
@@ -3530,7 +3530,7 @@
         <v>0.771499991416931</v>
       </c>
       <c r="G109" t="n">
-        <v>0.454870462417603</v>
+        <v>0.45487043261528</v>
       </c>
       <c r="H109" t="n">
         <v>3249545</v>
@@ -3559,7 +3559,7 @@
         <v>0.75</v>
       </c>
       <c r="G110" t="n">
-        <v>0.442194253206253</v>
+        <v>0.442194193601608</v>
       </c>
       <c r="H110" t="n">
         <v>3544053</v>
@@ -3588,7 +3588,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G111" t="n">
-        <v>0.443373382091522</v>
+        <v>0.443373411893845</v>
       </c>
       <c r="H111" t="n">
         <v>1440732</v>
@@ -3646,7 +3646,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G113" t="n">
-        <v>0.458997577428818</v>
+        <v>0.458997666835785</v>
       </c>
       <c r="H113" t="n">
         <v>2617023</v>
@@ -3675,7 +3675,7 @@
         <v>0.772499978542328</v>
       </c>
       <c r="G114" t="n">
-        <v>0.455460041761398</v>
+        <v>0.455459982156754</v>
       </c>
       <c r="H114" t="n">
         <v>4679301</v>
@@ -3704,7 +3704,7 @@
         <v>0.782999992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>0.461650758981705</v>
+        <v>0.461650669574738</v>
       </c>
       <c r="H115" t="n">
         <v>3811591</v>
@@ -3762,7 +3762,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G117" t="n">
-        <v>0.43983581662178</v>
+        <v>0.439835846424103</v>
       </c>
       <c r="H117" t="n">
         <v>1928963</v>
@@ -3791,7 +3791,7 @@
         <v>0.75</v>
       </c>
       <c r="G118" t="n">
-        <v>0.442194253206253</v>
+        <v>0.442194193601608</v>
       </c>
       <c r="H118" t="n">
         <v>2659942</v>
@@ -3849,7 +3849,7 @@
         <v>0.767499983310699</v>
       </c>
       <c r="G120" t="n">
-        <v>0.452512085437775</v>
+        <v>0.45251202583313</v>
       </c>
       <c r="H120" t="n">
         <v>7087782</v>
@@ -3936,7 +3936,7 @@
         <v>0.784500002861023</v>
       </c>
       <c r="G123" t="n">
-        <v>0.462535113096237</v>
+        <v>0.46253514289856</v>
       </c>
       <c r="H123" t="n">
         <v>3426875</v>
@@ -3965,7 +3965,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G124" t="n">
-        <v>0.449269354343414</v>
+        <v>0.449269324541092</v>
       </c>
       <c r="H124" t="n">
         <v>5241257</v>
@@ -4052,7 +4052,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G127" t="n">
-        <v>0.478748917579651</v>
+        <v>0.478748947381973</v>
       </c>
       <c r="H127" t="n">
         <v>4412125</v>
@@ -4081,7 +4081,7 @@
         <v>0.804499983787537</v>
       </c>
       <c r="G128" t="n">
-        <v>0.474326938390732</v>
+        <v>0.474326908588409</v>
       </c>
       <c r="H128" t="n">
         <v>3342172</v>
@@ -4110,7 +4110,7 @@
         <v>0.813499987125397</v>
       </c>
       <c r="G129" t="n">
-        <v>0.479633331298828</v>
+        <v>0.479633271694183</v>
       </c>
       <c r="H129" t="n">
         <v>8332842</v>
@@ -4139,7 +4139,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G130" t="n">
-        <v>0.489361524581909</v>
+        <v>0.489361643791199</v>
       </c>
       <c r="H130" t="n">
         <v>5007175</v>
@@ -4197,7 +4197,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G132" t="n">
-        <v>0.492309510707855</v>
+        <v>0.492309540510178</v>
       </c>
       <c r="H132" t="n">
         <v>5170096</v>
@@ -4226,7 +4226,7 @@
         <v>0.845000028610229</v>
       </c>
       <c r="G133" t="n">
-        <v>0.498205542564392</v>
+        <v>0.498205482959747</v>
       </c>
       <c r="H133" t="n">
         <v>2529416</v>
@@ -4255,7 +4255,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>0.502332627773285</v>
+        <v>0.50233268737793</v>
       </c>
       <c r="H134" t="n">
         <v>4721030</v>
@@ -4371,7 +4371,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>0.555690705776215</v>
+        <v>0.555690765380859</v>
       </c>
       <c r="H138" t="n">
         <v>5699918</v>
@@ -4429,7 +4429,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G140" t="n">
-        <v>0.536528944969177</v>
+        <v>0.536529004573822</v>
       </c>
       <c r="H140" t="n">
         <v>3100496</v>
@@ -4458,7 +4458,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G141" t="n">
-        <v>0.522378742694855</v>
+        <v>0.5223788022995</v>
       </c>
       <c r="H141" t="n">
         <v>1772750</v>
@@ -4516,7 +4516,7 @@
         <v>0.897499978542328</v>
       </c>
       <c r="G143" t="n">
-        <v>0.529159009456635</v>
+        <v>0.529159128665924</v>
       </c>
       <c r="H143" t="n">
         <v>840000</v>
@@ -4545,7 +4545,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G144" t="n">
-        <v>0.52709549665451</v>
+        <v>0.527095556259155</v>
       </c>
       <c r="H144" t="n">
         <v>742141</v>
@@ -4632,7 +4632,7 @@
         <v>0.834500014781952</v>
       </c>
       <c r="G147" t="n">
-        <v>0.492014765739441</v>
+        <v>0.492014735937119</v>
       </c>
       <c r="H147" t="n">
         <v>3274281</v>
@@ -4661,7 +4661,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.480517745018005</v>
+        <v>0.480517685413361</v>
       </c>
       <c r="H148" t="n">
         <v>2147821</v>
@@ -4690,7 +4690,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G149" t="n">
-        <v>0.481107324361801</v>
+        <v>0.481107264757156</v>
       </c>
       <c r="H149" t="n">
         <v>1484677</v>
@@ -4719,7 +4719,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G150" t="n">
-        <v>0.47992816567421</v>
+        <v>0.479928135871887</v>
       </c>
       <c r="H150" t="n">
         <v>738236</v>
@@ -4777,7 +4777,7 @@
         <v>0.734499990940094</v>
       </c>
       <c r="G152" t="n">
-        <v>0.433055549860001</v>
+        <v>0.433055520057678</v>
       </c>
       <c r="H152" t="n">
         <v>6285449</v>
@@ -4806,7 +4806,7 @@
         <v>0.762499988079071</v>
       </c>
       <c r="G153" t="n">
-        <v>0.449564188718796</v>
+        <v>0.449564129114151</v>
       </c>
       <c r="H153" t="n">
         <v>2885357</v>
@@ -4864,7 +4864,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G155" t="n">
-        <v>0.51058691740036</v>
+        <v>0.510586857795715</v>
       </c>
       <c r="H155" t="n">
         <v>5183024</v>
@@ -4922,7 +4922,7 @@
         <v>0.880500018596649</v>
       </c>
       <c r="G157" t="n">
-        <v>0.519136011600494</v>
+        <v>0.519136071205139</v>
       </c>
       <c r="H157" t="n">
         <v>1265515</v>
@@ -4951,7 +4951,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G158" t="n">
-        <v>0.536528944969177</v>
+        <v>0.536529004573822</v>
       </c>
       <c r="H158" t="n">
         <v>1183798</v>
@@ -5009,7 +5009,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G160" t="n">
-        <v>0.545372784137726</v>
+        <v>0.545372843742371</v>
       </c>
       <c r="H160" t="n">
         <v>711291</v>
@@ -5038,7 +5038,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G161" t="n">
-        <v>0.57072526216507</v>
+        <v>0.570725321769714</v>
       </c>
       <c r="H161" t="n">
         <v>2818445</v>
@@ -5154,7 +5154,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>0.609048902988434</v>
+        <v>0.609048783779144</v>
       </c>
       <c r="H165" t="n">
         <v>1315423</v>
@@ -5212,7 +5212,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G167" t="n">
-        <v>0.589297473430634</v>
+        <v>0.589297533035278</v>
       </c>
       <c r="H167" t="n">
         <v>895145</v>
@@ -5241,7 +5241,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G168" t="n">
-        <v>0.589297473430634</v>
+        <v>0.589297533035278</v>
       </c>
       <c r="H168" t="n">
         <v>435861</v>
@@ -5270,7 +5270,7 @@
         <v>0.981000006198883</v>
       </c>
       <c r="G169" t="n">
-        <v>0.578390002250671</v>
+        <v>0.578390121459961</v>
       </c>
       <c r="H169" t="n">
         <v>313669</v>
@@ -5328,7 +5328,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G171" t="n">
-        <v>0.571904480457306</v>
+        <v>0.571904540061951</v>
       </c>
       <c r="H171" t="n">
         <v>704350</v>
@@ -5357,7 +5357,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G172" t="n">
-        <v>0.58723384141922</v>
+        <v>0.587233901023865</v>
       </c>
       <c r="H172" t="n">
         <v>727241</v>
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0.589592278003693</v>
+        <v>0.589592218399048</v>
       </c>
       <c r="H174" t="n">
         <v>428087</v>
@@ -5502,7 +5502,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G177" t="n">
-        <v>0.599025666713715</v>
+        <v>0.599025726318359</v>
       </c>
       <c r="H177" t="n">
         <v>1165907</v>
@@ -5589,7 +5589,7 @@
         <v>1.00100004673004</v>
       </c>
       <c r="G180" t="n">
-        <v>0.590181887149811</v>
+        <v>0.590181827545166</v>
       </c>
       <c r="H180" t="n">
         <v>247003</v>
@@ -5618,7 +5618,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G181" t="n">
-        <v>0.584285914897919</v>
+        <v>0.584285974502563</v>
       </c>
       <c r="H181" t="n">
         <v>931680</v>
@@ -5734,7 +5734,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G185" t="n">
-        <v>0.560112714767456</v>
+        <v>0.560112655162811</v>
       </c>
       <c r="H185" t="n">
         <v>671107</v>
@@ -5792,7 +5792,7 @@
         <v>0.930499970912933</v>
       </c>
       <c r="G187" t="n">
-        <v>0.548615634441376</v>
+        <v>0.548615694046021</v>
       </c>
       <c r="H187" t="n">
         <v>1177556</v>
@@ -5937,7 +5937,7 @@
         <v>0.939499974250793</v>
       </c>
       <c r="G192" t="n">
-        <v>0.55392199754715</v>
+        <v>0.553921937942505</v>
       </c>
       <c r="H192" t="n">
         <v>141760</v>
@@ -5966,7 +5966,7 @@
         <v>0.9375</v>
       </c>
       <c r="G193" t="n">
-        <v>0.552742779254913</v>
+        <v>0.552742719650269</v>
       </c>
       <c r="H193" t="n">
         <v>616902</v>
@@ -5995,7 +5995,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G194" t="n">
-        <v>0.560112714767456</v>
+        <v>0.560112655162811</v>
       </c>
       <c r="H194" t="n">
         <v>245980</v>
@@ -6053,7 +6053,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G196" t="n">
-        <v>0.555690705776215</v>
+        <v>0.555690765380859</v>
       </c>
       <c r="H196" t="n">
         <v>1445760</v>
@@ -6082,7 +6082,7 @@
         <v>0.933000028133392</v>
       </c>
       <c r="G197" t="n">
-        <v>0.550089597702026</v>
+        <v>0.550089657306671</v>
       </c>
       <c r="H197" t="n">
         <v>415305</v>
@@ -6111,7 +6111,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G198" t="n">
-        <v>0.558933436870575</v>
+        <v>0.558933556079865</v>
       </c>
       <c r="H198" t="n">
         <v>341231</v>
@@ -6140,7 +6140,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G199" t="n">
-        <v>0.560702323913574</v>
+        <v>0.560702204704285</v>
       </c>
       <c r="H199" t="n">
         <v>519739</v>
@@ -6169,7 +6169,7 @@
         <v>0.961499989032745</v>
       </c>
       <c r="G200" t="n">
-        <v>0.566892921924591</v>
+        <v>0.566892981529236</v>
       </c>
       <c r="H200" t="n">
         <v>326936</v>
@@ -6198,7 +6198,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G201" t="n">
-        <v>0.568367004394531</v>
+        <v>0.568366944789886</v>
       </c>
       <c r="H201" t="n">
         <v>309895</v>
@@ -6227,7 +6227,7 @@
         <v>0.961499989032745</v>
       </c>
       <c r="G202" t="n">
-        <v>0.566892921924591</v>
+        <v>0.566892981529236</v>
       </c>
       <c r="H202" t="n">
         <v>298560</v>
@@ -6256,7 +6256,7 @@
         <v>0.968500018119812</v>
       </c>
       <c r="G203" t="n">
-        <v>0.571020185947418</v>
+        <v>0.571020126342773</v>
       </c>
       <c r="H203" t="n">
         <v>367081</v>
@@ -6314,7 +6314,7 @@
         <v>0.961499989032745</v>
       </c>
       <c r="G205" t="n">
-        <v>0.566892921924591</v>
+        <v>0.566892981529236</v>
       </c>
       <c r="H205" t="n">
         <v>156441</v>
@@ -6372,7 +6372,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G207" t="n">
-        <v>0.560112714767456</v>
+        <v>0.560112655162811</v>
       </c>
       <c r="H207" t="n">
         <v>309712</v>
@@ -6459,7 +6459,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G210" t="n">
-        <v>0.547141671180725</v>
+        <v>0.547141551971436</v>
       </c>
       <c r="H210" t="n">
         <v>276377</v>
@@ -6488,7 +6488,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G211" t="n">
-        <v>0.547141671180725</v>
+        <v>0.547141551971436</v>
       </c>
       <c r="H211" t="n">
         <v>399378</v>
@@ -6546,7 +6546,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G213" t="n">
-        <v>0.571904480457306</v>
+        <v>0.571904540061951</v>
       </c>
       <c r="H213" t="n">
         <v>940007</v>
@@ -6633,7 +6633,7 @@
         <v>0.952499985694885</v>
       </c>
       <c r="G216" t="n">
-        <v>0.561586618423462</v>
+        <v>0.561586678028107</v>
       </c>
       <c r="H216" t="n">
         <v>96041</v>
@@ -6662,7 +6662,7 @@
         <v>0.954500019550323</v>
       </c>
       <c r="G217" t="n">
-        <v>0.562765836715698</v>
+        <v>0.562765896320343</v>
       </c>
       <c r="H217" t="n">
         <v>145791</v>
@@ -6778,7 +6778,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G221" t="n">
-        <v>0.573673248291016</v>
+        <v>0.57367330789566</v>
       </c>
       <c r="H221" t="n">
         <v>489755</v>
@@ -6836,7 +6836,7 @@
         <v>0.940500020980835</v>
       </c>
       <c r="G223" t="n">
-        <v>0.554511547088623</v>
+        <v>0.554511487483978</v>
       </c>
       <c r="H223" t="n">
         <v>212135</v>
@@ -6865,7 +6865,7 @@
         <v>0.932500004768372</v>
       </c>
       <c r="G224" t="n">
-        <v>0.549794793128967</v>
+        <v>0.549794733524323</v>
       </c>
       <c r="H224" t="n">
         <v>344355</v>
@@ -6952,7 +6952,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G227" t="n">
-        <v>0.548320770263672</v>
+        <v>0.548320829868317</v>
       </c>
       <c r="H227" t="n">
         <v>412957</v>
@@ -6981,7 +6981,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G228" t="n">
-        <v>0.548320770263672</v>
+        <v>0.548320829868317</v>
       </c>
       <c r="H228" t="n">
         <v>265674</v>
@@ -7010,7 +7010,7 @@
         <v>0.891499996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>0.52562153339386</v>
+        <v>0.525621473789215</v>
       </c>
       <c r="H229" t="n">
         <v>255562</v>
@@ -7068,7 +7068,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G231" t="n">
-        <v>0.486413598060608</v>
+        <v>0.48641362786293</v>
       </c>
       <c r="H231" t="n">
         <v>963499</v>
@@ -7155,7 +7155,7 @@
         <v>0.732999980449677</v>
       </c>
       <c r="G234" t="n">
-        <v>0.432171136140823</v>
+        <v>0.432171106338501</v>
       </c>
       <c r="H234" t="n">
         <v>825128</v>
@@ -7184,7 +7184,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G235" t="n">
-        <v>0.458702832460403</v>
+        <v>0.458702802658081</v>
       </c>
       <c r="H235" t="n">
         <v>1460789</v>
@@ -7213,7 +7213,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G236" t="n">
-        <v>0.458702832460403</v>
+        <v>0.458702802658081</v>
       </c>
       <c r="H236" t="n">
         <v>509156</v>
@@ -7242,7 +7242,7 @@
         <v>0.772499978542328</v>
       </c>
       <c r="G237" t="n">
-        <v>0.455460041761398</v>
+        <v>0.455459982156754</v>
       </c>
       <c r="H237" t="n">
         <v>430077</v>
@@ -7300,7 +7300,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G239" t="n">
-        <v>0.457523584365845</v>
+        <v>0.457523673772812</v>
       </c>
       <c r="H239" t="n">
         <v>162290</v>
@@ -7387,7 +7387,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G242" t="n">
-        <v>0.473442584276199</v>
+        <v>0.473442554473877</v>
       </c>
       <c r="H242" t="n">
         <v>303714</v>
@@ -7416,7 +7416,7 @@
         <v>0.80349999666214</v>
       </c>
       <c r="G243" t="n">
-        <v>0.473737478256226</v>
+        <v>0.473737448453903</v>
       </c>
       <c r="H243" t="n">
         <v>316293</v>
@@ -7445,7 +7445,7 @@
         <v>0.816500008106232</v>
       </c>
       <c r="G244" t="n">
-        <v>0.481402099132538</v>
+        <v>0.481402158737183</v>
       </c>
       <c r="H244" t="n">
         <v>321337</v>
@@ -7474,7 +7474,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G245" t="n">
-        <v>0.509997367858887</v>
+        <v>0.509997308254242</v>
       </c>
       <c r="H245" t="n">
         <v>1242626</v>
@@ -7561,7 +7561,7 @@
         <v>0.822499990463257</v>
       </c>
       <c r="G248" t="n">
-        <v>0.48493966460228</v>
+        <v>0.48493954539299</v>
       </c>
       <c r="H248" t="n">
         <v>1346140</v>
@@ -7619,7 +7619,7 @@
         <v>0.861000001430511</v>
       </c>
       <c r="G250" t="n">
-        <v>0.507638871669769</v>
+        <v>0.507638931274414</v>
       </c>
       <c r="H250" t="n">
         <v>1246187</v>
@@ -7648,7 +7648,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G251" t="n">
-        <v>0.502922236919403</v>
+        <v>0.502922177314758</v>
       </c>
       <c r="H251" t="n">
         <v>419067</v>
@@ -7677,7 +7677,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G252" t="n">
-        <v>0.495257496833801</v>
+        <v>0.495257467031479</v>
       </c>
       <c r="H252" t="n">
         <v>600005</v>
@@ -7706,7 +7706,7 @@
         <v>0.849500000476837</v>
       </c>
       <c r="G253" t="n">
-        <v>0.50085860490799</v>
+        <v>0.500858664512634</v>
       </c>
       <c r="H253" t="n">
         <v>479528</v>
@@ -7764,7 +7764,7 @@
         <v>0.841000020503998</v>
       </c>
       <c r="G255" t="n">
-        <v>0.495847076177597</v>
+        <v>0.495847105979919</v>
       </c>
       <c r="H255" t="n">
         <v>311249</v>
@@ -7793,7 +7793,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G256" t="n">
-        <v>0.492309510707855</v>
+        <v>0.492309540510178</v>
       </c>
       <c r="H256" t="n">
         <v>223869</v>
@@ -7822,7 +7822,7 @@
         <v>0.834500014781952</v>
       </c>
       <c r="G257" t="n">
-        <v>0.492014765739441</v>
+        <v>0.492014735937119</v>
       </c>
       <c r="H257" t="n">
         <v>488184</v>
@@ -7851,7 +7851,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>0.494667857885361</v>
+        <v>0.494667917490005</v>
       </c>
       <c r="H258" t="n">
         <v>227885</v>
@@ -7880,7 +7880,7 @@
         <v>0.849500000476837</v>
       </c>
       <c r="G259" t="n">
-        <v>0.50085860490799</v>
+        <v>0.500858664512634</v>
       </c>
       <c r="H259" t="n">
         <v>607460</v>
@@ -7938,7 +7938,7 @@
         <v>0.899500012397766</v>
       </c>
       <c r="G261" t="n">
-        <v>0.530338287353516</v>
+        <v>0.530338227748871</v>
       </c>
       <c r="H261" t="n">
         <v>1050538</v>
@@ -8141,7 +8141,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G268" t="n">
-        <v>0.524737179279327</v>
+        <v>0.524737060070038</v>
       </c>
       <c r="H268" t="n">
         <v>286552</v>
@@ -8170,7 +8170,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G269" t="n">
-        <v>0.524737179279327</v>
+        <v>0.524737060070038</v>
       </c>
       <c r="H269" t="n">
         <v>158594</v>
@@ -8199,7 +8199,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G270" t="n">
-        <v>0.511766016483307</v>
+        <v>0.511766076087952</v>
       </c>
       <c r="H270" t="n">
         <v>512205</v>
@@ -8286,7 +8286,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G273" t="n">
-        <v>0.502332627773285</v>
+        <v>0.50233268737793</v>
       </c>
       <c r="H273" t="n">
         <v>184822</v>
@@ -8373,7 +8373,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G276" t="n">
-        <v>0.484644919633865</v>
+        <v>0.484644889831543</v>
       </c>
       <c r="H276" t="n">
         <v>464774</v>
@@ -8402,7 +8402,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G277" t="n">
-        <v>0.478748917579651</v>
+        <v>0.478748947381973</v>
       </c>
       <c r="H277" t="n">
         <v>274272</v>
@@ -8431,7 +8431,7 @@
         <v>0.814499974250793</v>
       </c>
       <c r="G278" t="n">
-        <v>0.480222851037979</v>
+        <v>0.480222910642624</v>
       </c>
       <c r="H278" t="n">
         <v>352834</v>
@@ -8460,7 +8460,7 @@
         <v>0.799000024795532</v>
       </c>
       <c r="G279" t="n">
-        <v>0.471084207296371</v>
+        <v>0.471084237098694</v>
       </c>
       <c r="H279" t="n">
         <v>418226</v>
@@ -8489,7 +8489,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G280" t="n">
-        <v>0.491130411624908</v>
+        <v>0.491130352020264</v>
       </c>
       <c r="H280" t="n">
         <v>199293</v>
@@ -8518,7 +8518,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G281" t="n">
-        <v>0.48317089676857</v>
+        <v>0.483170837163925</v>
       </c>
       <c r="H281" t="n">
         <v>201583</v>
@@ -8576,7 +8576,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G283" t="n">
-        <v>0.48228645324707</v>
+        <v>0.482286512851715</v>
       </c>
       <c r="H283" t="n">
         <v>127215</v>
@@ -8605,7 +8605,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G284" t="n">
-        <v>0.475506126880646</v>
+        <v>0.475506156682968</v>
       </c>
       <c r="H284" t="n">
         <v>168703</v>
@@ -8634,7 +8634,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G285" t="n">
-        <v>0.47815927863121</v>
+        <v>0.478159308433533</v>
       </c>
       <c r="H285" t="n">
         <v>268978</v>
@@ -8663,7 +8663,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G286" t="n">
-        <v>0.487003237009048</v>
+        <v>0.487003207206726</v>
       </c>
       <c r="H286" t="n">
         <v>209969</v>
@@ -8692,7 +8692,7 @@
         <v>0.834500014781952</v>
       </c>
       <c r="G287" t="n">
-        <v>0.492014765739441</v>
+        <v>0.492014735937119</v>
       </c>
       <c r="H287" t="n">
         <v>378929</v>
@@ -8721,7 +8721,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G288" t="n">
-        <v>0.47992816567421</v>
+        <v>0.479928135871887</v>
       </c>
       <c r="H288" t="n">
         <v>572858</v>
@@ -8750,7 +8750,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G289" t="n">
-        <v>0.480517745018005</v>
+        <v>0.480517685413361</v>
       </c>
       <c r="H289" t="n">
         <v>273557</v>
@@ -8779,7 +8779,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>0.481107324361801</v>
+        <v>0.481107264757156</v>
       </c>
       <c r="H290" t="n">
         <v>290367</v>
@@ -8808,7 +8808,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G291" t="n">
-        <v>0.472853004932404</v>
+        <v>0.472852975130081</v>
       </c>
       <c r="H291" t="n">
         <v>165946</v>
@@ -8866,7 +8866,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>0.485824078321457</v>
+        <v>0.485824018716812</v>
       </c>
       <c r="H293" t="n">
         <v>185726</v>
@@ -8895,7 +8895,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G294" t="n">
-        <v>0.477569699287415</v>
+        <v>0.477569729089737</v>
       </c>
       <c r="H294" t="n">
         <v>152333</v>
@@ -8953,7 +8953,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G296" t="n">
-        <v>0.477569699287415</v>
+        <v>0.477569729089737</v>
       </c>
       <c r="H296" t="n">
         <v>113240</v>
@@ -8982,7 +8982,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G297" t="n">
-        <v>0.468725860118866</v>
+        <v>0.468725830316544</v>
       </c>
       <c r="H297" t="n">
         <v>152394</v>
@@ -9011,7 +9011,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G298" t="n">
-        <v>0.470494657754898</v>
+        <v>0.470494598150253</v>
       </c>
       <c r="H298" t="n">
         <v>255443</v>
@@ -9069,7 +9069,7 @@
         <v>0.796500027179718</v>
       </c>
       <c r="G300" t="n">
-        <v>0.469610273838043</v>
+        <v>0.469610244035721</v>
       </c>
       <c r="H300" t="n">
         <v>124552</v>
@@ -9098,7 +9098,7 @@
         <v>0.805000007152557</v>
       </c>
       <c r="G301" t="n">
-        <v>0.474621772766113</v>
+        <v>0.474621802568436</v>
       </c>
       <c r="H301" t="n">
         <v>163393</v>
@@ -9127,7 +9127,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G302" t="n">
-        <v>0.473442584276199</v>
+        <v>0.473442554473877</v>
       </c>
       <c r="H302" t="n">
         <v>296991</v>
@@ -9156,7 +9156,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G303" t="n">
-        <v>0.464598685503006</v>
+        <v>0.464598715305328</v>
       </c>
       <c r="H303" t="n">
         <v>1275341</v>
@@ -9185,7 +9185,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>0.476095706224442</v>
+        <v>0.476095825433731</v>
       </c>
       <c r="H304" t="n">
         <v>417466</v>
@@ -9214,7 +9214,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G305" t="n">
-        <v>0.503511786460876</v>
+        <v>0.503511846065521</v>
       </c>
       <c r="H305" t="n">
         <v>2827982</v>
@@ -9272,7 +9272,7 @@
         <v>0.873000025749207</v>
       </c>
       <c r="G307" t="n">
-        <v>0.514714062213898</v>
+        <v>0.514714002609253</v>
       </c>
       <c r="H307" t="n">
         <v>799421</v>
@@ -9301,7 +9301,7 @@
         <v>0.883499979972839</v>
       </c>
       <c r="G308" t="n">
-        <v>0.520904779434204</v>
+        <v>0.520904719829559</v>
       </c>
       <c r="H308" t="n">
         <v>876768</v>
@@ -9388,7 +9388,7 @@
         <v>0.907500028610229</v>
       </c>
       <c r="G311" t="n">
-        <v>0.535055041313171</v>
+        <v>0.535054981708527</v>
       </c>
       <c r="H311" t="n">
         <v>1105195</v>
@@ -9417,7 +9417,7 @@
         <v>0.952499985694885</v>
       </c>
       <c r="G312" t="n">
-        <v>0.561586618423462</v>
+        <v>0.561586678028107</v>
       </c>
       <c r="H312" t="n">
         <v>6465978</v>
@@ -9446,7 +9446,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>0.58369642496109</v>
+        <v>0.583696365356445</v>
       </c>
       <c r="H313" t="n">
         <v>4301131</v>
@@ -9475,7 +9475,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G314" t="n">
-        <v>0.612586379051208</v>
+        <v>0.612586438655853</v>
       </c>
       <c r="H314" t="n">
         <v>6210448</v>
@@ -9562,7 +9562,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G317" t="n">
-        <v>0.70868992805481</v>
+        <v>0.708689987659454</v>
       </c>
       <c r="H317" t="n">
         <v>6696172</v>
@@ -9649,7 +9649,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G320" t="n">
-        <v>0.647961854934692</v>
+        <v>0.647961914539337</v>
       </c>
       <c r="H320" t="n">
         <v>2757976</v>
@@ -9736,7 +9736,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G323" t="n">
-        <v>0.695129215717316</v>
+        <v>0.695129334926605</v>
       </c>
       <c r="H323" t="n">
         <v>1238097</v>
@@ -9765,7 +9765,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G324" t="n">
-        <v>0.701614856719971</v>
+        <v>0.701614916324615</v>
       </c>
       <c r="H324" t="n">
         <v>885149</v>
@@ -9794,7 +9794,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G325" t="n">
-        <v>0.702204406261444</v>
+        <v>0.702204465866089</v>
       </c>
       <c r="H325" t="n">
         <v>905997</v>
@@ -9823,7 +9823,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G326" t="n">
-        <v>0.706921100616455</v>
+        <v>0.7069211602211</v>
       </c>
       <c r="H326" t="n">
         <v>465207</v>
@@ -9881,7 +9881,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G328" t="n">
-        <v>0.743475914001465</v>
+        <v>0.74347597360611</v>
       </c>
       <c r="H328" t="n">
         <v>1870875</v>
@@ -9939,7 +9939,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G330" t="n">
-        <v>0.714585840702057</v>
+        <v>0.714585781097412</v>
       </c>
       <c r="H330" t="n">
         <v>1034559</v>
@@ -9968,7 +9968,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>0.701614856719971</v>
+        <v>0.701614916324615</v>
       </c>
       <c r="H331" t="n">
         <v>1133838</v>
@@ -9997,7 +9997,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G332" t="n">
-        <v>0.669776797294617</v>
+        <v>0.669776856899261</v>
       </c>
       <c r="H332" t="n">
         <v>1321080</v>
@@ -10026,7 +10026,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G333" t="n">
-        <v>0.676262319087982</v>
+        <v>0.676262259483337</v>
       </c>
       <c r="H333" t="n">
         <v>1373239</v>
@@ -10055,7 +10055,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G334" t="n">
-        <v>0.688643753528595</v>
+        <v>0.68864369392395</v>
       </c>
       <c r="H334" t="n">
         <v>613828</v>
@@ -10113,7 +10113,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>0.702204406261444</v>
+        <v>0.702204465866089</v>
       </c>
       <c r="H336" t="n">
         <v>811287</v>
@@ -10171,7 +10171,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G338" t="n">
-        <v>0.706921100616455</v>
+        <v>0.7069211602211</v>
       </c>
       <c r="H338" t="n">
         <v>657663</v>
@@ -10287,7 +10287,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G342" t="n">
-        <v>0.821891665458679</v>
+        <v>0.821891725063324</v>
       </c>
       <c r="H342" t="n">
         <v>4412407</v>
@@ -10316,7 +10316,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G343" t="n">
-        <v>0.791232883930206</v>
+        <v>0.791232764720917</v>
       </c>
       <c r="H343" t="n">
         <v>4282398</v>
@@ -10374,7 +10374,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G345" t="n">
-        <v>0.831325054168701</v>
+        <v>0.831325173377991</v>
       </c>
       <c r="H345" t="n">
         <v>1368532</v>
@@ -10403,7 +10403,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G346" t="n">
-        <v>0.860804855823517</v>
+        <v>0.860804736614227</v>
       </c>
       <c r="H346" t="n">
         <v>4023106</v>
@@ -10432,7 +10432,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G347" t="n">
-        <v>0.859625637531281</v>
+        <v>0.859625518321991</v>
       </c>
       <c r="H347" t="n">
         <v>1701292</v>
@@ -10490,7 +10490,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G349" t="n">
-        <v>0.838400304317474</v>
+        <v>0.838400185108185</v>
       </c>
       <c r="H349" t="n">
         <v>1492868</v>
@@ -10519,7 +10519,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G350" t="n">
-        <v>0.819533288478851</v>
+        <v>0.819533348083496</v>
       </c>
       <c r="H350" t="n">
         <v>777496</v>
@@ -10606,7 +10606,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G353" t="n">
-        <v>0.833093762397766</v>
+        <v>0.833093881607056</v>
       </c>
       <c r="H353" t="n">
         <v>1007405</v>
@@ -10635,7 +10635,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G354" t="n">
-        <v>0.84665447473526</v>
+        <v>0.84665435552597</v>
       </c>
       <c r="H354" t="n">
         <v>625775</v>
@@ -10664,7 +10664,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G355" t="n">
-        <v>0.849602520465851</v>
+        <v>0.849602460861206</v>
       </c>
       <c r="H355" t="n">
         <v>475045</v>
@@ -10693,7 +10693,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>0.846064805984497</v>
+        <v>0.846064925193787</v>
       </c>
       <c r="H356" t="n">
         <v>455506</v>
@@ -10722,7 +10722,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G357" t="n">
-        <v>0.831325054168701</v>
+        <v>0.831325173377991</v>
       </c>
       <c r="H357" t="n">
         <v>601666</v>
@@ -10780,7 +10780,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G359" t="n">
-        <v>0.830145955085754</v>
+        <v>0.830145835876465</v>
       </c>
       <c r="H359" t="n">
         <v>555180</v>
@@ -10954,7 +10954,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>0.806562185287476</v>
+        <v>0.80656224489212</v>
       </c>
       <c r="H365" t="n">
         <v>592714</v>
@@ -11012,7 +11012,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G367" t="n">
-        <v>0.807151794433594</v>
+        <v>0.807151734828949</v>
       </c>
       <c r="H367" t="n">
         <v>697781</v>
@@ -11070,7 +11070,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G369" t="n">
-        <v>0.70338362455368</v>
+        <v>0.703383564949036</v>
       </c>
       <c r="H369" t="n">
         <v>4516781</v>
@@ -11099,7 +11099,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G370" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H370" t="n">
         <v>1366386</v>
@@ -11186,7 +11186,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G373" t="n">
-        <v>0.779441118240356</v>
+        <v>0.779440999031067</v>
       </c>
       <c r="H373" t="n">
         <v>1198542</v>
@@ -11215,7 +11215,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G374" t="n">
-        <v>0.734631955623627</v>
+        <v>0.734632015228271</v>
       </c>
       <c r="H374" t="n">
         <v>1054857</v>
@@ -11244,7 +11244,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G375" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H375" t="n">
         <v>340539</v>
@@ -11302,7 +11302,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G377" t="n">
-        <v>0.771776258945465</v>
+        <v>0.771776378154755</v>
       </c>
       <c r="H377" t="n">
         <v>878229</v>
@@ -11360,7 +11360,7 @@
         <v>1.25</v>
       </c>
       <c r="G379" t="n">
-        <v>0.736990332603455</v>
+        <v>0.73699027299881</v>
       </c>
       <c r="H379" t="n">
         <v>1001028</v>
@@ -11389,7 +11389,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G380" t="n">
-        <v>0.747013449668884</v>
+        <v>0.74701339006424</v>
       </c>
       <c r="H380" t="n">
         <v>493765</v>
@@ -11418,7 +11418,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G381" t="n">
-        <v>0.747602999210358</v>
+        <v>0.747603118419647</v>
       </c>
       <c r="H381" t="n">
         <v>222178</v>
@@ -11447,7 +11447,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G382" t="n">
-        <v>0.747013449668884</v>
+        <v>0.74701339006424</v>
       </c>
       <c r="H382" t="n">
         <v>340185</v>
@@ -11476,7 +11476,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G383" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H383" t="n">
         <v>366893</v>
@@ -11505,7 +11505,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G384" t="n">
-        <v>0.722250521183014</v>
+        <v>0.722250640392303</v>
       </c>
       <c r="H384" t="n">
         <v>615298</v>
@@ -11563,7 +11563,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G386" t="n">
-        <v>0.714585840702057</v>
+        <v>0.714585781097412</v>
       </c>
       <c r="H386" t="n">
         <v>467527</v>
@@ -11592,7 +11592,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G387" t="n">
-        <v>0.726967334747314</v>
+        <v>0.726967215538025</v>
       </c>
       <c r="H387" t="n">
         <v>956567</v>
@@ -11679,7 +11679,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G390" t="n">
-        <v>0.72991532087326</v>
+        <v>0.729915261268616</v>
       </c>
       <c r="H390" t="n">
         <v>274481</v>
@@ -11708,7 +11708,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G391" t="n">
-        <v>0.731684029102325</v>
+        <v>0.73168408870697</v>
       </c>
       <c r="H391" t="n">
         <v>153987</v>
@@ -11737,7 +11737,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G392" t="n">
-        <v>0.738169550895691</v>
+        <v>0.738169610500336</v>
       </c>
       <c r="H392" t="n">
         <v>616125</v>
@@ -11766,7 +11766,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G393" t="n">
-        <v>0.731684029102325</v>
+        <v>0.73168408870697</v>
       </c>
       <c r="H393" t="n">
         <v>303928</v>
@@ -11795,7 +11795,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G394" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H394" t="n">
         <v>259479</v>
@@ -11824,7 +11824,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G395" t="n">
-        <v>0.734631955623627</v>
+        <v>0.734632015228271</v>
       </c>
       <c r="H395" t="n">
         <v>378741</v>
@@ -11882,7 +11882,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G397" t="n">
-        <v>0.719302594661713</v>
+        <v>0.719302475452423</v>
       </c>
       <c r="H397" t="n">
         <v>746290</v>
@@ -11911,7 +11911,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G398" t="n">
-        <v>0.721071302890778</v>
+        <v>0.721071481704712</v>
       </c>
       <c r="H398" t="n">
         <v>579335</v>
@@ -11940,7 +11940,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G399" t="n">
-        <v>0.714585840702057</v>
+        <v>0.714585781097412</v>
       </c>
       <c r="H399" t="n">
         <v>246787</v>
@@ -11998,7 +11998,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>0.715764999389648</v>
+        <v>0.715765058994293</v>
       </c>
       <c r="H401" t="n">
         <v>1112778</v>
@@ -12027,7 +12027,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>0.713406682014465</v>
+        <v>0.71340674161911</v>
       </c>
       <c r="H402" t="n">
         <v>239424</v>
@@ -12085,7 +12085,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G404" t="n">
-        <v>0.708100199699402</v>
+        <v>0.708100318908691</v>
       </c>
       <c r="H404" t="n">
         <v>242394</v>
@@ -12114,7 +12114,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G405" t="n">
-        <v>0.715764999389648</v>
+        <v>0.715765058994293</v>
       </c>
       <c r="H405" t="n">
         <v>1610134</v>
@@ -12143,7 +12143,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G406" t="n">
-        <v>0.726967334747314</v>
+        <v>0.726967215538025</v>
       </c>
       <c r="H406" t="n">
         <v>264031</v>
@@ -12172,7 +12172,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G407" t="n">
-        <v>0.739938259124756</v>
+        <v>0.739938318729401</v>
       </c>
       <c r="H407" t="n">
         <v>1023851</v>
@@ -12230,7 +12230,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G409" t="n">
-        <v>0.784157693386078</v>
+        <v>0.784157752990723</v>
       </c>
       <c r="H409" t="n">
         <v>1623176</v>
@@ -12259,7 +12259,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G410" t="n">
-        <v>0.774134814739227</v>
+        <v>0.774134695529938</v>
       </c>
       <c r="H410" t="n">
         <v>919558</v>
@@ -12288,7 +12288,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G411" t="n">
-        <v>0.811279058456421</v>
+        <v>0.811278939247131</v>
       </c>
       <c r="H411" t="n">
         <v>1928389</v>
@@ -12317,7 +12317,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G412" t="n">
-        <v>0.801845550537109</v>
+        <v>0.801845490932465</v>
       </c>
       <c r="H412" t="n">
         <v>974358</v>
@@ -12375,7 +12375,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>0.781209826469421</v>
+        <v>0.781209886074066</v>
       </c>
       <c r="H414" t="n">
         <v>432906</v>
@@ -12404,7 +12404,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G415" t="n">
-        <v>0.772365689277649</v>
+        <v>0.772365808486938</v>
       </c>
       <c r="H415" t="n">
         <v>864901</v>
@@ -12433,7 +12433,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G416" t="n">
-        <v>0.801845550537109</v>
+        <v>0.801845490932465</v>
       </c>
       <c r="H416" t="n">
         <v>699323</v>
@@ -12491,7 +12491,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G418" t="n">
-        <v>0.795359969139099</v>
+        <v>0.795359909534454</v>
       </c>
       <c r="H418" t="n">
         <v>223440</v>
@@ -12520,7 +12520,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G419" t="n">
-        <v>0.783568143844604</v>
+        <v>0.78356808423996</v>
       </c>
       <c r="H419" t="n">
         <v>272088</v>
@@ -12607,7 +12607,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G422" t="n">
-        <v>0.766469895839691</v>
+        <v>0.766470015048981</v>
       </c>
       <c r="H422" t="n">
         <v>202799</v>
@@ -12810,7 +12810,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G429" t="n">
-        <v>0.730504810810089</v>
+        <v>0.730504930019379</v>
       </c>
       <c r="H429" t="n">
         <v>350159</v>
@@ -12839,7 +12839,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G430" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H430" t="n">
         <v>487413</v>
@@ -12955,7 +12955,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G434" t="n">
-        <v>0.745834171772003</v>
+        <v>0.745834112167358</v>
       </c>
       <c r="H434" t="n">
         <v>752937</v>
@@ -12984,7 +12984,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G435" t="n">
-        <v>0.74996143579483</v>
+        <v>0.749961376190186</v>
       </c>
       <c r="H435" t="n">
         <v>359177</v>
@@ -13071,7 +13071,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G438" t="n">
-        <v>0.751140654087067</v>
+        <v>0.751140594482422</v>
       </c>
       <c r="H438" t="n">
         <v>287016</v>
@@ -13100,7 +13100,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>0.771776258945465</v>
+        <v>0.771776378154755</v>
       </c>
       <c r="H439" t="n">
         <v>1159029</v>
@@ -13129,7 +13129,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G440" t="n">
-        <v>0.794770359992981</v>
+        <v>0.79477059841156</v>
       </c>
       <c r="H440" t="n">
         <v>1256860</v>
@@ -13158,7 +13158,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G441" t="n">
-        <v>0.797128736972809</v>
+        <v>0.797128796577454</v>
       </c>
       <c r="H441" t="n">
         <v>1254876</v>
@@ -13216,7 +13216,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G443" t="n">
-        <v>0.803024709224701</v>
+        <v>0.803024649620056</v>
       </c>
       <c r="H443" t="n">
         <v>1232924</v>
@@ -13245,7 +13245,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G444" t="n">
-        <v>0.797128736972809</v>
+        <v>0.797128796577454</v>
       </c>
       <c r="H444" t="n">
         <v>1167620</v>
@@ -13274,7 +13274,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G445" t="n">
-        <v>0.804203808307648</v>
+        <v>0.804203927516937</v>
       </c>
       <c r="H445" t="n">
         <v>466788</v>
@@ -13303,7 +13303,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G446" t="n">
-        <v>0.790643155574799</v>
+        <v>0.790643334388733</v>
       </c>
       <c r="H446" t="n">
         <v>334820</v>
@@ -13332,7 +13332,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G447" t="n">
-        <v>0.781799256801605</v>
+        <v>0.78179931640625</v>
       </c>
       <c r="H447" t="n">
         <v>399246</v>
@@ -13390,7 +13390,7 @@
         <v>1.32299995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>0.780030488967896</v>
+        <v>0.780030608177185</v>
       </c>
       <c r="H449" t="n">
         <v>315158</v>
@@ -13419,7 +13419,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G450" t="n">
-        <v>0.783568143844604</v>
+        <v>0.78356808423996</v>
       </c>
       <c r="H450" t="n">
         <v>218351</v>
@@ -13448,7 +13448,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G451" t="n">
-        <v>0.769417881965637</v>
+        <v>0.769417941570282</v>
       </c>
       <c r="H451" t="n">
         <v>701960</v>
@@ -13535,7 +13535,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>0.748782098293304</v>
+        <v>0.748782157897949</v>
       </c>
       <c r="H454" t="n">
         <v>785682</v>
@@ -13593,7 +13593,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>0.766469895839691</v>
+        <v>0.766470015048981</v>
       </c>
       <c r="H456" t="n">
         <v>968687</v>
@@ -13622,7 +13622,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G457" t="n">
-        <v>0.766469895839691</v>
+        <v>0.766470015048981</v>
       </c>
       <c r="H457" t="n">
         <v>280959</v>
@@ -13680,7 +13680,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G459" t="n">
-        <v>0.769417881965637</v>
+        <v>0.769417941570282</v>
       </c>
       <c r="H459" t="n">
         <v>346056</v>
@@ -13709,7 +13709,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G460" t="n">
-        <v>0.761753141880035</v>
+        <v>0.76175320148468</v>
       </c>
       <c r="H460" t="n">
         <v>175924</v>
@@ -13767,7 +13767,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G462" t="n">
-        <v>0.740527987480164</v>
+        <v>0.740527927875519</v>
       </c>
       <c r="H462" t="n">
         <v>444066</v>
@@ -13796,7 +13796,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G463" t="n">
-        <v>0.751140654087067</v>
+        <v>0.751140594482422</v>
       </c>
       <c r="H463" t="n">
         <v>212248</v>
@@ -13883,7 +13883,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G466" t="n">
-        <v>0.752319872379303</v>
+        <v>0.752319753170013</v>
       </c>
       <c r="H466" t="n">
         <v>368908</v>
@@ -13912,7 +13912,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G467" t="n">
-        <v>0.752909362316132</v>
+        <v>0.752909243106842</v>
       </c>
       <c r="H467" t="n">
         <v>173141</v>
@@ -13941,7 +13941,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G468" t="n">
-        <v>0.741707146167755</v>
+        <v>0.741707026958466</v>
       </c>
       <c r="H468" t="n">
         <v>173772</v>
@@ -13970,7 +13970,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G469" t="n">
-        <v>0.742296695709229</v>
+        <v>0.742296755313873</v>
       </c>
       <c r="H469" t="n">
         <v>161734</v>
@@ -14028,7 +14028,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G471" t="n">
-        <v>0.765290796756744</v>
+        <v>0.7652907371521</v>
       </c>
       <c r="H471" t="n">
         <v>182352</v>
@@ -14057,7 +14057,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G472" t="n">
-        <v>0.755267798900604</v>
+        <v>0.755267679691315</v>
       </c>
       <c r="H472" t="n">
         <v>215484</v>
@@ -14086,7 +14086,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G473" t="n">
-        <v>0.762342929840088</v>
+        <v>0.762342810630798</v>
       </c>
       <c r="H473" t="n">
         <v>226775</v>
@@ -14144,7 +14144,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G475" t="n">
-        <v>0.752319872379303</v>
+        <v>0.752319753170013</v>
       </c>
       <c r="H475" t="n">
         <v>257933</v>
@@ -14173,7 +14173,7 @@
         <v>1.25199997425079</v>
       </c>
       <c r="G476" t="n">
-        <v>0.738169550895691</v>
+        <v>0.738169610500336</v>
       </c>
       <c r="H476" t="n">
         <v>308646</v>
@@ -14202,7 +14202,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G477" t="n">
-        <v>0.741117477416992</v>
+        <v>0.741117417812347</v>
       </c>
       <c r="H477" t="n">
         <v>400686</v>
@@ -14260,7 +14260,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G479" t="n">
-        <v>0.721071302890778</v>
+        <v>0.721071481704712</v>
       </c>
       <c r="H479" t="n">
         <v>733414</v>
@@ -14318,7 +14318,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G481" t="n">
-        <v>0.702204406261444</v>
+        <v>0.702204465866089</v>
       </c>
       <c r="H481" t="n">
         <v>1124174</v>
@@ -14347,7 +14347,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G482" t="n">
-        <v>0.676262319087982</v>
+        <v>0.676262259483337</v>
       </c>
       <c r="H482" t="n">
         <v>529713</v>
@@ -14434,7 +14434,7 @@
         <v>1.16100001335144</v>
       </c>
       <c r="G485" t="n">
-        <v>0.684516549110413</v>
+        <v>0.684516668319702</v>
       </c>
       <c r="H485" t="n">
         <v>742902</v>
@@ -14463,7 +14463,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G486" t="n">
-        <v>0.706331551074982</v>
+        <v>0.706331491470337</v>
       </c>
       <c r="H486" t="n">
         <v>1047683</v>
@@ -14492,7 +14492,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G487" t="n">
-        <v>0.719302594661713</v>
+        <v>0.719302475452423</v>
       </c>
       <c r="H487" t="n">
         <v>422078</v>
@@ -14521,7 +14521,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G488" t="n">
-        <v>0.745834171772003</v>
+        <v>0.745834112167358</v>
       </c>
       <c r="H488" t="n">
         <v>1499085</v>
@@ -14579,7 +14579,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G490" t="n">
-        <v>0.718123376369476</v>
+        <v>0.718123435974121</v>
       </c>
       <c r="H490" t="n">
         <v>243326</v>
@@ -14608,7 +14608,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G491" t="n">
-        <v>0.721660912036896</v>
+        <v>0.721660971641541</v>
       </c>
       <c r="H491" t="n">
         <v>392931</v>
@@ -14637,7 +14637,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G492" t="n">
-        <v>0.729325592517853</v>
+        <v>0.729325711727142</v>
       </c>
       <c r="H492" t="n">
         <v>269974</v>
@@ -14666,7 +14666,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G493" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H493" t="n">
         <v>206839</v>
@@ -14695,7 +14695,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G494" t="n">
-        <v>0.728146493434906</v>
+        <v>0.728146374225616</v>
       </c>
       <c r="H494" t="n">
         <v>211828</v>
@@ -14724,7 +14724,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G495" t="n">
-        <v>0.731684029102325</v>
+        <v>0.73168408870697</v>
       </c>
       <c r="H495" t="n">
         <v>169964</v>
@@ -14782,7 +14782,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G497" t="n">
-        <v>0.707510769367218</v>
+        <v>0.707510709762573</v>
       </c>
       <c r="H497" t="n">
         <v>358771</v>
@@ -14811,7 +14811,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G498" t="n">
-        <v>0.704562902450562</v>
+        <v>0.704562842845917</v>
       </c>
       <c r="H498" t="n">
         <v>234858</v>
@@ -14840,7 +14840,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G499" t="n">
-        <v>0.712817013263702</v>
+        <v>0.712817132472992</v>
       </c>
       <c r="H499" t="n">
         <v>483802</v>
@@ -14869,7 +14869,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G500" t="n">
-        <v>0.741117477416992</v>
+        <v>0.741117417812347</v>
       </c>
       <c r="H500" t="n">
         <v>514781</v>
@@ -14898,7 +14898,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G501" t="n">
-        <v>0.729325592517853</v>
+        <v>0.729325711727142</v>
       </c>
       <c r="H501" t="n">
         <v>473595</v>
@@ -14956,7 +14956,7 @@
         <v>1.27799999713898</v>
       </c>
       <c r="G503" t="n">
-        <v>0.75349885225296</v>
+        <v>0.753498911857605</v>
       </c>
       <c r="H503" t="n">
         <v>2214429</v>
@@ -14985,7 +14985,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G504" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H504" t="n">
         <v>416132</v>
@@ -15043,7 +15043,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G506" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H506" t="n">
         <v>386311</v>
@@ -15072,7 +15072,7 @@
         <v>1.25</v>
       </c>
       <c r="G507" t="n">
-        <v>0.736990332603455</v>
+        <v>0.73699027299881</v>
       </c>
       <c r="H507" t="n">
         <v>702384</v>
@@ -15130,7 +15130,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G509" t="n">
-        <v>0.726377665996552</v>
+        <v>0.726377725601196</v>
       </c>
       <c r="H509" t="n">
         <v>502132</v>
@@ -15217,7 +15217,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G512" t="n">
-        <v>0.715764999389648</v>
+        <v>0.715765058994293</v>
       </c>
       <c r="H512" t="n">
         <v>83083</v>
@@ -15246,7 +15246,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G513" t="n">
-        <v>0.726377665996552</v>
+        <v>0.726377725601196</v>
       </c>
       <c r="H513" t="n">
         <v>118296</v>
@@ -15275,7 +15275,7 @@
         <v>1.25</v>
       </c>
       <c r="G514" t="n">
-        <v>0.736990332603455</v>
+        <v>0.73699027299881</v>
       </c>
       <c r="H514" t="n">
         <v>230557</v>
@@ -15333,7 +15333,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G516" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H516" t="n">
         <v>159880</v>
@@ -15362,7 +15362,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G517" t="n">
-        <v>0.744065523147583</v>
+        <v>0.744065344333649</v>
       </c>
       <c r="H517" t="n">
         <v>441160</v>
@@ -15391,7 +15391,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G518" t="n">
-        <v>0.758215665817261</v>
+        <v>0.758215725421906</v>
       </c>
       <c r="H518" t="n">
         <v>591276</v>
@@ -15420,7 +15420,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G519" t="n">
-        <v>0.752319872379303</v>
+        <v>0.752319753170013</v>
       </c>
       <c r="H519" t="n">
         <v>225314</v>
@@ -15507,7 +15507,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G522" t="n">
-        <v>0.719302594661713</v>
+        <v>0.719302475452423</v>
       </c>
       <c r="H522" t="n">
         <v>273565</v>
@@ -15565,7 +15565,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G524" t="n">
-        <v>0.718123376369476</v>
+        <v>0.718123435974121</v>
       </c>
       <c r="H524" t="n">
         <v>292362</v>
@@ -15652,7 +15652,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G527" t="n">
-        <v>0.721660912036896</v>
+        <v>0.721660971641541</v>
       </c>
       <c r="H527" t="n">
         <v>176061</v>
@@ -15710,7 +15710,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G529" t="n">
-        <v>0.715764999389648</v>
+        <v>0.715765058994293</v>
       </c>
       <c r="H529" t="n">
         <v>697859</v>
@@ -15739,7 +15739,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G530" t="n">
-        <v>0.715764999389648</v>
+        <v>0.715765058994293</v>
       </c>
       <c r="H530" t="n">
         <v>289550</v>
@@ -15768,7 +15768,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G531" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H531" t="n">
         <v>449866</v>
@@ -15797,7 +15797,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G532" t="n">
-        <v>0.711048245429993</v>
+        <v>0.711048364639282</v>
       </c>
       <c r="H532" t="n">
         <v>521881</v>
@@ -15826,7 +15826,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G533" t="n">
-        <v>0.706331551074982</v>
+        <v>0.706331491470337</v>
       </c>
       <c r="H533" t="n">
         <v>376945</v>
@@ -15855,7 +15855,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G534" t="n">
-        <v>0.706331551074982</v>
+        <v>0.706331491470337</v>
       </c>
       <c r="H534" t="n">
         <v>183079</v>
@@ -15942,7 +15942,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G537" t="n">
-        <v>0.645013988018036</v>
+        <v>0.645013928413391</v>
       </c>
       <c r="H537" t="n">
         <v>575067</v>
@@ -15971,7 +15971,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G538" t="n">
-        <v>0.687464535236359</v>
+        <v>0.687464594841003</v>
       </c>
       <c r="H538" t="n">
         <v>370385</v>
@@ -16000,7 +16000,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G539" t="n">
-        <v>0.654447495937347</v>
+        <v>0.654447436332703</v>
       </c>
       <c r="H539" t="n">
         <v>552687</v>
@@ -16029,7 +16029,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G540" t="n">
-        <v>0.646193146705627</v>
+        <v>0.646193206310272</v>
       </c>
       <c r="H540" t="n">
         <v>668856</v>
@@ -16058,7 +16058,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G541" t="n">
-        <v>0.635580480098724</v>
+        <v>0.63558042049408</v>
       </c>
       <c r="H541" t="n">
         <v>576413</v>
@@ -16116,7 +16116,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G543" t="n">
-        <v>0.636759638786316</v>
+        <v>0.636759698390961</v>
       </c>
       <c r="H543" t="n">
         <v>349246</v>
@@ -16145,7 +16145,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G544" t="n">
-        <v>0.623788595199585</v>
+        <v>0.62378853559494</v>
       </c>
       <c r="H544" t="n">
         <v>371070</v>
@@ -16232,7 +16232,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G547" t="n">
-        <v>0.635580480098724</v>
+        <v>0.63558042049408</v>
       </c>
       <c r="H547" t="n">
         <v>451462</v>
@@ -16493,7 +16493,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G556" t="n">
-        <v>0.636759638786316</v>
+        <v>0.636759698390961</v>
       </c>
       <c r="H556" t="n">
         <v>428343</v>
@@ -16580,7 +16580,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G559" t="n">
-        <v>0.663880944252014</v>
+        <v>0.663880884647369</v>
       </c>
       <c r="H559" t="n">
         <v>1182401</v>
@@ -16638,7 +16638,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G561" t="n">
-        <v>0.70043557882309</v>
+        <v>0.700435519218445</v>
       </c>
       <c r="H561" t="n">
         <v>432791</v>
@@ -16696,7 +16696,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>0.713406682014465</v>
+        <v>0.71340674161911</v>
       </c>
       <c r="H563" t="n">
         <v>1545017</v>
@@ -16725,7 +16725,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G564" t="n">
-        <v>0.718123376369476</v>
+        <v>0.718123435974121</v>
       </c>
       <c r="H564" t="n">
         <v>1134346</v>
@@ -16754,7 +16754,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G565" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H565" t="n">
         <v>1432750</v>
@@ -16783,7 +16783,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G566" t="n">
-        <v>0.72991532087326</v>
+        <v>0.729915261268616</v>
       </c>
       <c r="H566" t="n">
         <v>1933797</v>
@@ -16812,7 +16812,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G567" t="n">
-        <v>0.726377665996552</v>
+        <v>0.726377725601196</v>
       </c>
       <c r="H567" t="n">
         <v>396738</v>
@@ -16870,7 +16870,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G569" t="n">
-        <v>0.706331551074982</v>
+        <v>0.706331491470337</v>
       </c>
       <c r="H569" t="n">
         <v>623017</v>
@@ -16899,7 +16899,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G570" t="n">
-        <v>0.707510769367218</v>
+        <v>0.707510709762573</v>
       </c>
       <c r="H570" t="n">
         <v>502871</v>
@@ -16928,7 +16928,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G571" t="n">
-        <v>0.703973174095154</v>
+        <v>0.703973293304443</v>
       </c>
       <c r="H571" t="n">
         <v>221034</v>
@@ -17015,7 +17015,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G574" t="n">
-        <v>0.706331551074982</v>
+        <v>0.706331491470337</v>
       </c>
       <c r="H574" t="n">
         <v>447380</v>
@@ -17044,7 +17044,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G575" t="n">
-        <v>0.705152273178101</v>
+        <v>0.705152332782745</v>
       </c>
       <c r="H575" t="n">
         <v>206010</v>
@@ -17073,7 +17073,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G576" t="n">
-        <v>0.703973174095154</v>
+        <v>0.703973293304443</v>
       </c>
       <c r="H576" t="n">
         <v>174934</v>
@@ -17102,7 +17102,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G577" t="n">
-        <v>0.709869086742401</v>
+        <v>0.709869027137756</v>
       </c>
       <c r="H577" t="n">
         <v>303845</v>
@@ -17131,7 +17131,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G578" t="n">
-        <v>0.713406682014465</v>
+        <v>0.71340674161911</v>
       </c>
       <c r="H578" t="n">
         <v>124209</v>
@@ -17160,7 +17160,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G579" t="n">
-        <v>0.709869086742401</v>
+        <v>0.709869027137756</v>
       </c>
       <c r="H579" t="n">
         <v>122656</v>
@@ -17189,7 +17189,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G580" t="n">
-        <v>0.706331551074982</v>
+        <v>0.706331491470337</v>
       </c>
       <c r="H580" t="n">
         <v>295271</v>
@@ -17218,7 +17218,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G581" t="n">
-        <v>0.701614856719971</v>
+        <v>0.701614916324615</v>
       </c>
       <c r="H581" t="n">
         <v>148266</v>
@@ -17247,7 +17247,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G582" t="n">
-        <v>0.69689804315567</v>
+        <v>0.696898102760315</v>
       </c>
       <c r="H582" t="n">
         <v>131845</v>
@@ -17276,7 +17276,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G583" t="n">
-        <v>0.705152273178101</v>
+        <v>0.705152332782745</v>
       </c>
       <c r="H583" t="n">
         <v>229513</v>
@@ -17334,7 +17334,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G585" t="n">
-        <v>0.70043557882309</v>
+        <v>0.700435519218445</v>
       </c>
       <c r="H585" t="n">
         <v>205588</v>
@@ -17363,7 +17363,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G586" t="n">
-        <v>0.703973174095154</v>
+        <v>0.703973293304443</v>
       </c>
       <c r="H586" t="n">
         <v>117728</v>
@@ -17392,7 +17392,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G587" t="n">
-        <v>0.694539666175842</v>
+        <v>0.694539725780487</v>
       </c>
       <c r="H587" t="n">
         <v>316985</v>
@@ -17421,7 +17421,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G588" t="n">
-        <v>0.683926999568939</v>
+        <v>0.683927118778229</v>
       </c>
       <c r="H588" t="n">
         <v>372768</v>
@@ -17450,7 +17450,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G589" t="n">
-        <v>0.693360567092896</v>
+        <v>0.693360507488251</v>
       </c>
       <c r="H589" t="n">
         <v>373911</v>
@@ -17508,7 +17508,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G591" t="n">
-        <v>0.693360567092896</v>
+        <v>0.693360507488251</v>
       </c>
       <c r="H591" t="n">
         <v>83261</v>
@@ -17537,7 +17537,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G592" t="n">
-        <v>0.683926999568939</v>
+        <v>0.683927118778229</v>
       </c>
       <c r="H592" t="n">
         <v>344330</v>
@@ -17566,7 +17566,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G593" t="n">
-        <v>0.691002190113068</v>
+        <v>0.691002070903778</v>
       </c>
       <c r="H593" t="n">
         <v>629834</v>
@@ -17595,7 +17595,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G594" t="n">
-        <v>0.687464535236359</v>
+        <v>0.687464594841003</v>
       </c>
       <c r="H594" t="n">
         <v>802277</v>
@@ -17624,7 +17624,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G595" t="n">
-        <v>0.703973174095154</v>
+        <v>0.703973293304443</v>
       </c>
       <c r="H595" t="n">
         <v>543295</v>
@@ -17653,7 +17653,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>0.713406682014465</v>
+        <v>0.71340674161911</v>
       </c>
       <c r="H596" t="n">
         <v>349717</v>
@@ -17682,7 +17682,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G597" t="n">
-        <v>0.713406682014465</v>
+        <v>0.71340674161911</v>
       </c>
       <c r="H597" t="n">
         <v>257161</v>
@@ -17711,7 +17711,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G598" t="n">
-        <v>0.705152273178101</v>
+        <v>0.705152332782745</v>
       </c>
       <c r="H598" t="n">
         <v>185449</v>
@@ -17740,7 +17740,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G599" t="n">
-        <v>0.691002190113068</v>
+        <v>0.691002070903778</v>
       </c>
       <c r="H599" t="n">
         <v>455503</v>
@@ -17769,7 +17769,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G600" t="n">
-        <v>0.701614856719971</v>
+        <v>0.701614916324615</v>
       </c>
       <c r="H600" t="n">
         <v>1407778</v>
@@ -17798,7 +17798,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G601" t="n">
-        <v>0.714585840702057</v>
+        <v>0.714585781097412</v>
       </c>
       <c r="H601" t="n">
         <v>715401</v>
@@ -17827,7 +17827,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G602" t="n">
-        <v>0.719302594661713</v>
+        <v>0.719302475452423</v>
       </c>
       <c r="H602" t="n">
         <v>521070</v>
@@ -17856,7 +17856,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G603" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H603" t="n">
         <v>474553</v>
@@ -17885,7 +17885,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>0.707510769367218</v>
+        <v>0.707510709762573</v>
       </c>
       <c r="H604" t="n">
         <v>614290</v>
@@ -17914,7 +17914,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G605" t="n">
-        <v>0.694539666175842</v>
+        <v>0.694539725780487</v>
       </c>
       <c r="H605" t="n">
         <v>863359</v>
@@ -17943,7 +17943,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G606" t="n">
-        <v>0.709869086742401</v>
+        <v>0.709869027137756</v>
       </c>
       <c r="H606" t="n">
         <v>390100</v>
@@ -17972,7 +17972,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G607" t="n">
-        <v>0.701614856719971</v>
+        <v>0.701614916324615</v>
       </c>
       <c r="H607" t="n">
         <v>562350</v>
@@ -18001,7 +18001,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G608" t="n">
-        <v>0.689822912216187</v>
+        <v>0.689822852611542</v>
       </c>
       <c r="H608" t="n">
         <v>452140</v>
@@ -18030,7 +18030,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G609" t="n">
-        <v>0.689822912216187</v>
+        <v>0.689822852611542</v>
       </c>
       <c r="H609" t="n">
         <v>232632</v>
@@ -18088,7 +18088,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G611" t="n">
-        <v>0.705152273178101</v>
+        <v>0.705152332782745</v>
       </c>
       <c r="H611" t="n">
         <v>560105</v>
@@ -18117,7 +18117,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G612" t="n">
-        <v>0.692181289196014</v>
+        <v>0.692181408405304</v>
       </c>
       <c r="H612" t="n">
         <v>434791</v>
@@ -18146,7 +18146,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G613" t="n">
-        <v>0.663880944252014</v>
+        <v>0.663880884647369</v>
       </c>
       <c r="H613" t="n">
         <v>543747</v>
@@ -18175,7 +18175,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G614" t="n">
-        <v>0.645013988018036</v>
+        <v>0.645013928413391</v>
       </c>
       <c r="H614" t="n">
         <v>859997</v>
@@ -18233,7 +18233,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G616" t="n">
-        <v>0.672135174274445</v>
+        <v>0.6721351146698</v>
       </c>
       <c r="H616" t="n">
         <v>304960</v>
@@ -18291,7 +18291,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G618" t="n">
-        <v>0.687464535236359</v>
+        <v>0.687464594841003</v>
       </c>
       <c r="H618" t="n">
         <v>509468</v>
@@ -18349,7 +18349,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G620" t="n">
-        <v>0.650909841060638</v>
+        <v>0.650909900665283</v>
       </c>
       <c r="H620" t="n">
         <v>731600</v>
@@ -18407,7 +18407,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G622" t="n">
-        <v>0.649730741977692</v>
+        <v>0.649730682373047</v>
       </c>
       <c r="H622" t="n">
         <v>300084</v>
@@ -18465,7 +18465,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G624" t="n">
-        <v>0.663880944252014</v>
+        <v>0.663880884647369</v>
       </c>
       <c r="H624" t="n">
         <v>211705</v>
@@ -18494,7 +18494,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G625" t="n">
-        <v>0.669776797294617</v>
+        <v>0.669776856899261</v>
       </c>
       <c r="H625" t="n">
         <v>292336</v>
@@ -18523,7 +18523,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G626" t="n">
-        <v>0.674493610858917</v>
+        <v>0.674493730068207</v>
       </c>
       <c r="H626" t="n">
         <v>384978</v>
@@ -18552,7 +18552,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G627" t="n">
-        <v>0.665060043334961</v>
+        <v>0.665060102939606</v>
       </c>
       <c r="H627" t="n">
         <v>175480</v>
@@ -18610,7 +18610,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G629" t="n">
-        <v>0.649730741977692</v>
+        <v>0.649730682373047</v>
       </c>
       <c r="H629" t="n">
         <v>331090</v>
@@ -18639,7 +18639,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G630" t="n">
-        <v>0.662701785564423</v>
+        <v>0.662701666355133</v>
       </c>
       <c r="H630" t="n">
         <v>184528</v>
@@ -18668,7 +18668,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G631" t="n">
-        <v>0.643834710121155</v>
+        <v>0.6438347697258</v>
       </c>
       <c r="H631" t="n">
         <v>157703</v>
@@ -18784,7 +18784,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G635" t="n">
-        <v>0.633222103118896</v>
+        <v>0.633222043514252</v>
       </c>
       <c r="H635" t="n">
         <v>282271</v>
@@ -18813,7 +18813,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G636" t="n">
-        <v>0.654447495937347</v>
+        <v>0.654447436332703</v>
       </c>
       <c r="H636" t="n">
         <v>320823</v>
@@ -18842,7 +18842,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G637" t="n">
-        <v>0.636759638786316</v>
+        <v>0.636759698390961</v>
       </c>
       <c r="H637" t="n">
         <v>808077</v>
@@ -18871,7 +18871,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G638" t="n">
-        <v>0.650909841060638</v>
+        <v>0.650909900665283</v>
       </c>
       <c r="H638" t="n">
         <v>277973</v>
@@ -18900,7 +18900,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G639" t="n">
-        <v>0.649730741977692</v>
+        <v>0.649730682373047</v>
       </c>
       <c r="H639" t="n">
         <v>85501</v>
@@ -18929,7 +18929,7 @@
         <v>1.09399998188019</v>
       </c>
       <c r="G640" t="n">
-        <v>0.645013988018036</v>
+        <v>0.645013928413391</v>
       </c>
       <c r="H640" t="n">
         <v>83452</v>
@@ -18987,7 +18987,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G642" t="n">
-        <v>0.65208911895752</v>
+        <v>0.65208899974823</v>
       </c>
       <c r="H642" t="n">
         <v>60490</v>
@@ -19045,7 +19045,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G644" t="n">
-        <v>0.654447495937347</v>
+        <v>0.654447436332703</v>
       </c>
       <c r="H644" t="n">
         <v>107946</v>
@@ -19074,7 +19074,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G645" t="n">
-        <v>0.643834710121155</v>
+        <v>0.6438347697258</v>
       </c>
       <c r="H645" t="n">
         <v>107062</v>
@@ -19103,7 +19103,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G646" t="n">
-        <v>0.646193146705627</v>
+        <v>0.646193206310272</v>
       </c>
       <c r="H646" t="n">
         <v>55238</v>
@@ -19132,7 +19132,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G647" t="n">
-        <v>0.646193146705627</v>
+        <v>0.646193206310272</v>
       </c>
       <c r="H647" t="n">
         <v>62715</v>
@@ -19277,7 +19277,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G652" t="n">
-        <v>0.649730741977692</v>
+        <v>0.649730682373047</v>
       </c>
       <c r="H652" t="n">
         <v>73234</v>
@@ -19451,7 +19451,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G658" t="n">
-        <v>0.63204288482666</v>
+        <v>0.63204300403595</v>
       </c>
       <c r="H658" t="n">
         <v>512511</v>
@@ -19480,7 +19480,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G659" t="n">
-        <v>0.63204288482666</v>
+        <v>0.63204300403595</v>
       </c>
       <c r="H659" t="n">
         <v>181819</v>
@@ -19567,7 +19567,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G662" t="n">
-        <v>0.63204288482666</v>
+        <v>0.63204300403595</v>
       </c>
       <c r="H662" t="n">
         <v>1222339</v>
@@ -19625,7 +19625,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G664" t="n">
-        <v>0.633222103118896</v>
+        <v>0.633222043514252</v>
       </c>
       <c r="H664" t="n">
         <v>485601</v>
@@ -19654,7 +19654,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G665" t="n">
-        <v>0.635580480098724</v>
+        <v>0.63558042049408</v>
       </c>
       <c r="H665" t="n">
         <v>144872</v>
@@ -19683,7 +19683,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G666" t="n">
-        <v>0.629684507846832</v>
+        <v>0.629684567451477</v>
       </c>
       <c r="H666" t="n">
         <v>95269</v>
@@ -19741,7 +19741,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G668" t="n">
-        <v>0.611996710300446</v>
+        <v>0.611996829509735</v>
       </c>
       <c r="H668" t="n">
         <v>103020</v>
@@ -19770,7 +19770,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>0.613176047801971</v>
+        <v>0.613175988197327</v>
       </c>
       <c r="H669" t="n">
         <v>246959</v>
@@ -19915,7 +19915,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G674" t="n">
-        <v>0.602563261985779</v>
+        <v>0.602563321590424</v>
       </c>
       <c r="H674" t="n">
         <v>71302</v>
@@ -19944,7 +19944,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G675" t="n">
-        <v>0.596667408943176</v>
+        <v>0.596667349338531</v>
       </c>
       <c r="H675" t="n">
         <v>104843</v>
@@ -20031,7 +20031,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G678" t="n">
-        <v>0.594309031963348</v>
+        <v>0.594308972358704</v>
       </c>
       <c r="H678" t="n">
         <v>53077</v>
@@ -20060,7 +20060,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G679" t="n">
-        <v>0.593129754066467</v>
+        <v>0.593129932880402</v>
       </c>
       <c r="H679" t="n">
         <v>257719</v>
@@ -20089,7 +20089,7 @@
         <v>1</v>
       </c>
       <c r="G680" t="n">
-        <v>0.589592278003693</v>
+        <v>0.589592218399048</v>
       </c>
       <c r="H680" t="n">
         <v>386846</v>
@@ -20118,7 +20118,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G681" t="n">
-        <v>0.573673248291016</v>
+        <v>0.57367330789566</v>
       </c>
       <c r="H681" t="n">
         <v>674638</v>
@@ -20147,7 +20147,7 @@
         <v>0.936999976634979</v>
       </c>
       <c r="G682" t="n">
-        <v>0.552447915077209</v>
+        <v>0.552447974681854</v>
       </c>
       <c r="H682" t="n">
         <v>738064</v>
@@ -20263,7 +20263,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G686" t="n">
-        <v>0.548320770263672</v>
+        <v>0.548320829868317</v>
       </c>
       <c r="H686" t="n">
         <v>196827</v>
@@ -20292,7 +20292,7 @@
         <v>0.940999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>0.554806351661682</v>
+        <v>0.554806411266327</v>
       </c>
       <c r="H687" t="n">
         <v>247841</v>
@@ -20379,7 +20379,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G690" t="n">
-        <v>0.560702323913574</v>
+        <v>0.560702204704285</v>
       </c>
       <c r="H690" t="n">
         <v>223352</v>
@@ -20437,7 +20437,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G692" t="n">
-        <v>0.557754337787628</v>
+        <v>0.557754278182983</v>
       </c>
       <c r="H692" t="n">
         <v>162626</v>
@@ -20524,7 +20524,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G695" t="n">
-        <v>0.557754337787628</v>
+        <v>0.557754278182983</v>
       </c>
       <c r="H695" t="n">
         <v>356509</v>
@@ -20553,7 +20553,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G696" t="n">
-        <v>0.533581018447876</v>
+        <v>0.533580958843231</v>
       </c>
       <c r="H696" t="n">
         <v>2373268</v>
@@ -20582,7 +20582,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>0.577800452709198</v>
+        <v>0.577800393104553</v>
       </c>
       <c r="H697" t="n">
         <v>1815767</v>
@@ -20669,7 +20669,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G700" t="n">
-        <v>0.602563261985779</v>
+        <v>0.602563321590424</v>
       </c>
       <c r="H700" t="n">
         <v>338271</v>
@@ -20785,7 +20785,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G704" t="n">
-        <v>0.57072526216507</v>
+        <v>0.570725321769714</v>
       </c>
       <c r="H704" t="n">
         <v>257144</v>
@@ -20872,7 +20872,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G707" t="n">
-        <v>0.549499928951263</v>
+        <v>0.549499988555908</v>
       </c>
       <c r="H707" t="n">
         <v>500245</v>
@@ -20901,7 +20901,7 @@
         <v>0.921000003814697</v>
       </c>
       <c r="G708" t="n">
-        <v>0.543014526367188</v>
+        <v>0.543014466762543</v>
       </c>
       <c r="H708" t="n">
         <v>448877</v>
@@ -20959,7 +20959,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G710" t="n">
-        <v>0.525916278362274</v>
+        <v>0.525916337966919</v>
       </c>
       <c r="H710" t="n">
         <v>281083</v>
@@ -21017,7 +21017,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>0.521789193153381</v>
+        <v>0.521789133548737</v>
       </c>
       <c r="H712" t="n">
         <v>458152</v>
@@ -21046,7 +21046,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G713" t="n">
-        <v>0.545372784137726</v>
+        <v>0.545372843742371</v>
       </c>
       <c r="H713" t="n">
         <v>287417</v>
@@ -21104,7 +21104,7 @@
         <v>0.883000016212463</v>
       </c>
       <c r="G715" t="n">
-        <v>0.52061003446579</v>
+        <v>0.520609974861145</v>
       </c>
       <c r="H715" t="n">
         <v>85044</v>
@@ -21162,7 +21162,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G717" t="n">
-        <v>0.502922236919403</v>
+        <v>0.502922177314758</v>
       </c>
       <c r="H717" t="n">
         <v>188461</v>
@@ -21191,7 +21191,7 @@
         <v>0.847000002861023</v>
       </c>
       <c r="G718" t="n">
-        <v>0.499384671449661</v>
+        <v>0.499384731054306</v>
       </c>
       <c r="H718" t="n">
         <v>251563</v>
@@ -21220,7 +21220,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G719" t="n">
-        <v>0.491719931364059</v>
+        <v>0.491719961166382</v>
       </c>
       <c r="H719" t="n">
         <v>146562</v>
@@ -21249,7 +21249,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G720" t="n">
-        <v>0.495257496833801</v>
+        <v>0.495257467031479</v>
       </c>
       <c r="H720" t="n">
         <v>145905</v>
@@ -21278,7 +21278,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G721" t="n">
-        <v>0.492309510707855</v>
+        <v>0.492309540510178</v>
       </c>
       <c r="H721" t="n">
         <v>145937</v>
@@ -21336,7 +21336,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G723" t="n">
-        <v>0.52709549665451</v>
+        <v>0.527095556259155</v>
       </c>
       <c r="H723" t="n">
         <v>375298</v>
@@ -21423,7 +21423,7 @@
         <v>0.921000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>0.543014526367188</v>
+        <v>0.543014466762543</v>
       </c>
       <c r="H726" t="n">
         <v>217078</v>
@@ -21510,7 +21510,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G729" t="n">
-        <v>0.58723384141922</v>
+        <v>0.587233901023865</v>
       </c>
       <c r="H729" t="n">
         <v>1197109</v>
@@ -21539,7 +21539,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G730" t="n">
-        <v>0.586054742336273</v>
+        <v>0.586054801940918</v>
       </c>
       <c r="H730" t="n">
         <v>236252</v>
@@ -21597,7 +21597,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G732" t="n">
-        <v>0.571904480457306</v>
+        <v>0.571904540061951</v>
       </c>
       <c r="H732" t="n">
         <v>547062</v>
@@ -21655,7 +21655,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G734" t="n">
-        <v>0.560702323913574</v>
+        <v>0.560702204704285</v>
       </c>
       <c r="H734" t="n">
         <v>136466</v>
@@ -21713,7 +21713,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G736" t="n">
-        <v>0.531812191009521</v>
+        <v>0.531812310218811</v>
       </c>
       <c r="H736" t="n">
         <v>166471</v>
@@ -21742,7 +21742,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G737" t="n">
-        <v>0.528274714946747</v>
+        <v>0.528274655342102</v>
       </c>
       <c r="H737" t="n">
         <v>1893841</v>
@@ -21800,7 +21800,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G739" t="n">
-        <v>0.547141671180725</v>
+        <v>0.547141551971436</v>
       </c>
       <c r="H739" t="n">
         <v>652441</v>
@@ -21858,7 +21858,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G741" t="n">
-        <v>0.593129754066467</v>
+        <v>0.593129932880402</v>
       </c>
       <c r="H741" t="n">
         <v>1149252</v>
@@ -21887,7 +21887,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G742" t="n">
-        <v>0.65208911895752</v>
+        <v>0.65208899974823</v>
       </c>
       <c r="H742" t="n">
         <v>2166732</v>
@@ -21916,7 +21916,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G743" t="n">
-        <v>0.663880944252014</v>
+        <v>0.663880884647369</v>
       </c>
       <c r="H743" t="n">
         <v>1280175</v>
@@ -22032,7 +22032,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G747" t="n">
-        <v>0.712227404117584</v>
+        <v>0.712227463722229</v>
       </c>
       <c r="H747" t="n">
         <v>2171427</v>
@@ -22090,7 +22090,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G749" t="n">
-        <v>0.72991532087326</v>
+        <v>0.729915261268616</v>
       </c>
       <c r="H749" t="n">
         <v>1442717</v>
@@ -22148,7 +22148,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G751" t="n">
-        <v>0.703973174095154</v>
+        <v>0.703973293304443</v>
       </c>
       <c r="H751" t="n">
         <v>435456</v>
@@ -22177,7 +22177,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G752" t="n">
-        <v>0.674493610858917</v>
+        <v>0.674493730068207</v>
       </c>
       <c r="H752" t="n">
         <v>548296</v>
@@ -22206,7 +22206,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G753" t="n">
-        <v>0.683926999568939</v>
+        <v>0.683927118778229</v>
       </c>
       <c r="H753" t="n">
         <v>382682</v>
@@ -22235,7 +22235,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G754" t="n">
-        <v>0.707510769367218</v>
+        <v>0.707510709762573</v>
       </c>
       <c r="H754" t="n">
         <v>711393</v>
@@ -22264,7 +22264,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G755" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H755" t="n">
         <v>615271</v>
@@ -22380,7 +22380,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G759" t="n">
-        <v>0.683926999568939</v>
+        <v>0.683927118778229</v>
       </c>
       <c r="H759" t="n">
         <v>250559</v>
@@ -22409,7 +22409,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G760" t="n">
-        <v>0.688643753528595</v>
+        <v>0.68864369392395</v>
       </c>
       <c r="H760" t="n">
         <v>1419077</v>
@@ -22438,7 +22438,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G761" t="n">
-        <v>0.683926999568939</v>
+        <v>0.683927118778229</v>
       </c>
       <c r="H761" t="n">
         <v>389019</v>
@@ -22467,7 +22467,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>0.672135174274445</v>
+        <v>0.6721351146698</v>
       </c>
       <c r="H762" t="n">
         <v>173540</v>
@@ -22554,7 +22554,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G765" t="n">
-        <v>0.727556884288788</v>
+        <v>0.727556824684143</v>
       </c>
       <c r="H765" t="n">
         <v>831312</v>
@@ -22583,7 +22583,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G766" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H766" t="n">
         <v>503999</v>
@@ -22612,7 +22612,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G767" t="n">
-        <v>0.727556884288788</v>
+        <v>0.727556824684143</v>
       </c>
       <c r="H767" t="n">
         <v>427043</v>
@@ -22641,7 +22641,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G768" t="n">
-        <v>0.709869086742401</v>
+        <v>0.709869027137756</v>
       </c>
       <c r="H768" t="n">
         <v>807986</v>
@@ -22670,7 +22670,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G769" t="n">
-        <v>0.714585840702057</v>
+        <v>0.714585781097412</v>
       </c>
       <c r="H769" t="n">
         <v>579451</v>
@@ -22699,7 +22699,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G770" t="n">
-        <v>0.731094419956207</v>
+        <v>0.731094360351562</v>
       </c>
       <c r="H770" t="n">
         <v>433428</v>
@@ -22786,7 +22786,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G773" t="n">
-        <v>0.719302594661713</v>
+        <v>0.719302475452423</v>
       </c>
       <c r="H773" t="n">
         <v>665055</v>
@@ -22844,7 +22844,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G775" t="n">
-        <v>0.767649173736572</v>
+        <v>0.767649292945862</v>
       </c>
       <c r="H775" t="n">
         <v>777396</v>
@@ -22873,7 +22873,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G776" t="n">
-        <v>0.779441118240356</v>
+        <v>0.779440999031067</v>
       </c>
       <c r="H776" t="n">
         <v>1484898</v>
@@ -22960,7 +22960,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G779" t="n">
-        <v>0.810099720954895</v>
+        <v>0.81009978055954</v>
       </c>
       <c r="H779" t="n">
         <v>443916</v>
@@ -23018,7 +23018,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G781" t="n">
-        <v>0.81835412979126</v>
+        <v>0.818354070186615</v>
       </c>
       <c r="H781" t="n">
         <v>1100237</v>
@@ -23047,7 +23047,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G782" t="n">
-        <v>0.830145955085754</v>
+        <v>0.830145835876465</v>
       </c>
       <c r="H782" t="n">
         <v>1143982</v>
@@ -23105,7 +23105,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G784" t="n">
-        <v>0.859625637531281</v>
+        <v>0.859625518321991</v>
       </c>
       <c r="H784" t="n">
         <v>1279157</v>
@@ -23134,7 +23134,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G785" t="n">
-        <v>0.857267081737518</v>
+        <v>0.857267141342163</v>
       </c>
       <c r="H785" t="n">
         <v>1015434</v>
@@ -23163,7 +23163,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G786" t="n">
-        <v>0.857267081737518</v>
+        <v>0.857267141342163</v>
       </c>
       <c r="H786" t="n">
         <v>1147326</v>
@@ -23250,7 +23250,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G789" t="n">
-        <v>0.853729605674744</v>
+        <v>0.853729665279388</v>
       </c>
       <c r="H789" t="n">
         <v>2016906</v>
@@ -23279,7 +23279,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G790" t="n">
-        <v>0.805383026599884</v>
+        <v>0.805383145809174</v>
       </c>
       <c r="H790" t="n">
         <v>939339</v>
@@ -23308,7 +23308,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G791" t="n">
-        <v>0.780620098114014</v>
+        <v>0.780620157718658</v>
       </c>
       <c r="H791" t="n">
         <v>847088</v>
@@ -23395,7 +23395,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G794" t="n">
-        <v>0.794770359992981</v>
+        <v>0.79477059841156</v>
       </c>
       <c r="H794" t="n">
         <v>614107</v>
@@ -23424,7 +23424,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G795" t="n">
-        <v>0.819533288478851</v>
+        <v>0.819533348083496</v>
       </c>
       <c r="H795" t="n">
         <v>980608</v>
@@ -23453,7 +23453,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G796" t="n">
-        <v>0.833683490753174</v>
+        <v>0.833683609962463</v>
       </c>
       <c r="H796" t="n">
         <v>1514401</v>
@@ -23482,7 +23482,7 @@
         <v>1.38199996948242</v>
       </c>
       <c r="G797" t="n">
-        <v>0.814816534519196</v>
+        <v>0.81481659412384</v>
       </c>
       <c r="H797" t="n">
         <v>653553</v>
@@ -23598,7 +23598,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G801" t="n">
-        <v>0.810099720954895</v>
+        <v>0.81009978055954</v>
       </c>
       <c r="H801" t="n">
         <v>437432</v>
@@ -23656,7 +23656,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G803" t="n">
-        <v>0.819533288478851</v>
+        <v>0.819533348083496</v>
       </c>
       <c r="H803" t="n">
         <v>481992</v>
@@ -23685,7 +23685,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G804" t="n">
-        <v>0.801845550537109</v>
+        <v>0.801845490932465</v>
       </c>
       <c r="H804" t="n">
         <v>448693</v>
@@ -23714,7 +23714,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G805" t="n">
-        <v>0.804203808307648</v>
+        <v>0.804203927516937</v>
       </c>
       <c r="H805" t="n">
         <v>554225</v>
@@ -23743,7 +23743,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G806" t="n">
-        <v>0.808920621871948</v>
+        <v>0.808920502662659</v>
       </c>
       <c r="H806" t="n">
         <v>184145</v>
@@ -23772,7 +23772,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G807" t="n">
-        <v>0.821891665458679</v>
+        <v>0.821891725063324</v>
       </c>
       <c r="H807" t="n">
         <v>855372</v>
@@ -23801,7 +23801,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>0.872596800327301</v>
+        <v>0.872596621513367</v>
       </c>
       <c r="H808" t="n">
         <v>2766687</v>
@@ -23830,7 +23830,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G809" t="n">
-        <v>0.869058966636658</v>
+        <v>0.869059026241302</v>
       </c>
       <c r="H809" t="n">
         <v>642294</v>
@@ -23859,7 +23859,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G810" t="n">
-        <v>0.840758681297302</v>
+        <v>0.840758621692657</v>
       </c>
       <c r="H810" t="n">
         <v>828451</v>
@@ -23917,7 +23917,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G812" t="n">
-        <v>0.864342272281647</v>
+        <v>0.864342212677002</v>
       </c>
       <c r="H812" t="n">
         <v>1031546</v>
@@ -23946,7 +23946,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G813" t="n">
-        <v>0.861983954906464</v>
+        <v>0.861984014511108</v>
       </c>
       <c r="H813" t="n">
         <v>625826</v>
@@ -24004,7 +24004,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G815" t="n">
-        <v>0.843116879463196</v>
+        <v>0.843116998672485</v>
       </c>
       <c r="H815" t="n">
         <v>1881700</v>
@@ -24033,7 +24033,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G816" t="n">
-        <v>0.859625637531281</v>
+        <v>0.859625518321991</v>
       </c>
       <c r="H816" t="n">
         <v>734006</v>
@@ -24120,7 +24120,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G819" t="n">
-        <v>0.791232883930206</v>
+        <v>0.791232764720917</v>
       </c>
       <c r="H819" t="n">
         <v>1592750</v>
@@ -24178,7 +24178,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G821" t="n">
-        <v>0.774724304676056</v>
+        <v>0.774724185466766</v>
       </c>
       <c r="H821" t="n">
         <v>1017705</v>
@@ -24236,7 +24236,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G823" t="n">
-        <v>0.752319872379303</v>
+        <v>0.752319753170013</v>
       </c>
       <c r="H823" t="n">
         <v>710454</v>
@@ -24294,7 +24294,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G825" t="n">
-        <v>0.747602999210358</v>
+        <v>0.747603118419647</v>
       </c>
       <c r="H825" t="n">
         <v>949094</v>
@@ -24323,7 +24323,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G826" t="n">
-        <v>0.751140654087067</v>
+        <v>0.751140594482422</v>
       </c>
       <c r="H826" t="n">
         <v>921153</v>
@@ -24352,7 +24352,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>0.748782098293304</v>
+        <v>0.748782157897949</v>
       </c>
       <c r="H827" t="n">
         <v>535765</v>
@@ -24381,7 +24381,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G828" t="n">
-        <v>0.74996143579483</v>
+        <v>0.749961376190186</v>
       </c>
       <c r="H828" t="n">
         <v>549637</v>
@@ -24410,7 +24410,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G829" t="n">
-        <v>0.758215665817261</v>
+        <v>0.758215725421906</v>
       </c>
       <c r="H829" t="n">
         <v>541651</v>
@@ -24439,7 +24439,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G830" t="n">
-        <v>0.764111578464508</v>
+        <v>0.764111638069153</v>
       </c>
       <c r="H830" t="n">
         <v>515456</v>
@@ -24497,7 +24497,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G832" t="n">
-        <v>0.74996143579483</v>
+        <v>0.749961376190186</v>
       </c>
       <c r="H832" t="n">
         <v>323158</v>
@@ -24526,7 +24526,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G833" t="n">
-        <v>0.746423840522766</v>
+        <v>0.746423780918121</v>
       </c>
       <c r="H833" t="n">
         <v>425048</v>
@@ -24555,7 +24555,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G834" t="n">
-        <v>0.744065523147583</v>
+        <v>0.744065344333649</v>
       </c>
       <c r="H834" t="n">
         <v>279381</v>
@@ -24584,7 +24584,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G835" t="n">
-        <v>0.741707146167755</v>
+        <v>0.741707026958466</v>
       </c>
       <c r="H835" t="n">
         <v>288500</v>
@@ -24613,7 +24613,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G836" t="n">
-        <v>0.741707146167755</v>
+        <v>0.741707026958466</v>
       </c>
       <c r="H836" t="n">
         <v>137970</v>
@@ -24671,7 +24671,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G838" t="n">
-        <v>0.741707146167755</v>
+        <v>0.741707026958466</v>
       </c>
       <c r="H838" t="n">
         <v>231885</v>
@@ -24700,7 +24700,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G839" t="n">
-        <v>0.741707146167755</v>
+        <v>0.741707026958466</v>
       </c>
       <c r="H839" t="n">
         <v>158277</v>
@@ -24845,7 +24845,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G844" t="n">
-        <v>0.766469895839691</v>
+        <v>0.766470015048981</v>
       </c>
       <c r="H844" t="n">
         <v>189598</v>
@@ -24874,7 +24874,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G845" t="n">
-        <v>0.758215665817261</v>
+        <v>0.758215725421906</v>
       </c>
       <c r="H845" t="n">
         <v>194438</v>
@@ -24932,7 +24932,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G847" t="n">
-        <v>0.73345285654068</v>
+        <v>0.733452796936035</v>
       </c>
       <c r="H847" t="n">
         <v>836727</v>
@@ -24961,7 +24961,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G848" t="n">
-        <v>0.748782098293304</v>
+        <v>0.748782157897949</v>
       </c>
       <c r="H848" t="n">
         <v>366702</v>
@@ -25048,7 +25048,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G851" t="n">
-        <v>0.706331551074982</v>
+        <v>0.706331491470337</v>
       </c>
       <c r="H851" t="n">
         <v>601386</v>
@@ -25077,7 +25077,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G852" t="n">
-        <v>0.663880944252014</v>
+        <v>0.663880884647369</v>
       </c>
       <c r="H852" t="n">
         <v>2183330</v>
@@ -25164,7 +25164,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G855" t="n">
-        <v>0.595488250255585</v>
+        <v>0.59548819065094</v>
       </c>
       <c r="H855" t="n">
         <v>3256171</v>
@@ -25193,7 +25193,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G856" t="n">
-        <v>0.586054742336273</v>
+        <v>0.586054801940918</v>
       </c>
       <c r="H856" t="n">
         <v>1251535</v>
@@ -25222,7 +25222,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G857" t="n">
-        <v>0.591950654983521</v>
+        <v>0.591950595378876</v>
       </c>
       <c r="H857" t="n">
         <v>470029</v>
@@ -25251,7 +25251,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>0.595488250255585</v>
+        <v>0.59548819065094</v>
       </c>
       <c r="H858" t="n">
         <v>951724</v>
@@ -25338,7 +25338,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G861" t="n">
-        <v>0.581697940826416</v>
+        <v>0.581697881221771</v>
       </c>
       <c r="H861" t="n">
         <v>481572</v>
@@ -25425,7 +25425,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G864" t="n">
-        <v>0.595488250255585</v>
+        <v>0.59548819065094</v>
       </c>
       <c r="H864" t="n">
         <v>923897</v>
@@ -25512,7 +25512,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G867" t="n">
-        <v>0.554744303226471</v>
+        <v>0.554744243621826</v>
       </c>
       <c r="H867" t="n">
         <v>484527</v>
@@ -25599,7 +25599,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G870" t="n">
-        <v>0.559758841991425</v>
+        <v>0.559758901596069</v>
       </c>
       <c r="H870" t="n">
         <v>427684</v>
@@ -25715,7 +25715,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G874" t="n">
-        <v>0.567907750606537</v>
+        <v>0.567907631397247</v>
       </c>
       <c r="H874" t="n">
         <v>337813</v>
@@ -25744,7 +25744,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G875" t="n">
-        <v>0.559758841991425</v>
+        <v>0.559758901596069</v>
       </c>
       <c r="H875" t="n">
         <v>854969</v>
@@ -25773,7 +25773,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G876" t="n">
-        <v>0.552236914634705</v>
+        <v>0.55223685503006</v>
       </c>
       <c r="H876" t="n">
         <v>517065</v>
@@ -25802,7 +25802,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>0.586712598800659</v>
+        <v>0.586712539196014</v>
       </c>
       <c r="H877" t="n">
         <v>1489741</v>
@@ -25889,7 +25889,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G880" t="n">
-        <v>0.595488250255585</v>
+        <v>0.59548819065094</v>
       </c>
       <c r="H880" t="n">
         <v>554000</v>
@@ -25947,7 +25947,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G882" t="n">
-        <v>0.610532104969025</v>
+        <v>0.610532164573669</v>
       </c>
       <c r="H882" t="n">
         <v>713244</v>
@@ -25976,7 +25976,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G883" t="n">
-        <v>0.59235405921936</v>
+        <v>0.592353999614716</v>
       </c>
       <c r="H883" t="n">
         <v>3617135</v>
@@ -26005,7 +26005,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G884" t="n">
-        <v>0.586712598800659</v>
+        <v>0.586712539196014</v>
       </c>
       <c r="H884" t="n">
         <v>465294</v>
@@ -26034,7 +26034,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G885" t="n">
-        <v>0.581697940826416</v>
+        <v>0.581697881221771</v>
       </c>
       <c r="H885" t="n">
         <v>254204</v>
@@ -26237,7 +26237,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G892" t="n">
-        <v>0.585458934307098</v>
+        <v>0.585458993911743</v>
       </c>
       <c r="H892" t="n">
         <v>535497</v>
@@ -26295,7 +26295,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G894" t="n">
-        <v>0.583578407764435</v>
+        <v>0.58357834815979</v>
       </c>
       <c r="H894" t="n">
         <v>309944</v>
@@ -26440,7 +26440,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G899" t="n">
-        <v>0.586712598800659</v>
+        <v>0.586712539196014</v>
       </c>
       <c r="H899" t="n">
         <v>1551911</v>
@@ -26527,7 +26527,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G902" t="n">
-        <v>0.571041822433472</v>
+        <v>0.571041882038116</v>
       </c>
       <c r="H902" t="n">
         <v>220169</v>
@@ -26585,7 +26585,7 @@
         <v>0.898999989032745</v>
       </c>
       <c r="G904" t="n">
-        <v>0.563519835472107</v>
+        <v>0.563519895076752</v>
       </c>
       <c r="H904" t="n">
         <v>222288</v>
@@ -26730,7 +26730,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>0.597995579242706</v>
+        <v>0.597995519638062</v>
       </c>
       <c r="H909" t="n">
         <v>630123</v>
@@ -26788,7 +26788,7 @@
         <v>0.97299998998642</v>
       </c>
       <c r="G911" t="n">
-        <v>0.609905242919922</v>
+        <v>0.609905302524567</v>
       </c>
       <c r="H911" t="n">
         <v>993567</v>
@@ -26817,7 +26817,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G912" t="n">
-        <v>0.589219927787781</v>
+        <v>0.589219868183136</v>
       </c>
       <c r="H912" t="n">
         <v>1562877</v>
@@ -26875,7 +26875,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G914" t="n">
-        <v>0.577937006950378</v>
+        <v>0.577936947345734</v>
       </c>
       <c r="H914" t="n">
         <v>707543</v>
@@ -26904,7 +26904,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G915" t="n">
-        <v>0.565400362014771</v>
+        <v>0.565400421619415</v>
       </c>
       <c r="H915" t="n">
         <v>330326</v>
@@ -26962,7 +26962,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G917" t="n">
-        <v>0.567280828952789</v>
+        <v>0.567280769348145</v>
       </c>
       <c r="H917" t="n">
         <v>269728</v>
@@ -27020,7 +27020,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G919" t="n">
-        <v>0.510866224765778</v>
+        <v>0.510866165161133</v>
       </c>
       <c r="H919" t="n">
         <v>2362071</v>
@@ -27049,7 +27049,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G920" t="n">
-        <v>0.52214914560318</v>
+        <v>0.522149085998535</v>
       </c>
       <c r="H920" t="n">
         <v>895121</v>
@@ -27078,7 +27078,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G921" t="n">
-        <v>0.514000356197357</v>
+        <v>0.514000296592712</v>
       </c>
       <c r="H921" t="n">
         <v>427328</v>
@@ -27107,7 +27107,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G922" t="n">
-        <v>0.525910019874573</v>
+        <v>0.525910079479218</v>
       </c>
       <c r="H922" t="n">
         <v>332665</v>
@@ -27165,7 +27165,7 @@
         <v>0.828999996185303</v>
       </c>
       <c r="G924" t="n">
-        <v>0.519641757011414</v>
+        <v>0.519641816616058</v>
       </c>
       <c r="H924" t="n">
         <v>395199</v>
@@ -27339,7 +27339,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G930" t="n">
-        <v>0.542834520339966</v>
+        <v>0.542834460735321</v>
       </c>
       <c r="H930" t="n">
         <v>407084</v>
@@ -27513,7 +27513,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G936" t="n">
-        <v>0.557251513004303</v>
+        <v>0.557251572608948</v>
       </c>
       <c r="H936" t="n">
         <v>1069515</v>
@@ -27600,7 +27600,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G939" t="n">
-        <v>0.557878434658051</v>
+        <v>0.557878315448761</v>
       </c>
       <c r="H939" t="n">
         <v>653253</v>
@@ -27629,7 +27629,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G940" t="n">
-        <v>0.567907750606537</v>
+        <v>0.567907631397247</v>
       </c>
       <c r="H940" t="n">
         <v>835042</v>
@@ -27774,7 +27774,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G945" t="n">
-        <v>0.550983250141144</v>
+        <v>0.550983309745789</v>
       </c>
       <c r="H945" t="n">
         <v>222346</v>
@@ -28035,7 +28035,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G954" t="n">
-        <v>0.596115052700043</v>
+        <v>0.596114993095398</v>
       </c>
       <c r="H954" t="n">
         <v>512830</v>
@@ -28093,7 +28093,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G956" t="n">
-        <v>0.550983250141144</v>
+        <v>0.550983309745789</v>
       </c>
       <c r="H956" t="n">
         <v>467874</v>
@@ -28180,7 +28180,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G959" t="n">
-        <v>0.542834520339966</v>
+        <v>0.542834460735321</v>
       </c>
       <c r="H959" t="n">
         <v>246166</v>
@@ -28209,7 +28209,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G960" t="n">
-        <v>0.55662477016449</v>
+        <v>0.556624710559845</v>
       </c>
       <c r="H960" t="n">
         <v>444338</v>
@@ -28238,7 +28238,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G961" t="n">
-        <v>0.567280828952789</v>
+        <v>0.567280769348145</v>
       </c>
       <c r="H961" t="n">
         <v>1151949</v>
@@ -28383,7 +28383,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G966" t="n">
-        <v>0.577937006950378</v>
+        <v>0.577936947345734</v>
       </c>
       <c r="H966" t="n">
         <v>548038</v>
@@ -28470,7 +28470,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>0.583578407764435</v>
+        <v>0.58357834815979</v>
       </c>
       <c r="H969" t="n">
         <v>245470</v>
@@ -28557,7 +28557,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G972" t="n">
-        <v>0.566653966903687</v>
+        <v>0.566654026508331</v>
       </c>
       <c r="H972" t="n">
         <v>155436</v>
@@ -28644,7 +28644,7 @@
         <v>0.912999987602234</v>
       </c>
       <c r="G975" t="n">
-        <v>0.572295486927032</v>
+        <v>0.572295427322388</v>
       </c>
       <c r="H975" t="n">
         <v>211546</v>
@@ -28702,7 +28702,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G977" t="n">
-        <v>0.583578407764435</v>
+        <v>0.58357834815979</v>
       </c>
       <c r="H977" t="n">
         <v>905110</v>
@@ -28818,7 +28818,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G981" t="n">
-        <v>0.585458934307098</v>
+        <v>0.585458993911743</v>
       </c>
       <c r="H981" t="n">
         <v>1207352</v>
@@ -28963,7 +28963,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G986" t="n">
-        <v>0.561639487743378</v>
+        <v>0.561639368534088</v>
       </c>
       <c r="H986" t="n">
         <v>303695</v>
@@ -29021,7 +29021,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G988" t="n">
-        <v>0.561639487743378</v>
+        <v>0.561639368534088</v>
       </c>
       <c r="H988" t="n">
         <v>285198</v>
@@ -29137,7 +29137,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G992" t="n">
-        <v>0.567280828952789</v>
+        <v>0.567280769348145</v>
       </c>
       <c r="H992" t="n">
         <v>258666</v>
@@ -29166,7 +29166,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G993" t="n">
-        <v>0.566653966903687</v>
+        <v>0.566654026508331</v>
       </c>
       <c r="H993" t="n">
         <v>137382</v>
@@ -29195,7 +29195,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G994" t="n">
-        <v>0.594234526157379</v>
+        <v>0.594234585762024</v>
       </c>
       <c r="H994" t="n">
         <v>1520292</v>
@@ -29369,7 +29369,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.650649130344391</v>
+        <v>0.65064924955368</v>
       </c>
       <c r="H1000" t="n">
         <v>687283</v>
@@ -29398,7 +29398,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.665693163871765</v>
+        <v>0.66569310426712</v>
       </c>
       <c r="H1001" t="n">
         <v>860044</v>
@@ -29427,7 +29427,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.676976025104523</v>
+        <v>0.676976084709167</v>
       </c>
       <c r="H1002" t="n">
         <v>690539</v>
@@ -29456,7 +29456,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.666946768760681</v>
+        <v>0.666946828365326</v>
       </c>
       <c r="H1003" t="n">
         <v>1611733</v>
@@ -29485,7 +29485,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.675722360610962</v>
+        <v>0.675722301006317</v>
       </c>
       <c r="H1004" t="n">
         <v>622973</v>
@@ -29514,7 +29514,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.671961426734924</v>
+        <v>0.671961486339569</v>
       </c>
       <c r="H1005" t="n">
         <v>275954</v>
@@ -29543,7 +29543,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.670707702636719</v>
+        <v>0.670707762241364</v>
       </c>
       <c r="H1006" t="n">
         <v>472131</v>
@@ -29572,7 +29572,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.661932110786438</v>
+        <v>0.661932170391083</v>
       </c>
       <c r="H1007" t="n">
         <v>744327</v>
@@ -29601,7 +29601,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.666946768760681</v>
+        <v>0.666946828365326</v>
       </c>
       <c r="H1008" t="n">
         <v>336082</v>
@@ -29659,7 +29659,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.650649130344391</v>
+        <v>0.65064924955368</v>
       </c>
       <c r="H1010" t="n">
         <v>600655</v>
@@ -29688,7 +29688,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.651902914047241</v>
+        <v>0.651902854442596</v>
       </c>
       <c r="H1011" t="n">
         <v>442940</v>
@@ -29717,7 +29717,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.645634591579437</v>
+        <v>0.645634531974792</v>
       </c>
       <c r="H1012" t="n">
         <v>449215</v>
@@ -29746,7 +29746,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.640619874000549</v>
+        <v>0.640619933605194</v>
       </c>
       <c r="H1013" t="n">
         <v>288332</v>
@@ -29804,7 +29804,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.631844401359558</v>
+        <v>0.631844282150269</v>
       </c>
       <c r="H1015" t="n">
         <v>445410</v>
@@ -29862,7 +29862,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.633098006248474</v>
+        <v>0.633097946643829</v>
       </c>
       <c r="H1017" t="n">
         <v>665844</v>
@@ -29891,7 +29891,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.631844401359558</v>
+        <v>0.631844282150269</v>
       </c>
       <c r="H1018" t="n">
         <v>784918</v>
@@ -29920,7 +29920,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.633098006248474</v>
+        <v>0.633097946643829</v>
       </c>
       <c r="H1019" t="n">
         <v>266106</v>
@@ -29949,7 +29949,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.624949157238007</v>
+        <v>0.624949216842651</v>
       </c>
       <c r="H1020" t="n">
         <v>388690</v>
@@ -30065,7 +30065,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.594234526157379</v>
+        <v>0.594234585762024</v>
       </c>
       <c r="H1024" t="n">
         <v>2171342</v>
@@ -30094,7 +30094,7 @@
         <v>0.936999976634979</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.587339341640472</v>
+        <v>0.587339401245117</v>
       </c>
       <c r="H1025" t="n">
         <v>607405</v>
@@ -30123,7 +30123,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.58796626329422</v>
+        <v>0.587966203689575</v>
       </c>
       <c r="H1026" t="n">
         <v>412591</v>
@@ -30152,7 +30152,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.594234526157379</v>
+        <v>0.594234585762024</v>
       </c>
       <c r="H1027" t="n">
         <v>534801</v>
@@ -30268,7 +30268,7 @@
         <v>0.944999992847443</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.59235405921936</v>
+        <v>0.592353999614716</v>
       </c>
       <c r="H1031" t="n">
         <v>446583</v>
@@ -30326,7 +30326,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.571041822433472</v>
+        <v>0.571041882038116</v>
       </c>
       <c r="H1033" t="n">
         <v>969276</v>
@@ -30355,7 +30355,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.591727256774902</v>
+        <v>0.591727197170258</v>
       </c>
       <c r="H1034" t="n">
         <v>902715</v>
@@ -30471,7 +30471,7 @@
         <v>0.907000005245209</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.56853449344635</v>
+        <v>0.568534553050995</v>
       </c>
       <c r="H1038" t="n">
         <v>338242</v>
@@ -30587,7 +30587,7 @@
         <v>0.912999987602234</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.572295486927032</v>
+        <v>0.572295427322388</v>
       </c>
       <c r="H1042" t="n">
         <v>293023</v>
@@ -30819,7 +30819,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.583578407764435</v>
+        <v>0.58357834815979</v>
       </c>
       <c r="H1050" t="n">
         <v>156549</v>
@@ -30877,7 +30877,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.567280828952789</v>
+        <v>0.567280769348145</v>
       </c>
       <c r="H1052" t="n">
         <v>361174</v>
@@ -30906,7 +30906,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.53405886888504</v>
+        <v>0.534058928489685</v>
       </c>
       <c r="H1053" t="n">
         <v>1143503</v>
@@ -30964,7 +30964,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.567907750606537</v>
+        <v>0.567907631397247</v>
       </c>
       <c r="H1055" t="n">
         <v>683127</v>
@@ -31022,7 +31022,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.547849237918854</v>
+        <v>0.547849118709564</v>
       </c>
       <c r="H1057" t="n">
         <v>596731</v>
@@ -31109,7 +31109,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.51462709903717</v>
+        <v>0.51462721824646</v>
       </c>
       <c r="H1060" t="n">
         <v>386186</v>
@@ -31196,7 +31196,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.445049107074738</v>
+        <v>0.445049047470093</v>
       </c>
       <c r="H1063" t="n">
         <v>1021715</v>
@@ -31225,7 +31225,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.431258857250214</v>
+        <v>0.431258797645569</v>
       </c>
       <c r="H1064" t="n">
         <v>816145</v>
@@ -31254,7 +31254,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.42624419927597</v>
+        <v>0.426244169473648</v>
       </c>
       <c r="H1065" t="n">
         <v>893796</v>
@@ -31283,7 +31283,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.363561183214188</v>
+        <v>0.363561242818832</v>
       </c>
       <c r="H1066" t="n">
         <v>870890</v>
@@ -31312,7 +31312,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.389888077974319</v>
+        <v>0.389888048171997</v>
       </c>
       <c r="H1067" t="n">
         <v>834552</v>
@@ -31370,7 +31370,7 @@
         <v>0.574999988079071</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.360427021980286</v>
+        <v>0.360427051782608</v>
       </c>
       <c r="H1069" t="n">
         <v>600077</v>
@@ -31428,7 +31428,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.353531926870346</v>
+        <v>0.353531956672668</v>
       </c>
       <c r="H1071" t="n">
         <v>425741</v>
@@ -31457,7 +31457,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.37484410405159</v>
+        <v>0.374844133853912</v>
       </c>
       <c r="H1072" t="n">
         <v>414300</v>
@@ -31486,7 +31486,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.383619725704193</v>
+        <v>0.383619785308838</v>
       </c>
       <c r="H1073" t="n">
         <v>522069</v>
@@ -31515,7 +31515,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.401170998811722</v>
+        <v>0.401170969009399</v>
       </c>
       <c r="H1074" t="n">
         <v>347310</v>
@@ -31544,7 +31544,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.42624419927597</v>
+        <v>0.426244169473648</v>
       </c>
       <c r="H1075" t="n">
         <v>634305</v>
@@ -31573,7 +31573,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.432512491941452</v>
+        <v>0.432512521743774</v>
       </c>
       <c r="H1076" t="n">
         <v>381458</v>
@@ -31631,7 +31631,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.445675939321518</v>
+        <v>0.445675879716873</v>
       </c>
       <c r="H1078" t="n">
         <v>202876</v>
@@ -31660,7 +31660,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.455078363418579</v>
+        <v>0.455078274011612</v>
       </c>
       <c r="H1079" t="n">
         <v>257687</v>
@@ -31689,7 +31689,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.441288113594055</v>
+        <v>0.44128805398941</v>
       </c>
       <c r="H1080" t="n">
         <v>176795</v>
@@ -31718,7 +31718,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.440034478902817</v>
+        <v>0.440034419298172</v>
       </c>
       <c r="H1081" t="n">
         <v>221351</v>
@@ -31747,7 +31747,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.431885659694672</v>
+        <v>0.431885629892349</v>
       </c>
       <c r="H1082" t="n">
         <v>405701</v>
@@ -31776,7 +31776,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.440034478902817</v>
+        <v>0.440034419298172</v>
       </c>
       <c r="H1083" t="n">
         <v>247888</v>
@@ -31805,7 +31805,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.449436873197556</v>
+        <v>0.449436902999878</v>
       </c>
       <c r="H1084" t="n">
         <v>217982</v>
@@ -31834,7 +31834,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.463854044675827</v>
+        <v>0.463853985071182</v>
       </c>
       <c r="H1085" t="n">
         <v>320620</v>
@@ -31863,7 +31863,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.461973428726196</v>
+        <v>0.461973488330841</v>
       </c>
       <c r="H1086" t="n">
         <v>284063</v>
@@ -31892,7 +31892,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.46071982383728</v>
+        <v>0.460719853639603</v>
       </c>
       <c r="H1087" t="n">
         <v>266083</v>
@@ -31921,7 +31921,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.475136935710907</v>
+        <v>0.47513684630394</v>
       </c>
       <c r="H1088" t="n">
         <v>203722</v>
@@ -31950,7 +31950,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.448183208703995</v>
+        <v>0.448183238506317</v>
       </c>
       <c r="H1089" t="n">
         <v>245558</v>
@@ -32008,7 +32008,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.450690567493439</v>
+        <v>0.450690507888794</v>
       </c>
       <c r="H1091" t="n">
         <v>175084</v>
@@ -32037,7 +32037,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.455078363418579</v>
+        <v>0.455078274011612</v>
       </c>
       <c r="H1092" t="n">
         <v>114072</v>
@@ -32095,7 +32095,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.448810040950775</v>
+        <v>0.448810070753098</v>
       </c>
       <c r="H1094" t="n">
         <v>41034</v>
@@ -32153,7 +32153,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.453824669122696</v>
+        <v>0.453824698925018</v>
       </c>
       <c r="H1096" t="n">
         <v>223930</v>
@@ -32182,7 +32182,7 @@
         <v>0.718999981880188</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.450690567493439</v>
+        <v>0.450690507888794</v>
       </c>
       <c r="H1097" t="n">
         <v>129383</v>
@@ -32211,7 +32211,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.46071982383728</v>
+        <v>0.460719853639603</v>
       </c>
       <c r="H1098" t="n">
         <v>121235</v>
@@ -32269,7 +32269,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.439407616853714</v>
+        <v>0.439407527446747</v>
       </c>
       <c r="H1100" t="n">
         <v>227942</v>
@@ -32298,7 +32298,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.441288113594055</v>
+        <v>0.44128805398941</v>
       </c>
       <c r="H1101" t="n">
         <v>78665</v>
@@ -32327,7 +32327,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.397410005331039</v>
+        <v>0.397410064935684</v>
       </c>
       <c r="H1102" t="n">
         <v>2993560</v>
@@ -32414,7 +32414,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.407439261674881</v>
+        <v>0.407439321279526</v>
       </c>
       <c r="H1105" t="n">
         <v>208775</v>
@@ -32472,7 +32472,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.399917364120483</v>
+        <v>0.399917334318161</v>
       </c>
       <c r="H1107" t="n">
         <v>162479</v>
@@ -32501,7 +32501,7 @@
         <v>0.60699999332428</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.380485564470291</v>
+        <v>0.380485624074936</v>
       </c>
       <c r="H1108" t="n">
         <v>353703</v>
@@ -32588,7 +32588,7 @@
         <v>0.577000021934509</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.381231009960175</v>
+        <v>0.381231039762497</v>
       </c>
       <c r="H1111" t="n">
         <v>890139</v>
@@ -32617,7 +32617,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.383873909711838</v>
+        <v>0.383873879909515</v>
       </c>
       <c r="H1112" t="n">
         <v>482825</v>
@@ -32675,7 +32675,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.417570263147354</v>
+        <v>0.417570233345032</v>
       </c>
       <c r="H1114" t="n">
         <v>398096</v>
@@ -32733,7 +32733,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.424838036298752</v>
+        <v>0.424838095903397</v>
       </c>
       <c r="H1116" t="n">
         <v>229725</v>
@@ -32762,7 +32762,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.452587932348251</v>
+        <v>0.452587962150574</v>
       </c>
       <c r="H1117" t="n">
         <v>3188370</v>
@@ -32791,7 +32791,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.436070203781128</v>
+        <v>0.436070144176483</v>
       </c>
       <c r="H1118" t="n">
         <v>1469789</v>
@@ -32878,7 +32878,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.433427333831787</v>
+        <v>0.433427304029465</v>
       </c>
       <c r="H1121" t="n">
         <v>750775</v>
@@ -32907,7 +32907,7 @@
         <v>0.657000005245209</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.4340880215168</v>
+        <v>0.434087991714478</v>
       </c>
       <c r="H1122" t="n">
         <v>488772</v>
@@ -32936,7 +32936,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.436070203781128</v>
+        <v>0.436070144176483</v>
       </c>
       <c r="H1123" t="n">
         <v>610828</v>
@@ -32965,7 +32965,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.446641534566879</v>
+        <v>0.446641564369202</v>
       </c>
       <c r="H1124" t="n">
         <v>994113</v>
@@ -32994,7 +32994,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.463820099830627</v>
+        <v>0.463820070028305</v>
       </c>
       <c r="H1125" t="n">
         <v>2465961</v>
@@ -33110,7 +33110,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.414266645908356</v>
+        <v>0.414266675710678</v>
       </c>
       <c r="H1129" t="n">
         <v>848055</v>
@@ -33139,7 +33139,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.411623805761337</v>
+        <v>0.41162383556366</v>
       </c>
       <c r="H1130" t="n">
         <v>580344</v>
@@ -33197,7 +33197,7 @@
         <v>0.629000008106232</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.415588080883026</v>
+        <v>0.415588051080704</v>
       </c>
       <c r="H1132" t="n">
         <v>326063</v>
@@ -33226,7 +33226,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.418891608715057</v>
+        <v>0.418891698122025</v>
       </c>
       <c r="H1133" t="n">
         <v>298272</v>
@@ -33255,7 +33255,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.416909486055374</v>
+        <v>0.416909456253052</v>
       </c>
       <c r="H1134" t="n">
         <v>513853</v>
@@ -33284,7 +33284,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.411623805761337</v>
+        <v>0.41162383556366</v>
       </c>
       <c r="H1135" t="n">
         <v>569862</v>
@@ -33313,7 +33313,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.414266645908356</v>
+        <v>0.414266675710678</v>
       </c>
       <c r="H1136" t="n">
         <v>342880</v>
@@ -33371,7 +33371,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.410963118076324</v>
+        <v>0.410963088274002</v>
       </c>
       <c r="H1138" t="n">
         <v>627950</v>
@@ -33400,7 +33400,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.399730980396271</v>
+        <v>0.399731010198593</v>
       </c>
       <c r="H1139" t="n">
         <v>553252</v>
@@ -33429,7 +33429,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.410963118076324</v>
+        <v>0.410963088274002</v>
       </c>
       <c r="H1140" t="n">
         <v>455993</v>
@@ -33458,7 +33458,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.407659471035004</v>
+        <v>0.407659500837326</v>
       </c>
       <c r="H1141" t="n">
         <v>232217</v>
@@ -33487,7 +33487,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.399070203304291</v>
+        <v>0.399070262908936</v>
       </c>
       <c r="H1142" t="n">
         <v>544075</v>
@@ -33632,7 +33632,7 @@
         <v>0.64300000667572</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.424838036298752</v>
+        <v>0.424838095903397</v>
       </c>
       <c r="H1147" t="n">
         <v>581576</v>
@@ -33661,7 +33661,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.411623805761337</v>
+        <v>0.41162383556366</v>
       </c>
       <c r="H1148" t="n">
         <v>269579</v>
@@ -33690,7 +33690,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.426159471273422</v>
+        <v>0.4261594414711</v>
       </c>
       <c r="H1149" t="n">
         <v>263126</v>
@@ -33719,7 +33719,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.414266645908356</v>
+        <v>0.414266675710678</v>
       </c>
       <c r="H1150" t="n">
         <v>467200</v>
@@ -33748,7 +33748,7 @@
         <v>0.625</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.412945210933685</v>
+        <v>0.412945181131363</v>
       </c>
       <c r="H1151" t="n">
         <v>255745</v>
@@ -33777,7 +33777,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.424177348613739</v>
+        <v>0.424177378416061</v>
       </c>
       <c r="H1152" t="n">
         <v>355815</v>
@@ -33806,7 +33806,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.418891608715057</v>
+        <v>0.418891698122025</v>
       </c>
       <c r="H1153" t="n">
         <v>337679</v>
@@ -33835,7 +33835,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.416909486055374</v>
+        <v>0.416909456253052</v>
       </c>
       <c r="H1154" t="n">
         <v>33063</v>
@@ -33893,7 +33893,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.423516601324081</v>
+        <v>0.423516571521759</v>
       </c>
       <c r="H1156" t="n">
         <v>431315</v>
@@ -33922,7 +33922,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.418891608715057</v>
+        <v>0.418891698122025</v>
       </c>
       <c r="H1157" t="n">
         <v>207704</v>
@@ -34009,7 +34009,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.400391697883606</v>
+        <v>0.400391668081284</v>
       </c>
       <c r="H1160" t="n">
         <v>673400</v>
@@ -34038,7 +34038,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.391141772270203</v>
+        <v>0.391141712665558</v>
       </c>
       <c r="H1161" t="n">
         <v>335122</v>
@@ -34067,7 +34067,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.397748857736588</v>
+        <v>0.397748798131943</v>
       </c>
       <c r="H1162" t="n">
         <v>367865</v>
@@ -34125,7 +34125,7 @@
         <v>0.587000012397766</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.387838155031204</v>
+        <v>0.387838214635849</v>
       </c>
       <c r="H1164" t="n">
         <v>210884</v>
@@ -34154,7 +34154,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.387177467346191</v>
+        <v>0.387177407741547</v>
       </c>
       <c r="H1165" t="n">
         <v>351309</v>
@@ -34212,7 +34212,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.406338065862656</v>
+        <v>0.406338095664978</v>
       </c>
       <c r="H1167" t="n">
         <v>290328</v>
@@ -34270,7 +34270,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.399730980396271</v>
+        <v>0.399731010198593</v>
       </c>
       <c r="H1169" t="n">
         <v>271378</v>
@@ -34328,7 +34328,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.407659471035004</v>
+        <v>0.407659500837326</v>
       </c>
       <c r="H1171" t="n">
         <v>434330</v>
@@ -34357,7 +34357,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.404355943202972</v>
+        <v>0.404355973005295</v>
       </c>
       <c r="H1172" t="n">
         <v>303358</v>
@@ -34386,7 +34386,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.404355943202972</v>
+        <v>0.404355973005295</v>
       </c>
       <c r="H1173" t="n">
         <v>126519</v>
@@ -34444,7 +34444,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.393123865127563</v>
+        <v>0.393123894929886</v>
       </c>
       <c r="H1175" t="n">
         <v>265445</v>
@@ -34473,7 +34473,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.388498842716217</v>
+        <v>0.388498872518539</v>
       </c>
       <c r="H1176" t="n">
         <v>470646</v>
@@ -34502,7 +34502,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.393123865127563</v>
+        <v>0.393123894929886</v>
       </c>
       <c r="H1177" t="n">
         <v>186350</v>
@@ -34531,7 +34531,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.383873909711838</v>
+        <v>0.383873879909515</v>
       </c>
       <c r="H1178" t="n">
         <v>234967</v>
@@ -34560,7 +34560,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.377927452325821</v>
+        <v>0.377927541732788</v>
       </c>
       <c r="H1179" t="n">
         <v>299381</v>
@@ -34676,7 +34676,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.373302459716797</v>
+        <v>0.373302489519119</v>
       </c>
       <c r="H1183" t="n">
         <v>599394</v>
@@ -34705,7 +34705,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.376606047153473</v>
+        <v>0.376605987548828</v>
       </c>
       <c r="H1184" t="n">
         <v>323533</v>
@@ -34734,7 +34734,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.372641742229462</v>
+        <v>0.372641801834106</v>
       </c>
       <c r="H1185" t="n">
         <v>226096</v>
@@ -34763,7 +34763,7 @@
         <v>0.545000016689301</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.360088229179382</v>
+        <v>0.36008819937706</v>
       </c>
       <c r="H1186" t="n">
         <v>1205423</v>
@@ -34821,7 +34821,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.371981084346771</v>
+        <v>0.371981054544449</v>
       </c>
       <c r="H1188" t="n">
         <v>605549</v>
@@ -34850,7 +34850,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.388498842716217</v>
+        <v>0.388498872518539</v>
       </c>
       <c r="H1189" t="n">
         <v>1305697</v>
@@ -34908,7 +34908,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.373302459716797</v>
+        <v>0.373302489519119</v>
       </c>
       <c r="H1191" t="n">
         <v>168075</v>
@@ -34995,7 +34995,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.377927452325821</v>
+        <v>0.377927541732788</v>
       </c>
       <c r="H1194" t="n">
         <v>109042</v>
@@ -35024,7 +35024,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.376606047153473</v>
+        <v>0.376605987548828</v>
       </c>
       <c r="H1195" t="n">
         <v>244635</v>
@@ -35053,7 +35053,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.376606047153473</v>
+        <v>0.376605987548828</v>
       </c>
       <c r="H1196" t="n">
         <v>396380</v>
@@ -35227,7 +35227,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.337623983621597</v>
+        <v>0.33762401342392</v>
       </c>
       <c r="H1202" t="n">
         <v>1087499</v>
@@ -35256,7 +35256,7 @@
         <v>0.510999977588654</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.337623983621597</v>
+        <v>0.33762401342392</v>
       </c>
       <c r="H1203" t="n">
         <v>304003</v>
@@ -35314,7 +35314,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.331677615642548</v>
+        <v>0.331677585840225</v>
       </c>
       <c r="H1205" t="n">
         <v>91704</v>
@@ -35343,7 +35343,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.331677615642548</v>
+        <v>0.331677585840225</v>
       </c>
       <c r="H1206" t="n">
         <v>214791</v>
@@ -35401,7 +35401,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.333659768104553</v>
+        <v>0.333659738302231</v>
       </c>
       <c r="H1208" t="n">
         <v>90189</v>
@@ -35430,7 +35430,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.331677615642548</v>
+        <v>0.331677585840225</v>
       </c>
       <c r="H1209" t="n">
         <v>172610</v>
@@ -35459,7 +35459,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.333659768104553</v>
+        <v>0.333659738302231</v>
       </c>
       <c r="H1210" t="n">
         <v>110729</v>
@@ -35517,7 +35517,7 @@
         <v>0.546999990940094</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.361409664154053</v>
+        <v>0.36140963435173</v>
       </c>
       <c r="H1212" t="n">
         <v>621623</v>
@@ -35546,7 +35546,7 @@
         <v>0.549000024795532</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.362731128931046</v>
+        <v>0.362731099128723</v>
       </c>
       <c r="H1213" t="n">
         <v>229595</v>
@@ -35575,7 +35575,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.350177556276321</v>
+        <v>0.350177526473999</v>
       </c>
       <c r="H1214" t="n">
         <v>378570</v>
@@ -35604,7 +35604,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.346213310956955</v>
+        <v>0.346213281154633</v>
       </c>
       <c r="H1215" t="n">
         <v>101762</v>
@@ -35633,7 +35633,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.338284760713577</v>
+        <v>0.338284730911255</v>
       </c>
       <c r="H1216" t="n">
         <v>211820</v>
@@ -35691,7 +35691,7 @@
         <v>0.5</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.330356180667877</v>
+        <v>0.330356150865555</v>
       </c>
       <c r="H1218" t="n">
         <v>264270</v>
@@ -35778,7 +35778,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.338284760713577</v>
+        <v>0.338284730911255</v>
       </c>
       <c r="H1221" t="n">
         <v>172220</v>
@@ -35807,7 +35807,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.331677615642548</v>
+        <v>0.331677585840225</v>
       </c>
       <c r="H1222" t="n">
         <v>81698</v>
@@ -35836,7 +35836,7 @@
         <v>0.499000012874603</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.329695463180542</v>
+        <v>0.329695492982864</v>
       </c>
       <c r="H1223" t="n">
         <v>117326</v>
@@ -35865,7 +35865,7 @@
         <v>0.5</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.330356180667877</v>
+        <v>0.330356150865555</v>
       </c>
       <c r="H1224" t="n">
         <v>123819</v>
@@ -36097,7 +36097,7 @@
         <v>0.474500000476837</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.313508003950119</v>
+        <v>0.313508033752441</v>
       </c>
       <c r="H1232" t="n">
         <v>200674</v>
@@ -36213,7 +36213,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.335641890764236</v>
+        <v>0.335641860961914</v>
       </c>
       <c r="H1236" t="n">
         <v>589782</v>
@@ -36242,7 +36242,7 @@
         <v>0.504999995231628</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.333659768104553</v>
+        <v>0.333659738302231</v>
       </c>
       <c r="H1237" t="n">
         <v>278941</v>
@@ -36271,7 +36271,7 @@
         <v>0.507000029087067</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.334981173276901</v>
+        <v>0.334981203079224</v>
       </c>
       <c r="H1238" t="n">
         <v>120644</v>
@@ -36300,7 +36300,7 @@
         <v>0.512000024318695</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.338284760713577</v>
+        <v>0.338284730911255</v>
       </c>
       <c r="H1239" t="n">
         <v>219531</v>
@@ -36329,7 +36329,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.362070351839066</v>
+        <v>0.36207041144371</v>
       </c>
       <c r="H1240" t="n">
         <v>589201</v>
@@ -36358,7 +36358,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.368677496910095</v>
+        <v>0.368677526712418</v>
       </c>
       <c r="H1241" t="n">
         <v>548949</v>
@@ -36387,7 +36387,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.383213132619858</v>
+        <v>0.383213192224503</v>
       </c>
       <c r="H1242" t="n">
         <v>693013</v>
@@ -36416,7 +36416,7 @@
         <v>0.564999997615814</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.373302459716797</v>
+        <v>0.373302489519119</v>
       </c>
       <c r="H1243" t="n">
         <v>255907</v>
@@ -36474,7 +36474,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.383213132619858</v>
+        <v>0.383213192224503</v>
       </c>
       <c r="H1245" t="n">
         <v>455896</v>
@@ -36532,7 +36532,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.385856002569199</v>
+        <v>0.385855972766876</v>
       </c>
       <c r="H1247" t="n">
         <v>193021</v>
@@ -36561,7 +36561,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.390480995178223</v>
+        <v>0.390481024980545</v>
       </c>
       <c r="H1248" t="n">
         <v>201800</v>
@@ -36590,7 +36590,7 @@
         <v>0.591000020503998</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.390480995178223</v>
+        <v>0.390481024980545</v>
       </c>
       <c r="H1249" t="n">
         <v>152084</v>
@@ -36619,7 +36619,7 @@
         <v>0.583000004291534</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.385195344686508</v>
+        <v>0.385195314884186</v>
       </c>
       <c r="H1250" t="n">
         <v>126522</v>
@@ -36648,7 +36648,7 @@
         <v>0.580999970436096</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.383873909711838</v>
+        <v>0.383873879909515</v>
       </c>
       <c r="H1251" t="n">
         <v>131495</v>
@@ -36735,7 +36735,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.383213132619858</v>
+        <v>0.383213192224503</v>
       </c>
       <c r="H1254" t="n">
         <v>524257</v>
@@ -36764,7 +36764,7 @@
         <v>0.58899998664856</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.389159560203552</v>
+        <v>0.389159590005875</v>
       </c>
       <c r="H1255" t="n">
         <v>199698</v>
@@ -36793,7 +36793,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.383213132619858</v>
+        <v>0.383213192224503</v>
       </c>
       <c r="H1256" t="n">
         <v>117819</v>
@@ -36822,7 +36822,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.389820277690887</v>
+        <v>0.389820247888565</v>
       </c>
       <c r="H1257" t="n">
         <v>601116</v>
@@ -36880,7 +36880,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.377927452325821</v>
+        <v>0.377927541732788</v>
       </c>
       <c r="H1259" t="n">
         <v>189465</v>
@@ -36909,7 +36909,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.371320366859436</v>
+        <v>0.371320307254791</v>
       </c>
       <c r="H1260" t="n">
         <v>205623</v>
@@ -36938,7 +36938,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.366034656763077</v>
+        <v>0.366034626960754</v>
       </c>
       <c r="H1261" t="n">
         <v>258453</v>
@@ -37083,7 +37083,7 @@
         <v>0.546999990940094</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.361409664154053</v>
+        <v>0.36140963435173</v>
       </c>
       <c r="H1266" t="n">
         <v>100365</v>
@@ -37141,7 +37141,7 @@
         <v>0.559000015258789</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.369338244199753</v>
+        <v>0.36933821439743</v>
       </c>
       <c r="H1268" t="n">
         <v>407309</v>
@@ -37199,7 +37199,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.376606047153473</v>
+        <v>0.376605987548828</v>
       </c>
       <c r="H1270" t="n">
         <v>213467</v>
@@ -37228,7 +37228,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.368677496910095</v>
+        <v>0.368677526712418</v>
       </c>
       <c r="H1271" t="n">
         <v>140954</v>
@@ -37257,7 +37257,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.367356061935425</v>
+        <v>0.367356091737747</v>
       </c>
       <c r="H1272" t="n">
         <v>111860</v>
@@ -37286,7 +37286,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.371981084346771</v>
+        <v>0.371981054544449</v>
       </c>
       <c r="H1273" t="n">
         <v>112333</v>
@@ -37315,7 +37315,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.371320366859436</v>
+        <v>0.371320307254791</v>
       </c>
       <c r="H1274" t="n">
         <v>253489</v>
@@ -37402,7 +37402,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.359427511692047</v>
+        <v>0.359427571296692</v>
       </c>
       <c r="H1277" t="n">
         <v>639111</v>
@@ -37489,7 +37489,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.347534686326981</v>
+        <v>0.347534716129303</v>
       </c>
       <c r="H1280" t="n">
         <v>260725</v>
@@ -37721,7 +37721,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.342909693717957</v>
+        <v>0.342909723520279</v>
       </c>
       <c r="H1288" t="n">
         <v>52689</v>
@@ -37750,7 +37750,7 @@
         <v>0.518999993801117</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.342909693717957</v>
+        <v>0.342909723520279</v>
       </c>
       <c r="H1289" t="n">
         <v>151668</v>
@@ -37866,7 +37866,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.350177556276321</v>
+        <v>0.350177526473999</v>
       </c>
       <c r="H1293" t="n">
         <v>118142</v>
@@ -37924,7 +37924,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.362070351839066</v>
+        <v>0.36207041144371</v>
       </c>
       <c r="H1295" t="n">
         <v>297319</v>
@@ -38040,7 +38040,7 @@
         <v>0.595000028610229</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.393123865127563</v>
+        <v>0.393123894929886</v>
       </c>
       <c r="H1299" t="n">
         <v>255747</v>
@@ -38069,7 +38069,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.393784552812576</v>
+        <v>0.393784582614899</v>
       </c>
       <c r="H1300" t="n">
         <v>434124</v>
@@ -38098,7 +38098,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.399730980396271</v>
+        <v>0.399731010198593</v>
       </c>
       <c r="H1301" t="n">
         <v>424470</v>
@@ -38127,7 +38127,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.405677407979965</v>
+        <v>0.405677378177643</v>
       </c>
       <c r="H1302" t="n">
         <v>584172</v>
@@ -38156,7 +38156,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.404355943202972</v>
+        <v>0.404355973005295</v>
       </c>
       <c r="H1303" t="n">
         <v>512906</v>
@@ -38185,7 +38185,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.39642745256424</v>
+        <v>0.396427422761917</v>
       </c>
       <c r="H1304" t="n">
         <v>363432</v>
@@ -38243,7 +38243,7 @@
         <v>0.616999983787537</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.407659471035004</v>
+        <v>0.407659500837326</v>
       </c>
       <c r="H1306" t="n">
         <v>574533</v>
@@ -38272,7 +38272,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.409641653299332</v>
+        <v>0.409641623497009</v>
       </c>
       <c r="H1307" t="n">
         <v>361682</v>
@@ -38301,7 +38301,7 @@
         <v>0.625</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.412945210933685</v>
+        <v>0.412945181131363</v>
       </c>
       <c r="H1308" t="n">
         <v>299808</v>
@@ -38330,7 +38330,7 @@
         <v>0.625</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.412945210933685</v>
+        <v>0.412945181131363</v>
       </c>
       <c r="H1309" t="n">
         <v>475438</v>
@@ -38417,7 +38417,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.409641653299332</v>
+        <v>0.409641623497009</v>
       </c>
       <c r="H1312" t="n">
         <v>122778</v>
@@ -38475,7 +38475,7 @@
         <v>0.625</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.412945210933685</v>
+        <v>0.412945181131363</v>
       </c>
       <c r="H1314" t="n">
         <v>598600</v>
@@ -38504,7 +38504,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.409641653299332</v>
+        <v>0.409641623497009</v>
       </c>
       <c r="H1315" t="n">
         <v>168380</v>
@@ -38533,7 +38533,7 @@
         <v>0.619000017642975</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.408980995416641</v>
+        <v>0.408980965614319</v>
       </c>
       <c r="H1316" t="n">
         <v>240327</v>
@@ -38562,7 +38562,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.414266645908356</v>
+        <v>0.414266675710678</v>
       </c>
       <c r="H1317" t="n">
         <v>933421</v>
@@ -38591,7 +38591,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.417570263147354</v>
+        <v>0.417570233345032</v>
       </c>
       <c r="H1318" t="n">
         <v>430300</v>
@@ -38649,7 +38649,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.423516601324081</v>
+        <v>0.423516571521759</v>
       </c>
       <c r="H1320" t="n">
         <v>147405</v>
@@ -38707,7 +38707,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.438712984323502</v>
+        <v>0.438712954521179</v>
       </c>
       <c r="H1322" t="n">
         <v>352333</v>
@@ -38736,7 +38736,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.445320159196854</v>
+        <v>0.445320218801498</v>
       </c>
       <c r="H1323" t="n">
         <v>329905</v>
@@ -38765,7 +38765,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.457873672246933</v>
+        <v>0.457873642444611</v>
       </c>
       <c r="H1324" t="n">
         <v>721874</v>
@@ -38794,7 +38794,7 @@
         <v>0.725000023841858</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.479016482830048</v>
+        <v>0.479016453027725</v>
       </c>
       <c r="H1325" t="n">
         <v>1930959</v>
@@ -38823,7 +38823,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.476373612880707</v>
+        <v>0.476373672485352</v>
       </c>
       <c r="H1326" t="n">
         <v>780813</v>
@@ -38852,7 +38852,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.471087843179703</v>
+        <v>0.47108793258667</v>
       </c>
       <c r="H1327" t="n">
         <v>461183</v>
@@ -38881,7 +38881,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.480998635292053</v>
+        <v>0.480998575687408</v>
       </c>
       <c r="H1328" t="n">
         <v>521527</v>
@@ -38939,7 +38939,7 @@
         <v>0.72299998998642</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.477695018053055</v>
+        <v>0.477695047855377</v>
       </c>
       <c r="H1330" t="n">
         <v>205885</v>
@@ -38997,7 +38997,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.480998635292053</v>
+        <v>0.480998575687408</v>
       </c>
       <c r="H1332" t="n">
         <v>297307</v>
@@ -39026,7 +39026,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.471748560667038</v>
+        <v>0.47174859046936</v>
       </c>
       <c r="H1333" t="n">
         <v>197812</v>
@@ -39055,7 +39055,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.47703430056572</v>
+        <v>0.477034330368042</v>
       </c>
       <c r="H1334" t="n">
         <v>92172</v>
@@ -39084,7 +39084,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.485623568296432</v>
+        <v>0.485623627901077</v>
       </c>
       <c r="H1335" t="n">
         <v>412252</v>
@@ -39113,7 +39113,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.499498546123505</v>
+        <v>0.499498575925827</v>
       </c>
       <c r="H1336" t="n">
         <v>708066</v>
@@ -39171,7 +39171,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.488927125930786</v>
+        <v>0.488927185535431</v>
       </c>
       <c r="H1338" t="n">
         <v>396737</v>
@@ -39229,7 +39229,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.488927125930786</v>
+        <v>0.488927185535431</v>
       </c>
       <c r="H1340" t="n">
         <v>288336</v>
@@ -39258,7 +39258,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.488266497850418</v>
+        <v>0.488266468048096</v>
       </c>
       <c r="H1341" t="n">
         <v>104877</v>
@@ -39287,7 +39287,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.488927125930786</v>
+        <v>0.488927185535431</v>
       </c>
       <c r="H1342" t="n">
         <v>183101</v>
@@ -39374,7 +39374,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.487605661153793</v>
+        <v>0.487605690956116</v>
       </c>
       <c r="H1345" t="n">
         <v>744075</v>
@@ -39403,7 +39403,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.500819981098175</v>
+        <v>0.50081992149353</v>
       </c>
       <c r="H1346" t="n">
         <v>527196</v>
@@ -39432,7 +39432,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.506105720996857</v>
+        <v>0.506105601787567</v>
       </c>
       <c r="H1347" t="n">
         <v>341071</v>
@@ -39461,7 +39461,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.506105720996857</v>
+        <v>0.506105601787567</v>
       </c>
       <c r="H1348" t="n">
         <v>83370</v>
@@ -39490,7 +39490,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.503462791442871</v>
+        <v>0.503462851047516</v>
       </c>
       <c r="H1349" t="n">
         <v>102908</v>
@@ -39519,7 +39519,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.498837858438492</v>
+        <v>0.498837828636169</v>
       </c>
       <c r="H1350" t="n">
         <v>136615</v>
@@ -39577,7 +39577,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.487605661153793</v>
+        <v>0.487605690956116</v>
       </c>
       <c r="H1352" t="n">
         <v>376763</v>
@@ -39606,7 +39606,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.471748560667038</v>
+        <v>0.47174859046936</v>
       </c>
       <c r="H1353" t="n">
         <v>704712</v>
@@ -39664,7 +39664,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.47967717051506</v>
+        <v>0.479677110910416</v>
       </c>
       <c r="H1355" t="n">
         <v>423285</v>
@@ -39693,7 +39693,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.486284345388412</v>
+        <v>0.486284255981445</v>
       </c>
       <c r="H1356" t="n">
         <v>223105</v>
@@ -39722,7 +39722,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.486284345388412</v>
+        <v>0.486284255981445</v>
       </c>
       <c r="H1357" t="n">
         <v>342782</v>
@@ -39751,7 +39751,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.488266497850418</v>
+        <v>0.488266468048096</v>
       </c>
       <c r="H1358" t="n">
         <v>378257</v>
@@ -39780,7 +39780,7 @@
         <v>0.763000011444092</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.504123568534851</v>
+        <v>0.504123508930206</v>
       </c>
       <c r="H1359" t="n">
         <v>791653</v>
@@ -39809,7 +39809,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.494212836027145</v>
+        <v>0.49421289563179</v>
       </c>
       <c r="H1360" t="n">
         <v>1013471</v>
@@ -39838,7 +39838,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.504784226417542</v>
+        <v>0.504784286022186</v>
       </c>
       <c r="H1361" t="n">
         <v>438908</v>
@@ -39896,7 +39896,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.525266408920288</v>
+        <v>0.525266289710999</v>
       </c>
       <c r="H1363" t="n">
         <v>1328401</v>
@@ -40012,7 +40012,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.499861270189285</v>
+        <v>0.499861240386963</v>
       </c>
       <c r="H1367" t="n">
         <v>375047</v>
@@ -40070,7 +40070,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.489561915397644</v>
+        <v>0.489561975002289</v>
       </c>
       <c r="H1369" t="n">
         <v>229402</v>
@@ -40099,7 +40099,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.479949176311493</v>
+        <v>0.479949206113815</v>
       </c>
       <c r="H1370" t="n">
         <v>493029</v>
@@ -40128,7 +40128,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.47857603430748</v>
+        <v>0.478575974702835</v>
       </c>
       <c r="H1371" t="n">
         <v>333823</v>
@@ -40157,7 +40157,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.482009053230286</v>
+        <v>0.48200911283493</v>
       </c>
       <c r="H1372" t="n">
         <v>77499</v>
@@ -40331,7 +40331,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.514280438423157</v>
+        <v>0.514280319213867</v>
       </c>
       <c r="H1378" t="n">
         <v>251080</v>
@@ -40360,7 +40360,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.521833181381226</v>
+        <v>0.52183324098587</v>
       </c>
       <c r="H1379" t="n">
         <v>491738</v>
@@ -40389,7 +40389,7 @@
         <v>0.763000011444092</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.523893117904663</v>
+        <v>0.523893058300018</v>
       </c>
       <c r="H1380" t="n">
         <v>459360</v>
@@ -40534,7 +40534,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.542431950569153</v>
+        <v>0.542431890964508</v>
       </c>
       <c r="H1385" t="n">
         <v>300618</v>
@@ -40592,7 +40592,7 @@
         <v>0.778999984264374</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.53487902879715</v>
+        <v>0.534878969192505</v>
       </c>
       <c r="H1387" t="n">
         <v>235656</v>
@@ -40650,7 +40650,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.528699398040771</v>
+        <v>0.528699457645416</v>
       </c>
       <c r="H1389" t="n">
         <v>267009</v>
@@ -40708,7 +40708,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.504667639732361</v>
+        <v>0.504667580127716</v>
       </c>
       <c r="H1391" t="n">
         <v>85728</v>
@@ -40795,7 +40795,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.498488038778305</v>
+        <v>0.498488008975983</v>
       </c>
       <c r="H1394" t="n">
         <v>289227</v>
@@ -41027,7 +41027,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.480635851621628</v>
+        <v>0.480635821819305</v>
       </c>
       <c r="H1402" t="n">
         <v>256632</v>
@@ -41085,7 +41085,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.47857603430748</v>
+        <v>0.478575974702835</v>
       </c>
       <c r="H1404" t="n">
         <v>77676</v>
@@ -41143,7 +41143,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.480635851621628</v>
+        <v>0.480635821819305</v>
       </c>
       <c r="H1406" t="n">
         <v>34405</v>
@@ -41201,7 +41201,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.473769664764404</v>
+        <v>0.473769694566727</v>
       </c>
       <c r="H1408" t="n">
         <v>309633</v>
@@ -41288,7 +41288,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.45385754108429</v>
+        <v>0.453857570886612</v>
       </c>
       <c r="H1411" t="n">
         <v>361649</v>
@@ -41317,7 +41317,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.449737817049026</v>
+        <v>0.449737757444382</v>
       </c>
       <c r="H1412" t="n">
         <v>520270</v>
@@ -41404,7 +41404,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.446991384029388</v>
+        <v>0.446991324424744</v>
       </c>
       <c r="H1415" t="n">
         <v>131720</v>
@@ -41433,7 +41433,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.446991384029388</v>
+        <v>0.446991324424744</v>
       </c>
       <c r="H1416" t="n">
         <v>259108</v>
@@ -41462,7 +41462,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.447677940130234</v>
+        <v>0.447677999734879</v>
       </c>
       <c r="H1417" t="n">
         <v>186320</v>
@@ -41491,7 +41491,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.457977324724197</v>
+        <v>0.457977294921875</v>
       </c>
       <c r="H1418" t="n">
         <v>305934</v>
@@ -41578,7 +41578,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.482009053230286</v>
+        <v>0.48200911283493</v>
       </c>
       <c r="H1421" t="n">
         <v>237257</v>
@@ -41665,7 +41665,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.489561915397644</v>
+        <v>0.489561975002289</v>
       </c>
       <c r="H1424" t="n">
         <v>233029</v>
@@ -41781,7 +41781,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.483382344245911</v>
+        <v>0.483382284641266</v>
       </c>
       <c r="H1428" t="n">
         <v>270041</v>
@@ -41810,7 +41810,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.483382344245911</v>
+        <v>0.483382284641266</v>
       </c>
       <c r="H1429" t="n">
         <v>199779</v>
@@ -41839,7 +41839,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.481322467327118</v>
+        <v>0.481322437524796</v>
       </c>
       <c r="H1430" t="n">
         <v>142144</v>
@@ -41926,7 +41926,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1433" t="n">
-        <v>0.477889358997345</v>
+        <v>0.4778892993927</v>
       </c>
       <c r="H1433" t="n">
         <v>110870</v>
@@ -41955,7 +41955,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.488188713788986</v>
+        <v>0.488188683986664</v>
       </c>
       <c r="H1434" t="n">
         <v>96338</v>
@@ -41984,7 +41984,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.499861270189285</v>
+        <v>0.499861240386963</v>
       </c>
       <c r="H1435" t="n">
         <v>182362</v>
@@ -42042,7 +42042,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.506727457046509</v>
+        <v>0.506727516651154</v>
       </c>
       <c r="H1437" t="n">
         <v>568057</v>
@@ -42129,7 +42129,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.491621851921082</v>
+        <v>0.491621822118759</v>
       </c>
       <c r="H1440" t="n">
         <v>114661</v>
@@ -42158,7 +42158,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.4957415163517</v>
+        <v>0.495741575956345</v>
       </c>
       <c r="H1441" t="n">
         <v>41619</v>
@@ -42274,7 +42274,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.484068930149078</v>
+        <v>0.484068959951401</v>
       </c>
       <c r="H1445" t="n">
         <v>124909</v>
@@ -42303,7 +42303,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.482009053230286</v>
+        <v>0.48200911283493</v>
       </c>
       <c r="H1446" t="n">
         <v>108431</v>
@@ -42361,7 +42361,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.483382344245911</v>
+        <v>0.483382284641266</v>
       </c>
       <c r="H1448" t="n">
         <v>134448</v>
@@ -42390,7 +42390,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.481322467327118</v>
+        <v>0.481322437524796</v>
       </c>
       <c r="H1449" t="n">
         <v>76682</v>
@@ -42419,7 +42419,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.479262620210648</v>
+        <v>0.479262590408325</v>
       </c>
       <c r="H1450" t="n">
         <v>82266</v>
@@ -42448,7 +42448,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.472396373748779</v>
+        <v>0.472396343946457</v>
       </c>
       <c r="H1451" t="n">
         <v>133010</v>
@@ -42506,7 +42506,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.473769664764404</v>
+        <v>0.473769694566727</v>
       </c>
       <c r="H1453" t="n">
         <v>100740</v>
@@ -42535,7 +42535,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.466903388500214</v>
+        <v>0.466903358697891</v>
       </c>
       <c r="H1454" t="n">
         <v>100673</v>
@@ -42564,7 +42564,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.46072381734848</v>
+        <v>0.460723757743835</v>
       </c>
       <c r="H1455" t="n">
         <v>211205</v>
@@ -42593,7 +42593,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.463470309972763</v>
+        <v>0.463470369577408</v>
       </c>
       <c r="H1456" t="n">
         <v>63415</v>
@@ -42622,7 +42622,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.463470309972763</v>
+        <v>0.463470369577408</v>
       </c>
       <c r="H1457" t="n">
         <v>141749</v>
@@ -42651,7 +42651,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.46072381734848</v>
+        <v>0.460723757743835</v>
       </c>
       <c r="H1458" t="n">
         <v>68966</v>
@@ -42680,7 +42680,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.467590004205704</v>
+        <v>0.467589974403381</v>
       </c>
       <c r="H1459" t="n">
         <v>291240</v>
@@ -42709,7 +42709,7 @@
         <v>0.683000028133392</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.468963295221329</v>
+        <v>0.468963325023651</v>
       </c>
       <c r="H1460" t="n">
         <v>118516</v>
@@ -42738,7 +42738,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.466903388500214</v>
+        <v>0.466903358697891</v>
       </c>
       <c r="H1461" t="n">
         <v>25664</v>
@@ -42767,7 +42767,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.465530127286911</v>
+        <v>0.465530097484589</v>
       </c>
       <c r="H1462" t="n">
         <v>34926</v>
@@ -42796,7 +42796,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.472396373748779</v>
+        <v>0.472396343946457</v>
       </c>
       <c r="H1463" t="n">
         <v>110805</v>
@@ -42854,7 +42854,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.488188713788986</v>
+        <v>0.488188683986664</v>
       </c>
       <c r="H1465" t="n">
         <v>467970</v>
@@ -42941,7 +42941,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.504667639732361</v>
+        <v>0.504667580127716</v>
       </c>
       <c r="H1468" t="n">
         <v>701595</v>
@@ -42970,7 +42970,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.507414102554321</v>
+        <v>0.507414162158966</v>
       </c>
       <c r="H1469" t="n">
         <v>398658</v>
@@ -42999,7 +42999,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.504667639732361</v>
+        <v>0.504667580127716</v>
       </c>
       <c r="H1470" t="n">
         <v>144614</v>
@@ -43028,7 +43028,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.502607703208923</v>
+        <v>0.502607762813568</v>
       </c>
       <c r="H1471" t="n">
         <v>153872</v>
@@ -43057,7 +43057,7 @@
         <v>0.75</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.514966905117035</v>
+        <v>0.51496696472168</v>
       </c>
       <c r="H1472" t="n">
         <v>246817</v>
@@ -43086,7 +43086,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.514280438423157</v>
+        <v>0.514280319213867</v>
       </c>
       <c r="H1473" t="n">
         <v>201033</v>
@@ -43115,7 +43115,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.511533856391907</v>
+        <v>0.511533915996552</v>
       </c>
       <c r="H1474" t="n">
         <v>148210</v>
@@ -43202,7 +43202,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.502607703208923</v>
+        <v>0.502607762813568</v>
       </c>
       <c r="H1477" t="n">
         <v>37710</v>
@@ -43231,7 +43231,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.500547885894775</v>
+        <v>0.50054794549942</v>
       </c>
       <c r="H1478" t="n">
         <v>84732</v>
@@ -43260,7 +43260,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.492995023727417</v>
+        <v>0.492995053529739</v>
       </c>
       <c r="H1479" t="n">
         <v>148848</v>
@@ -43376,7 +43376,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.488188713788986</v>
+        <v>0.488188683986664</v>
       </c>
       <c r="H1483" t="n">
         <v>69502</v>
@@ -43492,7 +43492,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.488188713788986</v>
+        <v>0.488188683986664</v>
       </c>
       <c r="H1487" t="n">
         <v>54325</v>
@@ -43608,7 +43608,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.570583343505859</v>
+        <v>0.570583403110504</v>
       </c>
       <c r="H1491" t="n">
         <v>3162210</v>
@@ -43637,7 +43637,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.596675097942352</v>
+        <v>0.596675038337708</v>
       </c>
       <c r="H1492" t="n">
         <v>3741505</v>
@@ -43666,7 +43666,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.578822910785675</v>
+        <v>0.57882285118103</v>
       </c>
       <c r="H1493" t="n">
         <v>696071</v>
@@ -43695,7 +43695,7 @@
         <v>0.848999977111816</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.582942545413971</v>
+        <v>0.582942605018616</v>
       </c>
       <c r="H1494" t="n">
         <v>448898</v>
@@ -43753,7 +43753,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.573329865932465</v>
+        <v>0.573329925537109</v>
       </c>
       <c r="H1496" t="n">
         <v>196433</v>
@@ -43782,7 +43782,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.570583343505859</v>
+        <v>0.570583403110504</v>
       </c>
       <c r="H1497" t="n">
         <v>278364</v>
@@ -43811,7 +43811,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.570583343505859</v>
+        <v>0.570583403110504</v>
       </c>
       <c r="H1498" t="n">
         <v>480821</v>
@@ -43840,7 +43840,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.585689067840576</v>
+        <v>0.585689008235931</v>
       </c>
       <c r="H1499" t="n">
         <v>425929</v>
@@ -43927,7 +43927,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.57195657491684</v>
+        <v>0.571956694126129</v>
       </c>
       <c r="H1502" t="n">
         <v>129017</v>
@@ -43956,7 +43956,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.558910846710205</v>
+        <v>0.55891078710556</v>
       </c>
       <c r="H1503" t="n">
         <v>314413</v>
@@ -44101,7 +44101,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.547924816608429</v>
+        <v>0.547924876213074</v>
       </c>
       <c r="H1508" t="n">
         <v>118766</v>
@@ -44159,7 +44159,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.564403831958771</v>
+        <v>0.564403772354126</v>
       </c>
       <c r="H1510" t="n">
         <v>150451</v>
@@ -44188,7 +44188,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.558910846710205</v>
+        <v>0.55891078710556</v>
       </c>
       <c r="H1511" t="n">
         <v>128463</v>
@@ -44217,7 +44217,7 @@
         <v>0.802999973297119</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.551357924938202</v>
+        <v>0.551357984542847</v>
       </c>
       <c r="H1512" t="n">
         <v>72507</v>
@@ -44275,7 +44275,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.555477678775787</v>
+        <v>0.555477738380432</v>
       </c>
       <c r="H1514" t="n">
         <v>154548</v>
@@ -44391,7 +44391,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.57195657491684</v>
+        <v>0.571956694126129</v>
       </c>
       <c r="H1518" t="n">
         <v>363020</v>
@@ -44420,7 +44420,7 @@
         <v>0.830999970436096</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.570583343505859</v>
+        <v>0.570583403110504</v>
       </c>
       <c r="H1519" t="n">
         <v>132260</v>
@@ -44449,7 +44449,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.59598845243454</v>
+        <v>0.595988392829895</v>
       </c>
       <c r="H1520" t="n">
         <v>413857</v>
@@ -44652,7 +44652,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.620706796646118</v>
+        <v>0.620706856250763</v>
       </c>
       <c r="H1527" t="n">
         <v>62427</v>
@@ -44710,7 +44710,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.602854669094086</v>
+        <v>0.60285472869873</v>
       </c>
       <c r="H1529" t="n">
         <v>228530</v>
@@ -44913,7 +44913,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.602854669094086</v>
+        <v>0.60285472869873</v>
       </c>
       <c r="H1536" t="n">
         <v>877705</v>
@@ -45087,7 +45087,7 @@
         <v>0.837000012397766</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.57470315694809</v>
+        <v>0.574703097343445</v>
       </c>
       <c r="H1542" t="n">
         <v>237218</v>
@@ -45145,7 +45145,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.593241989612579</v>
+        <v>0.593241930007935</v>
       </c>
       <c r="H1544" t="n">
         <v>68081</v>
@@ -45232,7 +45232,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.593928515911102</v>
+        <v>0.593928575515747</v>
       </c>
       <c r="H1547" t="n">
         <v>217744</v>
@@ -45261,7 +45261,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.59598845243454</v>
+        <v>0.595988392829895</v>
       </c>
       <c r="H1548" t="n">
         <v>36332</v>
@@ -45290,7 +45290,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.602854669094086</v>
+        <v>0.60285472869873</v>
       </c>
       <c r="H1549" t="n">
         <v>75674</v>
@@ -45319,7 +45319,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.602854669094086</v>
+        <v>0.60285472869873</v>
       </c>
       <c r="H1550" t="n">
         <v>79760</v>
@@ -45348,7 +45348,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.593928515911102</v>
+        <v>0.593928575515747</v>
       </c>
       <c r="H1551" t="n">
         <v>139151</v>
@@ -45406,7 +45406,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.586375713348389</v>
+        <v>0.586375653743744</v>
       </c>
       <c r="H1553" t="n">
         <v>107203</v>
@@ -45435,7 +45435,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.604227960109711</v>
+        <v>0.604227900505066</v>
       </c>
       <c r="H1554" t="n">
         <v>137928</v>
@@ -45551,7 +45551,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.631006300449371</v>
+        <v>0.631006240844727</v>
       </c>
       <c r="H1558" t="n">
         <v>760028</v>
@@ -45580,7 +45580,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.628946304321289</v>
+        <v>0.628946363925934</v>
       </c>
       <c r="H1559" t="n">
         <v>261721</v>
@@ -45638,7 +45638,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.615213930606842</v>
+        <v>0.615213871002197</v>
       </c>
       <c r="H1561" t="n">
         <v>137167</v>
@@ -45667,7 +45667,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.590495526790619</v>
+        <v>0.590495467185974</v>
       </c>
       <c r="H1562" t="n">
         <v>422793</v>
@@ -45696,7 +45696,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.578822910785675</v>
+        <v>0.57882285118103</v>
       </c>
       <c r="H1563" t="n">
         <v>401094</v>
@@ -45725,7 +45725,7 @@
         <v>0.842999994754791</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.578822910785675</v>
+        <v>0.57882285118103</v>
       </c>
       <c r="H1564" t="n">
         <v>193810</v>
@@ -45754,7 +45754,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.53625226020813</v>
+        <v>0.536252319812775</v>
       </c>
       <c r="H1565" t="n">
         <v>1175570</v>
@@ -45783,7 +45783,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.542431950569153</v>
+        <v>0.542431890964508</v>
       </c>
       <c r="H1566" t="n">
         <v>544318</v>
@@ -45899,7 +45899,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.504667639732361</v>
+        <v>0.504667580127716</v>
       </c>
       <c r="H1570" t="n">
         <v>755874</v>
@@ -45928,7 +45928,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.473769664764404</v>
+        <v>0.473769694566727</v>
       </c>
       <c r="H1571" t="n">
         <v>1505046</v>
@@ -45957,7 +45957,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.465530127286911</v>
+        <v>0.465530097484589</v>
       </c>
       <c r="H1572" t="n">
         <v>1166320</v>
@@ -45986,7 +45986,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.471709728240967</v>
+        <v>0.471709668636322</v>
       </c>
       <c r="H1573" t="n">
         <v>624869</v>
@@ -46073,7 +46073,7 @@
         <v>0.717000007629395</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.492308467626572</v>
+        <v>0.492308437824249</v>
       </c>
       <c r="H1576" t="n">
         <v>339976</v>
@@ -46102,7 +46102,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.484068930149078</v>
+        <v>0.484068959951401</v>
       </c>
       <c r="H1577" t="n">
         <v>347860</v>
@@ -46131,7 +46131,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.488188713788986</v>
+        <v>0.488188683986664</v>
       </c>
       <c r="H1578" t="n">
         <v>202425</v>
@@ -46450,7 +46450,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.542431950569153</v>
+        <v>0.542431890964508</v>
       </c>
       <c r="H1589" t="n">
         <v>826806</v>
@@ -46479,7 +46479,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.530759334564209</v>
+        <v>0.530759274959564</v>
       </c>
       <c r="H1590" t="n">
         <v>628266</v>
@@ -46595,7 +46595,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.492995023727417</v>
+        <v>0.492995053529739</v>
       </c>
       <c r="H1594" t="n">
         <v>433543</v>
@@ -46624,7 +46624,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.49917459487915</v>
+        <v>0.499174624681473</v>
       </c>
       <c r="H1595" t="n">
         <v>263180</v>
@@ -46711,7 +46711,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.49917459487915</v>
+        <v>0.499174624681473</v>
       </c>
       <c r="H1598" t="n">
         <v>206269</v>
@@ -46769,7 +46769,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.521833181381226</v>
+        <v>0.52183324098587</v>
       </c>
       <c r="H1600" t="n">
         <v>553417</v>
@@ -46914,7 +46914,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.522519767284393</v>
+        <v>0.522519826889038</v>
       </c>
       <c r="H1605" t="n">
         <v>207424</v>
@@ -46972,7 +46972,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.518400073051453</v>
+        <v>0.518400132656097</v>
       </c>
       <c r="H1607" t="n">
         <v>492058</v>
@@ -47146,7 +47146,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.4957415163517</v>
+        <v>0.495741575956345</v>
       </c>
       <c r="H1613" t="n">
         <v>580287</v>
@@ -47204,7 +47204,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.492995023727417</v>
+        <v>0.492995053529739</v>
       </c>
       <c r="H1615" t="n">
         <v>475588</v>
@@ -47320,7 +47320,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.534192383289337</v>
+        <v>0.534192323684692</v>
       </c>
       <c r="H1619" t="n">
         <v>925748</v>
@@ -47349,7 +47349,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.541632413864136</v>
+        <v>0.541632354259491</v>
       </c>
       <c r="H1620" t="n">
         <v>1350968</v>
@@ -47407,7 +47407,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1622" t="n">
         <v>254768</v>
@@ -47668,7 +47668,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.526752412319183</v>
+        <v>0.526752471923828</v>
       </c>
       <c r="H1631" t="n">
         <v>166682</v>
@@ -47842,7 +47842,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.51410436630249</v>
+        <v>0.514104425907135</v>
       </c>
       <c r="H1637" t="n">
         <v>676981</v>
@@ -47958,7 +47958,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.4798803627491</v>
+        <v>0.479880332946777</v>
       </c>
       <c r="H1641" t="n">
         <v>299640</v>
@@ -48016,7 +48016,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.4798803627491</v>
+        <v>0.479880332946777</v>
       </c>
       <c r="H1643" t="n">
         <v>166140</v>
@@ -48045,7 +48045,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.485088378190994</v>
+        <v>0.485088348388672</v>
       </c>
       <c r="H1644" t="n">
         <v>144371</v>
@@ -48074,7 +48074,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.499224424362183</v>
+        <v>0.499224364757538</v>
       </c>
       <c r="H1645" t="n">
         <v>385344</v>
@@ -48103,7 +48103,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.509640395641327</v>
+        <v>0.509640336036682</v>
       </c>
       <c r="H1646" t="n">
         <v>322860</v>
@@ -48132,7 +48132,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.48955237865448</v>
+        <v>0.489552408456802</v>
       </c>
       <c r="H1647" t="n">
         <v>369808</v>
@@ -48161,7 +48161,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.485832333564758</v>
+        <v>0.485832363367081</v>
       </c>
       <c r="H1648" t="n">
         <v>167173</v>
@@ -48219,7 +48219,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G1650" t="n">
-        <v>0.485832333564758</v>
+        <v>0.485832363367081</v>
       </c>
       <c r="H1650" t="n">
         <v>211724</v>
@@ -48248,7 +48248,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.495504349470139</v>
+        <v>0.495504379272461</v>
       </c>
       <c r="H1651" t="n">
         <v>48388</v>
@@ -48277,7 +48277,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.488064378499985</v>
+        <v>0.488064348697662</v>
       </c>
       <c r="H1652" t="n">
         <v>54926</v>
@@ -48393,7 +48393,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.450120359659195</v>
+        <v>0.450120389461517</v>
       </c>
       <c r="H1656" t="n">
         <v>244689</v>
@@ -48422,7 +48422,7 @@
         <v>0.601000010967255</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.447144359350204</v>
+        <v>0.447144329547882</v>
       </c>
       <c r="H1657" t="n">
         <v>244002</v>
@@ -48451,7 +48451,7 @@
         <v>0.605000019073486</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.450120359659195</v>
+        <v>0.450120389461517</v>
       </c>
       <c r="H1658" t="n">
         <v>139639</v>
@@ -48480,7 +48480,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.470208406448364</v>
+        <v>0.470208376646042</v>
       </c>
       <c r="H1659" t="n">
         <v>162510</v>
@@ -48596,7 +48596,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.453840374946594</v>
+        <v>0.453840345144272</v>
       </c>
       <c r="H1663" t="n">
         <v>265644</v>
@@ -48654,7 +48654,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.521544396877289</v>
+        <v>0.521544456481934</v>
       </c>
       <c r="H1665" t="n">
         <v>564927</v>
@@ -48712,7 +48712,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.528984427452087</v>
+        <v>0.528984367847443</v>
       </c>
       <c r="H1667" t="n">
         <v>409939</v>
@@ -48741,7 +48741,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.531960368156433</v>
+        <v>0.531960427761078</v>
       </c>
       <c r="H1668" t="n">
         <v>502365</v>
@@ -48770,7 +48770,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.528984427452087</v>
+        <v>0.528984367847443</v>
       </c>
       <c r="H1669" t="n">
         <v>74346</v>
@@ -48799,7 +48799,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.541632413864136</v>
+        <v>0.541632354259491</v>
       </c>
       <c r="H1670" t="n">
         <v>465553</v>
@@ -48828,7 +48828,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.526752412319183</v>
+        <v>0.526752471923828</v>
       </c>
       <c r="H1671" t="n">
         <v>253800</v>
@@ -48886,7 +48886,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.541632413864136</v>
+        <v>0.541632354259491</v>
       </c>
       <c r="H1673" t="n">
         <v>202773</v>
@@ -49060,7 +49060,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.541632413864136</v>
+        <v>0.541632354259491</v>
       </c>
       <c r="H1679" t="n">
         <v>297304</v>
@@ -49089,7 +49089,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.540888369083405</v>
+        <v>0.540888428688049</v>
       </c>
       <c r="H1680" t="n">
         <v>1013313</v>
@@ -49147,7 +49147,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.536424458026886</v>
+        <v>0.536424398422241</v>
       </c>
       <c r="H1682" t="n">
         <v>46537</v>
@@ -49321,7 +49321,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.544608354568481</v>
+        <v>0.544608414173126</v>
       </c>
       <c r="H1688" t="n">
         <v>137416</v>
@@ -49379,7 +49379,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.549816429615021</v>
+        <v>0.549816489219666</v>
       </c>
       <c r="H1690" t="n">
         <v>94228</v>
@@ -49408,7 +49408,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1691" t="n">
         <v>169043</v>
@@ -49553,7 +49553,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.521544396877289</v>
+        <v>0.521544456481934</v>
       </c>
       <c r="H1696" t="n">
         <v>68957</v>
@@ -49698,7 +49698,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.523776412010193</v>
+        <v>0.523776352405548</v>
       </c>
       <c r="H1701" t="n">
         <v>45774</v>
@@ -49988,7 +49988,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.504432380199432</v>
+        <v>0.504432320594788</v>
       </c>
       <c r="H1711" t="n">
         <v>51224</v>
@@ -50017,7 +50017,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.497736394405365</v>
+        <v>0.497736364603043</v>
       </c>
       <c r="H1712" t="n">
         <v>114764</v>
@@ -50046,7 +50046,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.498480409383774</v>
+        <v>0.498480439186096</v>
       </c>
       <c r="H1713" t="n">
         <v>51573</v>
@@ -50075,7 +50075,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.498480409383774</v>
+        <v>0.498480439186096</v>
       </c>
       <c r="H1714" t="n">
         <v>58912</v>
@@ -50104,7 +50104,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.488064378499985</v>
+        <v>0.488064348697662</v>
       </c>
       <c r="H1715" t="n">
         <v>56235</v>
@@ -50133,7 +50133,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.48434442281723</v>
+        <v>0.484344393014908</v>
       </c>
       <c r="H1716" t="n">
         <v>77196</v>
@@ -50162,7 +50162,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.4798803627491</v>
+        <v>0.479880332946777</v>
       </c>
       <c r="H1717" t="n">
         <v>70057</v>
@@ -50191,7 +50191,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.48955237865448</v>
+        <v>0.489552408456802</v>
       </c>
       <c r="H1718" t="n">
         <v>55128</v>
@@ -50278,7 +50278,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.485088378190994</v>
+        <v>0.485088348388672</v>
       </c>
       <c r="H1721" t="n">
         <v>111983</v>
@@ -50365,7 +50365,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.479136347770691</v>
+        <v>0.479136377573013</v>
       </c>
       <c r="H1724" t="n">
         <v>24498</v>
@@ -50452,7 +50452,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.467232376337051</v>
+        <v>0.467232346534729</v>
       </c>
       <c r="H1727" t="n">
         <v>28541</v>
@@ -50481,7 +50481,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.467232376337051</v>
+        <v>0.467232346534729</v>
       </c>
       <c r="H1728" t="n">
         <v>35986</v>
@@ -50568,7 +50568,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.470208406448364</v>
+        <v>0.470208376646042</v>
       </c>
       <c r="H1731" t="n">
         <v>36604</v>
@@ -50626,7 +50626,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.470208406448364</v>
+        <v>0.470208376646042</v>
       </c>
       <c r="H1733" t="n">
         <v>25908</v>
@@ -50655,7 +50655,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.47467240691185</v>
+        <v>0.474672377109528</v>
       </c>
       <c r="H1734" t="n">
         <v>20309</v>
@@ -50713,7 +50713,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.485832333564758</v>
+        <v>0.485832363367081</v>
       </c>
       <c r="H1736" t="n">
         <v>90700</v>
@@ -50887,7 +50887,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.494760394096375</v>
+        <v>0.494760423898697</v>
       </c>
       <c r="H1742" t="n">
         <v>149335</v>
@@ -50916,7 +50916,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.494760394096375</v>
+        <v>0.494760423898697</v>
       </c>
       <c r="H1743" t="n">
         <v>52291</v>
@@ -50974,7 +50974,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.494760394096375</v>
+        <v>0.494760423898697</v>
       </c>
       <c r="H1745" t="n">
         <v>150936</v>
@@ -51003,7 +51003,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.494760394096375</v>
+        <v>0.494760423898697</v>
       </c>
       <c r="H1746" t="n">
         <v>117026</v>
@@ -51032,7 +51032,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.48955237865448</v>
+        <v>0.489552408456802</v>
       </c>
       <c r="H1747" t="n">
         <v>298673</v>
@@ -51061,7 +51061,7 @@
         <v>0.662999987602234</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.493272334337234</v>
+        <v>0.493272364139557</v>
       </c>
       <c r="H1748" t="n">
         <v>209271</v>
@@ -51119,7 +51119,7 @@
         <v>0.658999979496002</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.490296393632889</v>
+        <v>0.490296363830566</v>
       </c>
       <c r="H1750" t="n">
         <v>150284</v>
@@ -51177,7 +51177,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.485088378190994</v>
+        <v>0.485088348388672</v>
       </c>
       <c r="H1752" t="n">
         <v>160071</v>
@@ -51206,7 +51206,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.4798803627491</v>
+        <v>0.479880332946777</v>
       </c>
       <c r="H1753" t="n">
         <v>117955</v>
@@ -51554,7 +51554,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.48434442281723</v>
+        <v>0.484344393014908</v>
       </c>
       <c r="H1765" t="n">
         <v>100390</v>
@@ -51612,7 +51612,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.488064378499985</v>
+        <v>0.488064348697662</v>
       </c>
       <c r="H1767" t="n">
         <v>67249</v>
@@ -51641,7 +51641,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.4798803627491</v>
+        <v>0.479880332946777</v>
       </c>
       <c r="H1768" t="n">
         <v>116726</v>
@@ -51670,7 +51670,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.479136347770691</v>
+        <v>0.479136377573013</v>
       </c>
       <c r="H1769" t="n">
         <v>270208</v>
@@ -51699,7 +51699,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.4798803627491</v>
+        <v>0.479880332946777</v>
       </c>
       <c r="H1770" t="n">
         <v>38084</v>
@@ -51728,7 +51728,7 @@
         <v>0.652999997138977</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.485832333564758</v>
+        <v>0.485832363367081</v>
       </c>
       <c r="H1771" t="n">
         <v>189419</v>
@@ -51786,7 +51786,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.495504349470139</v>
+        <v>0.495504379272461</v>
       </c>
       <c r="H1773" t="n">
         <v>139590</v>
@@ -51873,7 +51873,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.488064378499985</v>
+        <v>0.488064348697662</v>
       </c>
       <c r="H1776" t="n">
         <v>48203</v>
@@ -51931,7 +51931,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.502200424671173</v>
+        <v>0.502200365066528</v>
       </c>
       <c r="H1778" t="n">
         <v>167037</v>
@@ -51960,7 +51960,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.499224424362183</v>
+        <v>0.499224364757538</v>
       </c>
       <c r="H1779" t="n">
         <v>9503</v>
@@ -51989,7 +51989,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.494760394096375</v>
+        <v>0.494760423898697</v>
       </c>
       <c r="H1780" t="n">
         <v>114011</v>
@@ -52047,7 +52047,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.499224424362183</v>
+        <v>0.499224364757538</v>
       </c>
       <c r="H1782" t="n">
         <v>30561</v>
@@ -52105,7 +52105,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.504432380199432</v>
+        <v>0.504432320594788</v>
       </c>
       <c r="H1784" t="n">
         <v>112160</v>
@@ -52134,7 +52134,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.50889641046524</v>
+        <v>0.508896470069885</v>
       </c>
       <c r="H1785" t="n">
         <v>134275</v>
@@ -52163,7 +52163,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.509640395641327</v>
+        <v>0.509640336036682</v>
       </c>
       <c r="H1786" t="n">
         <v>252829</v>
@@ -52366,7 +52366,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.518568456172943</v>
+        <v>0.518568396568298</v>
       </c>
       <c r="H1793" t="n">
         <v>110966</v>
@@ -52424,7 +52424,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.518568456172943</v>
+        <v>0.518568396568298</v>
       </c>
       <c r="H1795" t="n">
         <v>136213</v>
@@ -52656,7 +52656,7 @@
         <v>0.721000015735626</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.536424458026886</v>
+        <v>0.536424398422241</v>
       </c>
       <c r="H1803" t="n">
         <v>344402</v>
@@ -52743,7 +52743,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.534192383289337</v>
+        <v>0.534192323684692</v>
       </c>
       <c r="H1806" t="n">
         <v>98180</v>
@@ -52830,7 +52830,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1809" t="n">
         <v>189649</v>
@@ -52859,7 +52859,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1810" t="n">
         <v>284927</v>
@@ -52888,7 +52888,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1811" t="n">
         <v>227711</v>
@@ -52917,7 +52917,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1812" t="n">
         <v>139864</v>
@@ -52975,7 +52975,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1814" t="n">
         <v>299732</v>
@@ -53033,7 +53033,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.546096384525299</v>
+        <v>0.546096444129944</v>
       </c>
       <c r="H1816" t="n">
         <v>92269</v>
@@ -53091,7 +53091,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.540888369083405</v>
+        <v>0.540888428688049</v>
       </c>
       <c r="H1818" t="n">
         <v>46651</v>
@@ -53236,7 +53236,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.534192383289337</v>
+        <v>0.534192323684692</v>
       </c>
       <c r="H1823" t="n">
         <v>119848</v>
@@ -53265,7 +53265,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.534192383289337</v>
+        <v>0.534192323684692</v>
       </c>
       <c r="H1824" t="n">
         <v>105425</v>
@@ -53468,7 +53468,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.535680413246155</v>
+        <v>0.5356804728508</v>
       </c>
       <c r="H1831" t="n">
         <v>119882</v>
@@ -53555,7 +53555,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.531960368156433</v>
+        <v>0.531960427761078</v>
       </c>
       <c r="H1834" t="n">
         <v>94560</v>
@@ -53700,7 +53700,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.526752412319183</v>
+        <v>0.526752471923828</v>
       </c>
       <c r="H1839" t="n">
         <v>243929</v>
@@ -53903,7 +53903,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.576600432395935</v>
+        <v>0.57660037279129</v>
       </c>
       <c r="H1846" t="n">
         <v>147695</v>
@@ -53961,7 +53961,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.557256519794464</v>
+        <v>0.557256460189819</v>
       </c>
       <c r="H1848" t="n">
         <v>372816</v>
@@ -53990,7 +53990,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.561720430850983</v>
+        <v>0.561720490455627</v>
       </c>
       <c r="H1849" t="n">
         <v>100055</v>
@@ -54019,7 +54019,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.560232400894165</v>
+        <v>0.56023246049881</v>
       </c>
       <c r="H1850" t="n">
         <v>238198</v>
@@ -54164,7 +54164,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.576600432395935</v>
+        <v>0.57660037279129</v>
       </c>
       <c r="H1855" t="n">
         <v>66625</v>
@@ -54541,7 +54541,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.5981764793396</v>
+        <v>0.598176419734955</v>
       </c>
       <c r="H1868" t="n">
         <v>183898</v>
@@ -54570,7 +54570,7 @@
         <v>0.796999990940094</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.592968463897705</v>
+        <v>0.59296840429306</v>
       </c>
       <c r="H1869" t="n">
         <v>188177</v>
@@ -54686,7 +54686,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.604128420352936</v>
+        <v>0.604128479957581</v>
       </c>
       <c r="H1873" t="n">
         <v>113503</v>
@@ -54773,7 +54773,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.576600432395935</v>
+        <v>0.57660037279129</v>
       </c>
       <c r="H1876" t="n">
         <v>102801</v>
@@ -54831,7 +54831,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.577344417572021</v>
+        <v>0.577344477176666</v>
       </c>
       <c r="H1878" t="n">
         <v>369991</v>
@@ -54947,7 +54947,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H1882" t="n">
         <v>48304</v>
@@ -54976,7 +54976,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H1883" t="n">
         <v>44896</v>
@@ -55005,7 +55005,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.587200939655304</v>
+        <v>0.587200880050659</v>
       </c>
       <c r="H1884" t="n">
         <v>150551</v>
@@ -55092,7 +55092,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.571091175079346</v>
+        <v>0.57109123468399</v>
       </c>
       <c r="H1887" t="n">
         <v>110758</v>
@@ -55498,7 +55498,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.579951524734497</v>
+        <v>0.579951584339142</v>
       </c>
       <c r="H1901" t="n">
         <v>55873</v>
@@ -55527,7 +55527,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.571091175079346</v>
+        <v>0.57109123468399</v>
       </c>
       <c r="H1902" t="n">
         <v>43336</v>
@@ -55701,7 +55701,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.575924038887024</v>
+        <v>0.575924098491669</v>
       </c>
       <c r="H1908" t="n">
         <v>19593</v>
@@ -55730,7 +55730,7 @@
         <v>0.728999972343445</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.587200939655304</v>
+        <v>0.587200880050659</v>
       </c>
       <c r="H1909" t="n">
         <v>215658</v>
@@ -55759,7 +55759,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.588006496429443</v>
+        <v>0.588006436824799</v>
       </c>
       <c r="H1910" t="n">
         <v>150088</v>
@@ -55788,7 +55788,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1911" t="n">
-        <v>0.588006496429443</v>
+        <v>0.588006436824799</v>
       </c>
       <c r="H1911" t="n">
         <v>69993</v>
@@ -55933,7 +55933,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.570285737514496</v>
+        <v>0.570285677909851</v>
       </c>
       <c r="H1916" t="n">
         <v>42350</v>
@@ -55991,7 +55991,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1918" t="n">
-        <v>0.570285737514496</v>
+        <v>0.570285677909851</v>
       </c>
       <c r="H1918" t="n">
         <v>96516</v>
@@ -56165,7 +56165,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.570285737514496</v>
+        <v>0.570285677909851</v>
       </c>
       <c r="H1924" t="n">
         <v>38965</v>
@@ -56223,7 +56223,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.571091175079346</v>
+        <v>0.57109123468399</v>
       </c>
       <c r="H1926" t="n">
         <v>55182</v>
@@ -56281,7 +56281,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.579951524734497</v>
+        <v>0.579951584339142</v>
       </c>
       <c r="H1928" t="n">
         <v>72842</v>
@@ -56339,7 +56339,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.579951524734497</v>
+        <v>0.579951584339142</v>
       </c>
       <c r="H1930" t="n">
         <v>316631</v>
@@ -56455,7 +56455,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.575924038887024</v>
+        <v>0.575924098491669</v>
       </c>
       <c r="H1934" t="n">
         <v>128687</v>
@@ -56484,7 +56484,7 @@
         <v>0.708999991416931</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.571091175079346</v>
+        <v>0.57109123468399</v>
       </c>
       <c r="H1935" t="n">
         <v>24074</v>
@@ -56890,7 +56890,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G1949" t="n">
-        <v>0.575924038887024</v>
+        <v>0.575924098491669</v>
       </c>
       <c r="H1949" t="n">
         <v>204531</v>
@@ -57615,7 +57615,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.560619831085205</v>
+        <v>0.56061977148056</v>
       </c>
       <c r="H1974" t="n">
         <v>28443</v>
@@ -57702,7 +57702,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.560619831085205</v>
+        <v>0.56061977148056</v>
       </c>
       <c r="H1977" t="n">
         <v>37285</v>
@@ -57905,7 +57905,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1984" t="n">
-        <v>0.560619831085205</v>
+        <v>0.56061977148056</v>
       </c>
       <c r="H1984" t="n">
         <v>9570</v>
@@ -57934,7 +57934,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1985" t="n">
-        <v>0.560619831085205</v>
+        <v>0.56061977148056</v>
       </c>
       <c r="H1985" t="n">
         <v>22986</v>
@@ -58108,7 +58108,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1991" t="n">
-        <v>0.560619831085205</v>
+        <v>0.56061977148056</v>
       </c>
       <c r="H1991" t="n">
         <v>8687</v>
@@ -58659,7 +58659,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.570285737514496</v>
+        <v>0.570285677909851</v>
       </c>
       <c r="H2010" t="n">
         <v>59767</v>
@@ -58833,7 +58833,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.563036262989044</v>
+        <v>0.563036322593689</v>
       </c>
       <c r="H2016" t="n">
         <v>56880</v>
@@ -59007,7 +59007,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G2022" t="n">
-        <v>0.57350766658783</v>
+        <v>0.573507606983185</v>
       </c>
       <c r="H2022" t="n">
         <v>132772</v>
@@ -59065,7 +59065,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2024" t="n">
-        <v>0.575924038887024</v>
+        <v>0.575924098491669</v>
       </c>
       <c r="H2024" t="n">
         <v>119478</v>
@@ -59123,7 +59123,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G2026" t="n">
-        <v>0.575924038887024</v>
+        <v>0.575924098491669</v>
       </c>
       <c r="H2026" t="n">
         <v>56202</v>
@@ -59268,7 +59268,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2031" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2031" t="n">
         <v>105092</v>
@@ -59297,7 +59297,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2032" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2032" t="n">
         <v>91740</v>
@@ -59326,7 +59326,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2033" t="n">
-        <v>0.589617371559143</v>
+        <v>0.589617431163788</v>
       </c>
       <c r="H2033" t="n">
         <v>164573</v>
@@ -59355,7 +59355,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2034" t="n">
-        <v>0.594450294971466</v>
+        <v>0.594450354576111</v>
       </c>
       <c r="H2034" t="n">
         <v>83928</v>
@@ -59384,7 +59384,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2035" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2035" t="n">
         <v>158407</v>
@@ -59413,7 +59413,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2036" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2036" t="n">
         <v>111634</v>
@@ -59442,7 +59442,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2037" t="n">
-        <v>0.594450294971466</v>
+        <v>0.594450354576111</v>
       </c>
       <c r="H2037" t="n">
         <v>100093</v>
@@ -59500,7 +59500,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2039" t="n">
-        <v>0.599283277988434</v>
+        <v>0.599283218383789</v>
       </c>
       <c r="H2039" t="n">
         <v>286540</v>
@@ -59703,7 +59703,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2046" t="n">
-        <v>0.600894272327423</v>
+        <v>0.600894212722778</v>
       </c>
       <c r="H2046" t="n">
         <v>83136</v>
@@ -59732,7 +59732,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2047" t="n">
-        <v>0.606532633304596</v>
+        <v>0.606532692909241</v>
       </c>
       <c r="H2047" t="n">
         <v>152713</v>
@@ -59819,7 +59819,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2050" t="n">
-        <v>0.606532633304596</v>
+        <v>0.606532692909241</v>
       </c>
       <c r="H2050" t="n">
         <v>26123</v>
@@ -60022,7 +60022,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2057" t="n">
-        <v>0.603310704231262</v>
+        <v>0.603310763835907</v>
       </c>
       <c r="H2057" t="n">
         <v>41986</v>
@@ -60080,7 +60080,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2059" t="n">
-        <v>0.603310704231262</v>
+        <v>0.603310763835907</v>
       </c>
       <c r="H2059" t="n">
         <v>29848</v>
@@ -60167,7 +60167,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G2062" t="n">
-        <v>0.589617371559143</v>
+        <v>0.589617431163788</v>
       </c>
       <c r="H2062" t="n">
         <v>156128</v>
@@ -60486,7 +60486,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2073" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2073" t="n">
         <v>57866</v>
@@ -60573,7 +60573,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2076" t="n">
         <v>102146</v>
@@ -60602,7 +60602,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.603310704231262</v>
+        <v>0.603310763835907</v>
       </c>
       <c r="H2077" t="n">
         <v>65346</v>
@@ -60631,7 +60631,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G2078" t="n">
-        <v>0.599283277988434</v>
+        <v>0.599283218383789</v>
       </c>
       <c r="H2078" t="n">
         <v>46184</v>
@@ -60689,7 +60689,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2080" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2080" t="n">
         <v>49199</v>
@@ -60776,7 +60776,7 @@
         <v>0.74099999666214</v>
       </c>
       <c r="G2083" t="n">
-        <v>0.596866846084595</v>
+        <v>0.59686678647995</v>
       </c>
       <c r="H2083" t="n">
         <v>37907</v>
@@ -60834,7 +60834,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G2085" t="n">
-        <v>0.594450294971466</v>
+        <v>0.594450354576111</v>
       </c>
       <c r="H2085" t="n">
         <v>112095</v>
@@ -60921,7 +60921,7 @@
         <v>0.749000012874603</v>
       </c>
       <c r="G2088" t="n">
-        <v>0.603310704231262</v>
+        <v>0.603310763835907</v>
       </c>
       <c r="H2088" t="n">
         <v>42803</v>
@@ -61037,7 +61037,7 @@
         <v>0.753000020980835</v>
       </c>
       <c r="G2092" t="n">
-        <v>0.606532633304596</v>
+        <v>0.606532692909241</v>
       </c>
       <c r="H2092" t="n">
         <v>183383</v>
@@ -61153,7 +61153,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G2096" t="n">
-        <v>0.623447895050049</v>
+        <v>0.623447954654694</v>
       </c>
       <c r="H2096" t="n">
         <v>274976</v>
@@ -61385,7 +61385,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2104" t="n">
-        <v>0.642779648303986</v>
+        <v>0.642779588699341</v>
       </c>
       <c r="H2104" t="n">
         <v>127456</v>
@@ -61472,7 +61472,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2107" t="n">
-        <v>0.642779648303986</v>
+        <v>0.642779588699341</v>
       </c>
       <c r="H2107" t="n">
         <v>150455</v>
@@ -61617,7 +61617,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2112" t="n">
-        <v>0.642779648303986</v>
+        <v>0.642779588699341</v>
       </c>
       <c r="H2112" t="n">
         <v>95378</v>
@@ -61675,7 +61675,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G2114" t="n">
-        <v>0.639557719230652</v>
+        <v>0.639557659626007</v>
       </c>
       <c r="H2114" t="n">
         <v>134503</v>
@@ -61762,7 +61762,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G2117" t="n">
-        <v>0.642779648303986</v>
+        <v>0.642779588699341</v>
       </c>
       <c r="H2117" t="n">
         <v>75271</v>
@@ -61849,7 +61849,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G2120" t="n">
-        <v>0.658889353275299</v>
+        <v>0.658889412879944</v>
       </c>
       <c r="H2120" t="n">
         <v>322468</v>
@@ -62052,7 +62052,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.702385723590851</v>
+        <v>0.702385783195496</v>
       </c>
       <c r="H2127" t="n">
         <v>304460</v>
@@ -80038,6 +80038,35 @@
         <v>282418</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.827000021934509</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.827000021934509</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.809000015258789</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.809000015258789</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.809000015258789</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>81477</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>
